--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -10,58 +10,22 @@
     <x:sheet name="March 2026" sheetId="8" r:id="rId8"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -116,7 +80,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -143,12 +107,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -159,17 +117,23 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -177,20 +141,13 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -218,15 +175,15 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="15">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -238,14 +195,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -263,10 +220,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -277,13 +234,30 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -438,37 +412,37 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -477,16 +451,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -495,67 +466,78 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -567,20 +549,20 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -588,6 +570,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -851,190 +837,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46049.5725925926</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46049.5726273148</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="J6" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46049.5962615741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="B9" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>23</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="B11" s="23" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2102,190 +2084,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="G6" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
+      <x:c r="H6" s="13">
+        <x:v>46078.2888888889</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46078.2901041667</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46078.2888888889</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46078.2901041667</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46089.2508680556</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="B9" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>23</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="B11" s="23" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>CERTIFICATE SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -141,7 +141,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -175,7 +175,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="15">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -220,10 +220,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -234,30 +234,13 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="none">
+      <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="thick">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -439,10 +422,13 @@
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -451,22 +437,19 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -533,11 +516,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -549,11 +536,7 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -561,8 +544,12 @@
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -570,10 +557,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -839,7 +822,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>46023</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -971,14 +954,12 @@
       <x:c r="L8" s="9" t="s"/>
       <x:c r="M8" s="9" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -987,41 +968,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2002,13 +1991,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2218,14 +2208,12 @@
       <x:c r="L8" s="9" t="s"/>
       <x:c r="M8" s="9" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -2234,41 +2222,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3249,13 +3245,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -453,7 +453,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -489,27 +489,31 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -883,7 +887,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -939,20 +943,20 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -970,44 +974,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="24" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="27" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2137,7 +2141,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -2193,20 +2197,20 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -2224,44 +2228,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="24" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="27" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -857,7 +857,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -927,7 +927,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>
@@ -2111,7 +2111,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -2181,7 +2181,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -23,9 +23,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <x:si>
     <x:t>CERTIFICATE SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -80,7 +116,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -125,15 +161,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -148,6 +184,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -395,27 +438,24 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -437,10 +477,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -453,7 +496,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -484,36 +527,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -540,15 +567,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -859,18 +886,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -888,75 +903,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46049.5725925926</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46049.5726273148</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46049.5962615741</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46049.5725925926</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46049.5726273148</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46049.5962615741</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -974,44 +1001,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>11</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2113,18 +2140,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2142,75 +2157,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46078.2888888889</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46078.2901041667</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46089.2508680556</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46078.2888888889</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46078.2901041667</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46089.2508680556</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -2228,44 +2255,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>11</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -427,11 +427,14 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -496,7 +499,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -526,6 +529,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -836,7 +843,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46023</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -908,80 +917,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46049.5725925926</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46049.5726273148</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="s">
+      <x:c r="J8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46049.5962615741</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -1001,44 +1010,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="C11" s="16" t="s"/>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="17" t="s"/>
+      <x:c r="F11" s="17" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="B13" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="24" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2090,7 +2099,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46082</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -2162,80 +2173,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46078.2888888889</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46078.2901041667</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="s">
+      <x:c r="J8" s="12" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46089.2508680556</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -2255,44 +2266,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="C11" s="16" t="s"/>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="17" t="s"/>
+      <x:c r="F11" s="17" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="B13" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="24" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -23,9 +23,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <x:si>
-    <x:t>CERTIFICATE SUMMARY</x:t>
+    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CERTIFICATES SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XIV | January 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -100,6 +106,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>XIV | March 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-06446</x:t>
   </x:si>
   <x:si>
@@ -116,7 +125,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -156,6 +165,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -427,17 +460,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -450,56 +489,56 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -530,71 +569,79 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -823,58 +870,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46023</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -917,81 +964,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="F8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46049.5725925926</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="15">
         <x:v>46049.5726273148</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="J8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>46049.5962615741</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1010,44 +1057,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="B11" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
-        <x:v>23</x:v>
+      <x:c r="B12" s="20" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2034,7 +2081,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>
@@ -2079,58 +2126,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -2173,81 +2220,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46078.2888888889</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="15">
         <x:v>46078.2901041667</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="J8" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>46089.2508680556</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2266,44 +2313,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="B11" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
-        <x:v>23</x:v>
+      <x:c r="B12" s="20" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3290,7 +3337,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -68,6 +68,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -122,10 +158,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -170,15 +208,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -194,15 +224,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -217,13 +247,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -460,26 +483,26 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -489,56 +512,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -569,79 +595,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -870,78 +908,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -962,7 +1012,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1002,104 +1052,141 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46049.5725925926</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>46049.5726273148</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J10" s="16" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>46049.5962615741</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
+        <x:v>37</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2078,14 +2165,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2126,78 +2214,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2218,7 +2318,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2258,104 +2358,141 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="E10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46078.2888888889</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>46078.2901041667</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J10" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>46089.2508680556</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
+        <x:v>37</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3334,14 +3471,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -68,42 +68,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -163,7 +127,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -207,14 +171,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -229,10 +185,18 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -247,6 +211,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -491,16 +462,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -512,24 +483,21 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -548,10 +516,13 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -564,7 +535,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -595,28 +566,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -631,10 +594,6 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -659,15 +618,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1012,7 +971,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1052,138 +1011,101 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>46049.5725925926</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46049.5726273148</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="K8" s="16" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46049.5962615741</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46049.5725925926</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46049.5726273148</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46049.5962615741</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="B13" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>37</x:v>
+      <x:c r="B14" s="20" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2285,7 +2207,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2318,7 +2240,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2358,138 +2280,101 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46078.2888888889</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46078.2901041667</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46089.2508680556</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46078.2888888889</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46078.2901041667</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46089.2508680556</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="B13" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>37</x:v>
+      <x:c r="B14" s="20" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -1065,50 +1065,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2092,10 +2092,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2334,50 +2334,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3361,10 +3361,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -1032,10 +1032,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46049.5725925926</x:v>
+        <x:v>46049.5726010069</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46049.5726273148</x:v>
+        <x:v>46049.5726341898</x:v>
       </x:c>
       <x:c r="J8" s="14" t="s">
         <x:v>21</x:v>
@@ -1044,7 +1044,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>46049.5962615741</x:v>
+        <x:v>46049.5962660532</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>22</x:v>
@@ -2301,10 +2301,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46078.2888888889</x:v>
+        <x:v>46078.2888967361</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46078.2901041667</x:v>
+        <x:v>46078.2901145602</x:v>
       </x:c>
       <x:c r="J8" s="14" t="s">
         <x:v>30</x:v>
@@ -2313,7 +2313,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>46089.2508680556</x:v>
+        <x:v>46089.2508762037</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>22</x:v>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -109,13 +109,31 @@
     <x:t>XIV | March 2026</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-07610</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1161-496</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-07584</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1160-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-07583</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1159-185</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-06446</x:t>
   </x:si>
   <x:si>
     <x:t>61-2-2026-1085-817</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -454,7 +472,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -534,8 +552,14 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -640,6 +664,26 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -2282,103 +2326,201 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="31">
+        <x:v>46106.5066742245</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
+        <x:v>46106.5082381134</x:v>
+      </x:c>
+      <x:c r="J8" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="33">
+        <x:v>46106.5099302546</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="29" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F9" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H9" s="31">
+        <x:v>46105.676846794</x:v>
+      </x:c>
+      <x:c r="I9" s="31">
+        <x:v>46106.5084437037</x:v>
+      </x:c>
+      <x:c r="J9" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L9" s="33">
+        <x:v>46106.5101144792</x:v>
+      </x:c>
+      <x:c r="M9" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H10" s="31">
+        <x:v>46105.6741278125</x:v>
+      </x:c>
+      <x:c r="I10" s="31">
+        <x:v>46106.5086548727</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="33">
+        <x:v>46106.5103567593</x:v>
+      </x:c>
+      <x:c r="M10" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D11" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="29" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G11" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="31">
         <x:v>46078.2888967361</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I11" s="31">
         <x:v>46078.2901145602</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L11" s="33">
         <x:v>46089.2508762037</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="s"/>
+      <x:c r="D14" s="18" t="s"/>
+      <x:c r="E14" s="19" t="s"/>
+      <x:c r="F14" s="19" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="20" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="22" t="s">
+        <x:v>25</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
-        <x:v>1</x:v>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3361,10 +3503,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -1015,7 +1015,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1055,7 +1055,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -2284,7 +2284,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2324,7 +2324,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
         <x:v>15</x:v>
@@ -2363,7 +2363,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2401,7 +2401,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2439,7 +2439,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -23,15 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
   <x:si>
     <x:t>CERTIFICATES SUMMARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XIV | January 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -104,9 +101,6 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XIV | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-07610</x:t>
@@ -472,7 +466,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="29">
+  <x:cellStyleXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -489,6 +483,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -559,7 +556,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -595,6 +592,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -981,20 +982,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1017,81 +1018,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="16">
+        <x:v>46049.5726010069</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46049.5726341898</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46049.5726010069</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46049.5726341898</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="s">
+      <x:c r="K8" s="17" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="16">
+        <x:v>46049.5962660532</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46049.5962660532</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1110,44 +1111,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2250,20 +2251,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2286,238 +2287,238 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="29" t="s">
+      <x:c r="B8" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="29" t="s">
+      <x:c r="D8" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
+      <x:c r="E8" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="29" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="29" t="s">
+      <x:c r="F8" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G8" s="30" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
+        <x:v>46106.5066742245</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>46106.5082381134</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G8" s="29" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H8" s="31">
-        <x:v>46106.5066742245</x:v>
-      </x:c>
-      <x:c r="I8" s="31">
-        <x:v>46106.5082381134</x:v>
-      </x:c>
-      <x:c r="J8" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
+      <x:c r="K8" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="33">
+      <x:c r="L8" s="34">
         <x:v>46106.5099302546</x:v>
       </x:c>
-      <x:c r="M8" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M8" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="29" t="s">
+      <x:c r="B9" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C9" s="29" t="s">
+      <x:c r="D9" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="30" t="s">
+      <x:c r="E9" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="29" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F9" s="29" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G9" s="29" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H9" s="31">
+      <x:c r="F9" s="30" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G9" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H9" s="32">
         <x:v>46105.676846794</x:v>
       </x:c>
-      <x:c r="I9" s="31">
+      <x:c r="I9" s="32">
         <x:v>46106.5084437037</x:v>
       </x:c>
-      <x:c r="J9" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
+      <x:c r="J9" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K9" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="33">
+      <x:c r="L9" s="34">
         <x:v>46106.5101144792</x:v>
       </x:c>
-      <x:c r="M9" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="29" t="s">
+      <x:c r="B10" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="29" t="s">
+      <x:c r="D10" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="s">
+      <x:c r="E10" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H10" s="31">
+      <x:c r="F10" s="30" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
         <x:v>46105.6741278125</x:v>
       </x:c>
-      <x:c r="I10" s="31">
+      <x:c r="I10" s="32">
         <x:v>46106.5086548727</x:v>
       </x:c>
-      <x:c r="J10" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="J10" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K10" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="33">
+      <x:c r="L10" s="34">
         <x:v>46106.5103567593</x:v>
       </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="29" t="s">
+      <x:c r="B11" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="29" t="s">
+      <x:c r="D11" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D11" s="30" t="s">
+      <x:c r="E11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="29" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F11" s="29" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G11" s="29" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H11" s="31">
+      <x:c r="F11" s="30" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
         <x:v>46078.2888967361</x:v>
       </x:c>
-      <x:c r="I11" s="31">
+      <x:c r="I11" s="32">
         <x:v>46078.2901145602</x:v>
       </x:c>
-      <x:c r="J11" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="J11" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K11" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="33">
+      <x:c r="L11" s="34">
         <x:v>46089.2508762037</x:v>
       </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="18" t="s"/>
-      <x:c r="D14" s="18" t="s"/>
-      <x:c r="E14" s="19" t="s"/>
-      <x:c r="F14" s="19" t="s"/>
+      <x:c r="B14" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C14" s="19" t="s"/>
+      <x:c r="D14" s="19" t="s"/>
+      <x:c r="E14" s="20" t="s"/>
+      <x:c r="F14" s="20" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="20" t="s">
+      <x:c r="B15" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="B17" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -8,6 +8,7 @@
   <x:sheets>
     <x:sheet name="January 2026" sheetId="7" r:id="rId7"/>
     <x:sheet name="March 2026" sheetId="8" r:id="rId8"/>
+    <x:sheet name="April 2026" sheetId="9" r:id="rId9"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -128,6 +129,24 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1085-817</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amateur Radio Operator Certificate (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDWARD LANCE LORILLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sarphil subdivision celica, s, Baungon, Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1220-376</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3522,4 +3541,1273 @@
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46118.3222074537</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="L8" s="16">
+        <x:v>46118.3241166898</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -147,6 +147,42 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1220-376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3713,105 +3749,250 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="30" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="30" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="D8" s="31" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="30" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="30" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="30" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="32">
         <x:v>46118.3222074537</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="32">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="31" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="33" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="34">
         <x:v>46118.3241166898</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F9" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G9" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H9" s="32">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K9" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L9" s="34">
+        <x:v>46118.7577859143</x:v>
+      </x:c>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K10" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="34">
+        <x:v>46118.743899213</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K11" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L11" s="34">
+        <x:v>46118.4241364815</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K12" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L12" s="34">
+        <x:v>46118.3476865394</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C15" s="19" t="s"/>
+      <x:c r="D15" s="19" t="s"/>
+      <x:c r="E15" s="20" t="s"/>
+      <x:c r="F15" s="20" t="s"/>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
-        <x:v>1</x:v>
+      <x:c r="C19" s="28" t="s"/>
+      <x:c r="D19" s="28" t="s"/>
+      <x:c r="E19" s="28" t="s"/>
+      <x:c r="F19" s="29" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4787,15 +4968,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -147,6 +147,24 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1220-376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08044</x:t>
@@ -3806,10 +3824,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>43</x:v>
@@ -3818,7 +3836,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -3844,10 +3862,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>46</x:v>
@@ -3856,7 +3874,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -3882,10 +3900,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>49</x:v>
@@ -3894,7 +3912,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -3920,10 +3938,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>52</x:v>
@@ -3932,69 +3950,143 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="18" t="s">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K13" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L13" s="34">
+        <x:v>46118.4241364815</x:v>
+      </x:c>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F14" s="30" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H14" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I14" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K14" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L14" s="34">
+        <x:v>46118.3476865394</x:v>
+      </x:c>
+      <x:c r="M14" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C15" s="19" t="s"/>
-      <x:c r="D15" s="19" t="s"/>
-      <x:c r="E15" s="20" t="s"/>
-      <x:c r="F15" s="20" t="s"/>
+      <x:c r="C17" s="19" t="s"/>
+      <x:c r="D17" s="19" t="s"/>
+      <x:c r="E17" s="20" t="s"/>
+      <x:c r="F17" s="20" t="s"/>
     </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="21" t="s">
+    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B18" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="s">
+      <x:c r="C18" s="22" t="s"/>
+      <x:c r="D18" s="22" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="24" t="s">
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="n">
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="24" t="s">
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="26" t="n">
-        <x:v>4</x:v>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="27" t="s">
+    <x:row r="21" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B21" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C19" s="28" t="s"/>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="28" t="s"/>
-      <x:c r="F19" s="29" t="n">
-        <x:v>5</x:v>
+      <x:c r="C21" s="28" t="s"/>
+      <x:c r="D21" s="28" t="s"/>
+      <x:c r="E21" s="28" t="s"/>
+      <x:c r="F21" s="29" t="n">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4973,11 +5065,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B15:F15"/>
-    <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B17:F17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -147,6 +147,15 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1220-376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08048</x:t>
@@ -3824,10 +3833,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>43</x:v>
@@ -3836,7 +3845,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -3862,10 +3871,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>46</x:v>
@@ -3874,7 +3883,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -3900,10 +3909,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>49</x:v>
@@ -3912,7 +3921,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -3938,10 +3947,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>52</x:v>
@@ -3950,7 +3959,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -3976,10 +3985,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>55</x:v>
@@ -3988,7 +3997,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -4014,10 +4023,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>58</x:v>
@@ -4026,68 +4035,105 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F15" s="30" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H15" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K15" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L15" s="34">
+        <x:v>46118.3476865394</x:v>
+      </x:c>
+      <x:c r="M15" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="18" t="s">
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C17" s="19" t="s"/>
-      <x:c r="D17" s="19" t="s"/>
-      <x:c r="E17" s="20" t="s"/>
-      <x:c r="F17" s="20" t="s"/>
+      <x:c r="C18" s="19" t="s"/>
+      <x:c r="D18" s="19" t="s"/>
+      <x:c r="E18" s="20" t="s"/>
+      <x:c r="F18" s="20" t="s"/>
     </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="21" t="s">
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="s">
+      <x:c r="C19" s="22" t="s"/>
+      <x:c r="D19" s="22" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="24" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C19" s="25" t="s"/>
-      <x:c r="D19" s="25" t="s"/>
-      <x:c r="E19" s="25" t="s"/>
-      <x:c r="F19" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C20" s="25" t="s"/>
       <x:c r="D20" s="25" t="s"/>
       <x:c r="E20" s="25" t="s"/>
       <x:c r="F20" s="26" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="27" t="s">
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="s"/>
+      <x:c r="D21" s="25" t="s"/>
+      <x:c r="E21" s="25" t="s"/>
+      <x:c r="F21" s="26" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="29" t="n">
-        <x:v>7</x:v>
+      <x:c r="C22" s="28" t="s"/>
+      <x:c r="D22" s="28" t="s"/>
+      <x:c r="E22" s="28" t="s"/>
+      <x:c r="F22" s="29" t="n">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5065,11 +5111,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B17:F17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -147,6 +147,57 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1220-376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08082</x:t>
@@ -3833,10 +3884,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>43</x:v>
@@ -3845,7 +3896,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -3871,10 +3922,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>46</x:v>
@@ -3883,7 +3934,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -3909,10 +3960,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>49</x:v>
@@ -3921,7 +3972,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -3947,10 +3998,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>52</x:v>
@@ -3959,7 +4010,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -3985,10 +4036,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>55</x:v>
@@ -3997,7 +4048,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -4023,19 +4074,19 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>58</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -4055,91 +4106,313 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="H15" s="32">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="H15" s="32">
-        <x:v>46118.3446055671</x:v>
-      </x:c>
-      <x:c r="I15" s="32">
-        <x:v>46118.476906412</x:v>
-      </x:c>
-      <x:c r="J15" s="31" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F16" s="30" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H16" s="32">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="K16" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L16" s="34">
+        <x:v>46119.0764109954</x:v>
+      </x:c>
+      <x:c r="M16" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F17" s="30" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H17" s="32">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I17" s="32">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="K17" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L17" s="34">
+        <x:v>46119.076169375</x:v>
+      </x:c>
+      <x:c r="M17" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="18" t="s">
+      <x:c r="B18" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D18" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F18" s="30" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H18" s="32">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="K18" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L18" s="34">
+        <x:v>46118.7577859143</x:v>
+      </x:c>
+      <x:c r="M18" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D19" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E19" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F19" s="30" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G19" s="30" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H19" s="32">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I19" s="32">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K19" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L19" s="34">
+        <x:v>46118.743899213</x:v>
+      </x:c>
+      <x:c r="M19" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D20" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F20" s="30" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H20" s="32">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K20" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L20" s="34">
+        <x:v>46118.4241364815</x:v>
+      </x:c>
+      <x:c r="M20" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D21" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E21" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F21" s="30" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G21" s="30" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H21" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I21" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="K21" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L21" s="34">
+        <x:v>46118.3476865394</x:v>
+      </x:c>
+      <x:c r="M21" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C18" s="19" t="s"/>
-      <x:c r="D18" s="19" t="s"/>
-      <x:c r="E18" s="20" t="s"/>
-      <x:c r="F18" s="20" t="s"/>
+      <x:c r="C24" s="19" t="s"/>
+      <x:c r="D24" s="19" t="s"/>
+      <x:c r="E24" s="20" t="s"/>
+      <x:c r="F24" s="20" t="s"/>
     </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="21" t="s">
+    <x:row r="25" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B25" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="s">
+      <x:c r="C25" s="22" t="s"/>
+      <x:c r="D25" s="22" t="s"/>
+      <x:c r="E25" s="22" t="s"/>
+      <x:c r="F25" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="24" t="s">
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C20" s="25" t="s"/>
-      <x:c r="D20" s="25" t="s"/>
-      <x:c r="E20" s="25" t="s"/>
-      <x:c r="F20" s="26" t="n">
+      <x:c r="C26" s="25" t="s"/>
+      <x:c r="D26" s="25" t="s"/>
+      <x:c r="E26" s="25" t="s"/>
+      <x:c r="F26" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="24" t="s">
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C21" s="25" t="s"/>
-      <x:c r="D21" s="25" t="s"/>
-      <x:c r="E21" s="25" t="s"/>
-      <x:c r="F21" s="26" t="n">
-        <x:v>7</x:v>
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="25" t="s"/>
+      <x:c r="F27" s="26" t="n">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="27" t="s">
+    <x:row r="28" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B28" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C22" s="28" t="s"/>
-      <x:c r="D22" s="28" t="s"/>
-      <x:c r="E22" s="28" t="s"/>
-      <x:c r="F22" s="29" t="n">
-        <x:v>8</x:v>
+      <x:c r="C28" s="28" t="s"/>
+      <x:c r="D28" s="28" t="s"/>
+      <x:c r="E28" s="28" t="s"/>
+      <x:c r="F28" s="29" t="n">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5111,11 +5384,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B18:F18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B24:F24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -149,6 +149,102 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08094</x:t>
   </x:si>
   <x:si>
@@ -158,100 +254,31 @@
     <x:t>zczxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
@@ -261,6 +288,15 @@
   </x:si>
   <x:si>
     <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3884,10 +3920,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>43</x:v>
@@ -3896,7 +3932,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -3922,10 +3958,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>46</x:v>
@@ -3934,7 +3970,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -3960,10 +3996,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>49</x:v>
@@ -3972,7 +4008,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -3998,10 +4034,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>52</x:v>
@@ -4010,7 +4046,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -4036,10 +4072,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>55</x:v>
@@ -4048,7 +4084,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -4074,19 +4110,19 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -4106,25 +4142,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G15" s="30" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
-        <x:v>60</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -4150,10 +4186,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
         <x:v>63</x:v>
@@ -4162,7 +4198,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -4188,10 +4224,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
         <x:v>66</x:v>
@@ -4200,7 +4236,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -4226,10 +4262,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
         <x:v>69</x:v>
@@ -4238,7 +4274,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -4264,10 +4300,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
         <x:v>72</x:v>
@@ -4276,7 +4312,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -4302,10 +4338,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
         <x:v>75</x:v>
@@ -4314,7 +4350,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -4340,10 +4376,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
         <x:v>78</x:v>
@@ -4352,71 +4388,219 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D22" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E22" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F22" s="30" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G22" s="30" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H22" s="32">
+        <x:v>46119.7285584838</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46119.7318005208</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K22" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L22" s="34">
+        <x:v>46119.7339888773</x:v>
+      </x:c>
+      <x:c r="M22" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D23" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E23" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F23" s="30" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H23" s="32">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I23" s="32">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K23" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L23" s="34">
+        <x:v>46119.7327704398</x:v>
+      </x:c>
+      <x:c r="M23" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="18" t="s">
+      <x:c r="B24" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D24" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E24" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F24" s="30" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G24" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H24" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I24" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K24" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L24" s="34">
+        <x:v>46118.3476865394</x:v>
+      </x:c>
+      <x:c r="M24" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C25" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D25" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E25" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F25" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G25" s="30" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H25" s="32">
+        <x:v>46119.7297941435</x:v>
+      </x:c>
+      <x:c r="I25" s="32">
+        <x:v>46119.731450544</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K25" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L25" s="34">
+        <x:v>46119.7324832755</x:v>
+      </x:c>
+      <x:c r="M25" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C24" s="19" t="s"/>
-      <x:c r="D24" s="19" t="s"/>
-      <x:c r="E24" s="20" t="s"/>
-      <x:c r="F24" s="20" t="s"/>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="21" t="s">
+      <x:c r="C28" s="19" t="s"/>
+      <x:c r="D28" s="19" t="s"/>
+      <x:c r="E28" s="20" t="s"/>
+      <x:c r="F28" s="20" t="s"/>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B29" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C25" s="22" t="s"/>
-      <x:c r="D25" s="22" t="s"/>
-      <x:c r="E25" s="22" t="s"/>
-      <x:c r="F25" s="23" t="s">
+      <x:c r="C29" s="22" t="s"/>
+      <x:c r="D29" s="22" t="s"/>
+      <x:c r="E29" s="22" t="s"/>
+      <x:c r="F29" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="24" t="s">
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C26" s="25" t="s"/>
-      <x:c r="D26" s="25" t="s"/>
-      <x:c r="E26" s="25" t="s"/>
-      <x:c r="F26" s="26" t="n">
+      <x:c r="C30" s="25" t="s"/>
+      <x:c r="D30" s="25" t="s"/>
+      <x:c r="E30" s="25" t="s"/>
+      <x:c r="F30" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="24" t="s">
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C27" s="25" t="s"/>
-      <x:c r="D27" s="25" t="s"/>
-      <x:c r="E27" s="25" t="s"/>
-      <x:c r="F27" s="26" t="n">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B28" s="27" t="s">
+      <x:c r="C31" s="25" t="s"/>
+      <x:c r="D31" s="25" t="s"/>
+      <x:c r="E31" s="25" t="s"/>
+      <x:c r="F31" s="26" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B32" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C28" s="28" t="s"/>
-      <x:c r="D28" s="28" t="s"/>
-      <x:c r="E28" s="28" t="s"/>
-      <x:c r="F28" s="29" t="n">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C32" s="28" t="s"/>
+      <x:c r="D32" s="28" t="s"/>
+      <x:c r="E32" s="28" t="s"/>
+      <x:c r="F32" s="29" t="n">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5384,11 +5568,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B24:F24"/>
-    <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
-    <x:mergeCell ref="B27:E27"/>
-    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B28:F28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -281,6 +281,21 @@
     <x:t>zcasdqwezxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -290,13 +305,10 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4490,10 +4502,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
         <x:v>87</x:v>
@@ -4502,7 +4514,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -4528,81 +4540,155 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>90</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="18" t="s">
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C26" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D26" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E26" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F26" s="30" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G26" s="30" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H26" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I26" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K26" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L26" s="34">
+        <x:v>46118.3476865394</x:v>
+      </x:c>
+      <x:c r="M26" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C27" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D27" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E27" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F27" s="30" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G27" s="30" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H27" s="32">
+        <x:v>46119.8023724884</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
+        <x:v>46119.8046602662</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K27" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L27" s="34">
+        <x:v>46119.8055532407</x:v>
+      </x:c>
+      <x:c r="M27" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C28" s="19" t="s"/>
-      <x:c r="D28" s="19" t="s"/>
-      <x:c r="E28" s="20" t="s"/>
-      <x:c r="F28" s="20" t="s"/>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="21" t="s">
+      <x:c r="C30" s="19" t="s"/>
+      <x:c r="D30" s="19" t="s"/>
+      <x:c r="E30" s="20" t="s"/>
+      <x:c r="F30" s="20" t="s"/>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B31" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C29" s="22" t="s"/>
-      <x:c r="D29" s="22" t="s"/>
-      <x:c r="E29" s="22" t="s"/>
-      <x:c r="F29" s="23" t="s">
+      <x:c r="C31" s="22" t="s"/>
+      <x:c r="D31" s="22" t="s"/>
+      <x:c r="E31" s="22" t="s"/>
+      <x:c r="F31" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="24" t="s">
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C30" s="25" t="s"/>
-      <x:c r="D30" s="25" t="s"/>
-      <x:c r="E30" s="25" t="s"/>
-      <x:c r="F30" s="26" t="n">
+      <x:c r="C32" s="25" t="s"/>
+      <x:c r="D32" s="25" t="s"/>
+      <x:c r="E32" s="25" t="s"/>
+      <x:c r="F32" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="24" t="s">
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C31" s="25" t="s"/>
-      <x:c r="D31" s="25" t="s"/>
-      <x:c r="E31" s="25" t="s"/>
-      <x:c r="F31" s="26" t="n">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B32" s="27" t="s">
+      <x:c r="C33" s="25" t="s"/>
+      <x:c r="D33" s="25" t="s"/>
+      <x:c r="E33" s="25" t="s"/>
+      <x:c r="F33" s="26" t="n">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B34" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C32" s="28" t="s"/>
-      <x:c r="D32" s="28" t="s"/>
-      <x:c r="E32" s="28" t="s"/>
-      <x:c r="F32" s="29" t="n">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C34" s="28" t="s"/>
+      <x:c r="D34" s="28" t="s"/>
+      <x:c r="E34" s="28" t="s"/>
+      <x:c r="F34" s="29" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5568,11 +5654,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B28:F28"/>
-    <x:mergeCell ref="B29:E29"/>
-    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B30:F30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -296,6 +296,30 @@
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -305,10 +329,13 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4578,19 +4605,19 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>92</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -4610,16 +4637,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G27" s="30" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G27" s="30" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="H27" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
         <x:v>81</x:v>
@@ -4628,71 +4655,219 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C28" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D28" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E28" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F28" s="30" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G28" s="30" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H28" s="32">
+        <x:v>46120.2349196412</x:v>
+      </x:c>
+      <x:c r="I28" s="32">
+        <x:v>46120.5229746296</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K28" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="34">
+        <x:v>46120.5255047106</x:v>
+      </x:c>
+      <x:c r="M28" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C29" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D29" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E29" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F29" s="30" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G29" s="30" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H29" s="32">
+        <x:v>46120.2362105324</x:v>
+      </x:c>
+      <x:c r="I29" s="32">
+        <x:v>46120.5226826273</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K29" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L29" s="34">
+        <x:v>46120.5252627315</x:v>
+      </x:c>
+      <x:c r="M29" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="18" t="s">
+      <x:c r="B30" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C30" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D30" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E30" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F30" s="30" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G30" s="30" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H30" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I30" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K30" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L30" s="34">
+        <x:v>46118.3476865394</x:v>
+      </x:c>
+      <x:c r="M30" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B31" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C31" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D31" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E31" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F31" s="30" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G31" s="30" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H31" s="32">
+        <x:v>46120.2374046412</x:v>
+      </x:c>
+      <x:c r="I31" s="32">
+        <x:v>46120.5224942245</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="K31" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L31" s="34">
+        <x:v>46120.5250032292</x:v>
+      </x:c>
+      <x:c r="M31" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B34" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C30" s="19" t="s"/>
-      <x:c r="D30" s="19" t="s"/>
-      <x:c r="E30" s="20" t="s"/>
-      <x:c r="F30" s="20" t="s"/>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B31" s="21" t="s">
+      <x:c r="C34" s="19" t="s"/>
+      <x:c r="D34" s="19" t="s"/>
+      <x:c r="E34" s="20" t="s"/>
+      <x:c r="F34" s="20" t="s"/>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B35" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C31" s="22" t="s"/>
-      <x:c r="D31" s="22" t="s"/>
-      <x:c r="E31" s="22" t="s"/>
-      <x:c r="F31" s="23" t="s">
+      <x:c r="C35" s="22" t="s"/>
+      <x:c r="D35" s="22" t="s"/>
+      <x:c r="E35" s="22" t="s"/>
+      <x:c r="F35" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="24" t="s">
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C32" s="25" t="s"/>
-      <x:c r="D32" s="25" t="s"/>
-      <x:c r="E32" s="25" t="s"/>
-      <x:c r="F32" s="26" t="n">
+      <x:c r="C36" s="25" t="s"/>
+      <x:c r="D36" s="25" t="s"/>
+      <x:c r="E36" s="25" t="s"/>
+      <x:c r="F36" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="24" t="s">
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C33" s="25" t="s"/>
-      <x:c r="D33" s="25" t="s"/>
-      <x:c r="E33" s="25" t="s"/>
-      <x:c r="F33" s="26" t="n">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="27" t="s">
+      <x:c r="C37" s="25" t="s"/>
+      <x:c r="D37" s="25" t="s"/>
+      <x:c r="E37" s="25" t="s"/>
+      <x:c r="F37" s="26" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B38" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C34" s="28" t="s"/>
-      <x:c r="D34" s="28" t="s"/>
-      <x:c r="E34" s="28" t="s"/>
-      <x:c r="F34" s="29" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C38" s="28" t="s"/>
+      <x:c r="D38" s="28" t="s"/>
+      <x:c r="E38" s="28" t="s"/>
+      <x:c r="F38" s="29" t="n">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5654,11 +5829,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B30:F30"/>
-    <x:mergeCell ref="B31:E31"/>
-    <x:mergeCell ref="B32:E32"/>
-    <x:mergeCell ref="B33:E33"/>
-    <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B34:F34"/>
+    <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B38:E38"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -320,6 +320,21 @@
     <x:t>61-4-2026-1256-775</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -329,13 +344,13 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4757,10 +4772,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
         <x:v>100</x:v>
@@ -4769,7 +4784,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -4795,81 +4810,155 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>103</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B34" s="18" t="s">
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B32" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C32" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D32" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E32" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F32" s="30" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G32" s="30" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H32" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I32" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J32" s="31" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="K32" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L32" s="34">
+        <x:v>46118.3476865394</x:v>
+      </x:c>
+      <x:c r="M32" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C33" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D33" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E33" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F33" s="30" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G33" s="30" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H33" s="32">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I33" s="32">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J33" s="31" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K33" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L33" s="34">
+        <x:v>46121.1027298958</x:v>
+      </x:c>
+      <x:c r="M33" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B36" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C34" s="19" t="s"/>
-      <x:c r="D34" s="19" t="s"/>
-      <x:c r="E34" s="20" t="s"/>
-      <x:c r="F34" s="20" t="s"/>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B35" s="21" t="s">
+      <x:c r="C36" s="19" t="s"/>
+      <x:c r="D36" s="19" t="s"/>
+      <x:c r="E36" s="20" t="s"/>
+      <x:c r="F36" s="20" t="s"/>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B37" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C35" s="22" t="s"/>
-      <x:c r="D35" s="22" t="s"/>
-      <x:c r="E35" s="22" t="s"/>
-      <x:c r="F35" s="23" t="s">
+      <x:c r="C37" s="22" t="s"/>
+      <x:c r="D37" s="22" t="s"/>
+      <x:c r="E37" s="22" t="s"/>
+      <x:c r="F37" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="24" t="s">
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C36" s="25" t="s"/>
-      <x:c r="D36" s="25" t="s"/>
-      <x:c r="E36" s="25" t="s"/>
-      <x:c r="F36" s="26" t="n">
+      <x:c r="C38" s="25" t="s"/>
+      <x:c r="D38" s="25" t="s"/>
+      <x:c r="E38" s="25" t="s"/>
+      <x:c r="F38" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="24" t="s">
+    <x:row r="39" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B39" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C37" s="25" t="s"/>
-      <x:c r="D37" s="25" t="s"/>
-      <x:c r="E37" s="25" t="s"/>
-      <x:c r="F37" s="26" t="n">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B38" s="27" t="s">
+      <x:c r="C39" s="25" t="s"/>
+      <x:c r="D39" s="25" t="s"/>
+      <x:c r="E39" s="25" t="s"/>
+      <x:c r="F39" s="26" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C38" s="28" t="s"/>
-      <x:c r="D38" s="28" t="s"/>
-      <x:c r="E38" s="28" t="s"/>
-      <x:c r="F38" s="29" t="n">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B40" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C40" s="28" t="s"/>
+      <x:c r="D40" s="28" t="s"/>
+      <x:c r="E40" s="28" t="s"/>
+      <x:c r="F40" s="29" t="n">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5829,11 +5918,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B34:F34"/>
-    <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B36:F36"/>
     <x:mergeCell ref="B37:E37"/>
     <x:mergeCell ref="B38:E38"/>
+    <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B40:E40"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -245,6 +245,15 @@
     <x:t>zcx</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08094</x:t>
   </x:si>
   <x:si>
@@ -254,103 +263,100 @@
     <x:t>zczxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08095</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1246-201</x:t>
   </x:si>
   <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4392,10 +4398,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
         <x:v>75</x:v>
@@ -4404,7 +4410,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -4430,10 +4436,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
         <x:v>78</x:v>
@@ -4442,7 +4448,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -4588,7 +4594,7 @@
         <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>78</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
@@ -4614,10 +4620,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H26" s="32">
         <x:v>46119.8023724884</x:v>
@@ -4652,10 +4658,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G27" s="30" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H27" s="32">
         <x:v>46119.8029380671</x:v>
@@ -4690,10 +4696,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H28" s="32">
         <x:v>46120.2349196412</x:v>
@@ -4728,10 +4734,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G29" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H29" s="32">
         <x:v>46120.2362105324</x:v>
@@ -4766,10 +4772,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G30" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H30" s="32">
         <x:v>46120.2374046412</x:v>
@@ -4778,7 +4784,7 @@
         <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
@@ -4804,10 +4810,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H31" s="32">
         <x:v>46120.7129542245</x:v>
@@ -4842,25 +4848,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -4880,86 +4886,123 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>108</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B34" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C34" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D34" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E34" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F34" s="30" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G34" s="30" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H34" s="32">
+        <x:v>46121.2273626852</x:v>
+      </x:c>
+      <x:c r="I34" s="32">
+        <x:v>46121.228379213</x:v>
+      </x:c>
+      <x:c r="J34" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K34" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L34" s="34">
+        <x:v>46121.2291153125</x:v>
+      </x:c>
+      <x:c r="M34" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B36" s="18" t="s">
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B37" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C36" s="19" t="s"/>
-      <x:c r="D36" s="19" t="s"/>
-      <x:c r="E36" s="20" t="s"/>
-      <x:c r="F36" s="20" t="s"/>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B37" s="21" t="s">
+      <x:c r="C37" s="19" t="s"/>
+      <x:c r="D37" s="19" t="s"/>
+      <x:c r="E37" s="20" t="s"/>
+      <x:c r="F37" s="20" t="s"/>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B38" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C37" s="22" t="s"/>
-      <x:c r="D37" s="22" t="s"/>
-      <x:c r="E37" s="22" t="s"/>
-      <x:c r="F37" s="23" t="s">
+      <x:c r="C38" s="22" t="s"/>
+      <x:c r="D38" s="22" t="s"/>
+      <x:c r="E38" s="22" t="s"/>
+      <x:c r="F38" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="24" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C38" s="25" t="s"/>
-      <x:c r="D38" s="25" t="s"/>
-      <x:c r="E38" s="25" t="s"/>
-      <x:c r="F38" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="18" customHeight="1">
       <x:c r="B39" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C39" s="25" t="s"/>
       <x:c r="D39" s="25" t="s"/>
       <x:c r="E39" s="25" t="s"/>
       <x:c r="F39" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B40" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C40" s="25" t="s"/>
+      <x:c r="D40" s="25" t="s"/>
+      <x:c r="E40" s="25" t="s"/>
+      <x:c r="F40" s="26" t="n">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B41" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B40" s="27" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C40" s="28" t="s"/>
-      <x:c r="D40" s="28" t="s"/>
-      <x:c r="E40" s="28" t="s"/>
-      <x:c r="F40" s="29" t="n">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C41" s="28" t="s"/>
+      <x:c r="D41" s="28" t="s"/>
+      <x:c r="E41" s="28" t="s"/>
+      <x:c r="F41" s="29" t="n">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5918,11 +5961,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B36:F36"/>
-    <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B37:F37"/>
     <x:mergeCell ref="B38:E38"/>
     <x:mergeCell ref="B39:E39"/>
     <x:mergeCell ref="B40:E40"/>
+    <x:mergeCell ref="B41:E41"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -245,6 +245,15 @@
     <x:t>zcx</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -254,13 +263,103 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08096</x:t>
@@ -269,94 +368,13 @@
     <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
-    <x:t>zxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4398,10 +4416,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
         <x:v>75</x:v>
@@ -4410,7 +4428,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -4436,10 +4454,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
         <x:v>78</x:v>
@@ -4448,7 +4466,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -4474,10 +4492,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
         <x:v>81</x:v>
@@ -4486,7 +4504,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -4594,7 +4612,7 @@
         <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>90</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
@@ -4620,10 +4638,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G26" s="30" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="G26" s="30" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="H26" s="32">
         <x:v>46119.8023724884</x:v>
@@ -4632,7 +4650,7 @@
         <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
@@ -4670,7 +4688,7 @@
         <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
@@ -4892,19 +4910,19 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>90</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -4930,81 +4948,155 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="18" t="s">
+    <x:row r="35" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B35" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C35" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D35" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E35" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F35" s="30" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G35" s="30" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H35" s="32">
+        <x:v>46119.7285584838</x:v>
+      </x:c>
+      <x:c r="I35" s="32">
+        <x:v>46119.7318005208</x:v>
+      </x:c>
+      <x:c r="J35" s="31" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K35" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L35" s="34">
+        <x:v>46119.7339888773</x:v>
+      </x:c>
+      <x:c r="M35" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B36" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C36" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D36" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E36" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F36" s="30" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G36" s="30" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H36" s="32">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I36" s="32">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J36" s="31" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="K36" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L36" s="34">
+        <x:v>46121.4980146875</x:v>
+      </x:c>
+      <x:c r="M36" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B39" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C37" s="19" t="s"/>
-      <x:c r="D37" s="19" t="s"/>
-      <x:c r="E37" s="20" t="s"/>
-      <x:c r="F37" s="20" t="s"/>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B38" s="21" t="s">
+      <x:c r="C39" s="19" t="s"/>
+      <x:c r="D39" s="19" t="s"/>
+      <x:c r="E39" s="20" t="s"/>
+      <x:c r="F39" s="20" t="s"/>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B40" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C38" s="22" t="s"/>
-      <x:c r="D38" s="22" t="s"/>
-      <x:c r="E38" s="22" t="s"/>
-      <x:c r="F38" s="23" t="s">
+      <x:c r="C40" s="22" t="s"/>
+      <x:c r="D40" s="22" t="s"/>
+      <x:c r="E40" s="22" t="s"/>
+      <x:c r="F40" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B39" s="24" t="s">
+    <x:row r="41" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B41" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C39" s="25" t="s"/>
-      <x:c r="D39" s="25" t="s"/>
-      <x:c r="E39" s="25" t="s"/>
-      <x:c r="F39" s="26" t="n">
+      <x:c r="C41" s="25" t="s"/>
+      <x:c r="D41" s="25" t="s"/>
+      <x:c r="E41" s="25" t="s"/>
+      <x:c r="F41" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B40" s="24" t="s">
+    <x:row r="42" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B42" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C40" s="25" t="s"/>
-      <x:c r="D40" s="25" t="s"/>
-      <x:c r="E40" s="25" t="s"/>
-      <x:c r="F40" s="26" t="n">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B41" s="27" t="s">
+      <x:c r="C42" s="25" t="s"/>
+      <x:c r="D42" s="25" t="s"/>
+      <x:c r="E42" s="25" t="s"/>
+      <x:c r="F42" s="26" t="n">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B43" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C41" s="28" t="s"/>
-      <x:c r="D41" s="28" t="s"/>
-      <x:c r="E41" s="28" t="s"/>
-      <x:c r="F41" s="29" t="n">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C43" s="28" t="s"/>
+      <x:c r="D43" s="28" t="s"/>
+      <x:c r="E43" s="28" t="s"/>
+      <x:c r="F43" s="29" t="n">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5961,11 +6053,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B37:F37"/>
-    <x:mergeCell ref="B38:E38"/>
-    <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B39:F39"/>
     <x:mergeCell ref="B40:E40"/>
     <x:mergeCell ref="B41:E41"/>
+    <x:mergeCell ref="B42:E42"/>
+    <x:mergeCell ref="B43:E43"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -149,6 +149,123 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08033</x:t>
   </x:si>
   <x:si>
@@ -158,102 +275,12 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08087</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1238-244</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -263,24 +290,6 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08098</x:t>
   </x:si>
   <x:si>
@@ -290,19 +299,112 @@
     <x:t>zxcasdqwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasd</x:t>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
@@ -311,70 +413,16 @@
     <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08137</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3998,10 +4046,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>43</x:v>
@@ -4010,7 +4058,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -4036,10 +4084,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>46</x:v>
@@ -4048,7 +4096,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -4074,10 +4122,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>49</x:v>
@@ -4086,7 +4134,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -4112,10 +4160,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>52</x:v>
@@ -4124,7 +4172,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -4150,10 +4198,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>55</x:v>
@@ -4162,7 +4210,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -4188,10 +4236,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>58</x:v>
@@ -4200,7 +4248,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -4226,19 +4274,19 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -4258,10 +4306,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G16" s="30" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H16" s="32">
         <x:v>46119.5267212153</x:v>
@@ -4270,7 +4318,7 @@
         <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
@@ -4296,25 +4344,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G17" s="30" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -4334,25 +4382,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G18" s="30" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -4372,25 +4420,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G19" s="30" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -4410,25 +4458,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G20" s="30" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -4448,25 +4496,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G21" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -4486,25 +4534,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -4524,25 +4572,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G23" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>84</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -4568,10 +4616,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
         <x:v>87</x:v>
@@ -4580,7 +4628,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -4606,19 +4654,19 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>81</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -4638,10 +4686,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H26" s="32">
         <x:v>46119.8023724884</x:v>
@@ -4650,7 +4698,7 @@
         <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>92</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
@@ -4682,19 +4730,19 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -4714,25 +4762,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>87</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -4752,25 +4800,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G29" s="30" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>87</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -4790,25 +4838,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G30" s="30" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -4828,25 +4876,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -4866,25 +4914,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -4904,25 +4952,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -4942,10 +4990,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>110</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H34" s="32">
         <x:v>46121.2464636111</x:v>
@@ -4954,7 +5002,7 @@
         <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
@@ -4980,25 +5028,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>92</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -5018,91 +5066,313 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G36" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>116</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B37" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C37" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D37" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E37" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F37" s="30" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G37" s="30" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H37" s="32">
+        <x:v>46120.2374046412</x:v>
+      </x:c>
+      <x:c r="I37" s="32">
+        <x:v>46120.5224942245</x:v>
+      </x:c>
+      <x:c r="J37" s="31" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="K37" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L37" s="34">
+        <x:v>46120.5250032292</x:v>
+      </x:c>
+      <x:c r="M37" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B38" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C38" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D38" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E38" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F38" s="30" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G38" s="30" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H38" s="32">
+        <x:v>46120.2362105324</x:v>
+      </x:c>
+      <x:c r="I38" s="32">
+        <x:v>46120.5226826273</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K38" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L38" s="34">
+        <x:v>46120.5252627315</x:v>
+      </x:c>
+      <x:c r="M38" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B39" s="18" t="s">
+      <x:c r="B39" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C39" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D39" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E39" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F39" s="30" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G39" s="30" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H39" s="32">
+        <x:v>46120.2349196412</x:v>
+      </x:c>
+      <x:c r="I39" s="32">
+        <x:v>46120.5229746296</x:v>
+      </x:c>
+      <x:c r="J39" s="31" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K39" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L39" s="34">
+        <x:v>46120.5255047106</x:v>
+      </x:c>
+      <x:c r="M39" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B40" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C40" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D40" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E40" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F40" s="30" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G40" s="30" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="H40" s="32">
+        <x:v>46119.8029380671</x:v>
+      </x:c>
+      <x:c r="I40" s="32">
+        <x:v>46120.5237086343</x:v>
+      </x:c>
+      <x:c r="J40" s="31" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K40" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L40" s="34">
+        <x:v>46120.5257164468</x:v>
+      </x:c>
+      <x:c r="M40" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B41" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C41" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D41" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E41" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F41" s="30" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G41" s="30" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H41" s="32">
+        <x:v>46121.2273626852</x:v>
+      </x:c>
+      <x:c r="I41" s="32">
+        <x:v>46121.228379213</x:v>
+      </x:c>
+      <x:c r="J41" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K41" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L41" s="34">
+        <x:v>46121.2291153125</x:v>
+      </x:c>
+      <x:c r="M41" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B42" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C42" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D42" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E42" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F42" s="30" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G42" s="30" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H42" s="32">
+        <x:v>46122.2429836343</x:v>
+      </x:c>
+      <x:c r="I42" s="32">
+        <x:v>46122.244317963</x:v>
+      </x:c>
+      <x:c r="J42" s="31" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="K42" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L42" s="34">
+        <x:v>46122.2448800694</x:v>
+      </x:c>
+      <x:c r="M42" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C39" s="19" t="s"/>
-      <x:c r="D39" s="19" t="s"/>
-      <x:c r="E39" s="20" t="s"/>
-      <x:c r="F39" s="20" t="s"/>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B40" s="21" t="s">
+      <x:c r="C45" s="19" t="s"/>
+      <x:c r="D45" s="19" t="s"/>
+      <x:c r="E45" s="20" t="s"/>
+      <x:c r="F45" s="20" t="s"/>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B46" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C40" s="22" t="s"/>
-      <x:c r="D40" s="22" t="s"/>
-      <x:c r="E40" s="22" t="s"/>
-      <x:c r="F40" s="23" t="s">
+      <x:c r="C46" s="22" t="s"/>
+      <x:c r="D46" s="22" t="s"/>
+      <x:c r="E46" s="22" t="s"/>
+      <x:c r="F46" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B41" s="24" t="s">
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C41" s="25" t="s"/>
-      <x:c r="D41" s="25" t="s"/>
-      <x:c r="E41" s="25" t="s"/>
-      <x:c r="F41" s="26" t="n">
+      <x:c r="C47" s="25" t="s"/>
+      <x:c r="D47" s="25" t="s"/>
+      <x:c r="E47" s="25" t="s"/>
+      <x:c r="F47" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B42" s="24" t="s">
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C42" s="25" t="s"/>
-      <x:c r="D42" s="25" t="s"/>
-      <x:c r="E42" s="25" t="s"/>
-      <x:c r="F42" s="26" t="n">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B43" s="27" t="s">
+      <x:c r="C48" s="25" t="s"/>
+      <x:c r="D48" s="25" t="s"/>
+      <x:c r="E48" s="25" t="s"/>
+      <x:c r="F48" s="26" t="n">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B49" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C43" s="28" t="s"/>
-      <x:c r="D43" s="28" t="s"/>
-      <x:c r="E43" s="28" t="s"/>
-      <x:c r="F43" s="29" t="n">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C49" s="28" t="s"/>
+      <x:c r="D49" s="28" t="s"/>
+      <x:c r="E49" s="28" t="s"/>
+      <x:c r="F49" s="29" t="n">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
     <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6053,11 +6323,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B39:F39"/>
-    <x:mergeCell ref="B40:E40"/>
-    <x:mergeCell ref="B41:E41"/>
-    <x:mergeCell ref="B42:E42"/>
-    <x:mergeCell ref="B43:E43"/>
+    <x:mergeCell ref="B45:F45"/>
+    <x:mergeCell ref="B46:E46"/>
+    <x:mergeCell ref="B47:E47"/>
+    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B49:E49"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -149,24 +149,54 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08096</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
-    <x:t>zxcasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08095</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1246-201</x:t>
   </x:si>
   <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08094</x:t>
   </x:si>
   <x:si>
@@ -185,6 +215,12 @@
     <x:t>zcx</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08092</x:t>
   </x:si>
   <x:si>
@@ -194,6 +230,75 @@
     <x:t>zsd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08091</x:t>
   </x:si>
   <x:si>
@@ -203,84 +308,6 @@
     <x:t>zdd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -290,19 +317,79 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08153</x:t>
@@ -314,115 +401,82 @@
     <x:t>zxcasdadasdxasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08152</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1273-639</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4046,10 +4100,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>43</x:v>
@@ -4058,7 +4112,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -4084,10 +4138,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>46</x:v>
@@ -4096,7 +4150,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -4122,10 +4176,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>49</x:v>
@@ -4134,7 +4188,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -4160,10 +4214,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>52</x:v>
@@ -4172,7 +4226,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -4198,19 +4252,19 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K13" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -4230,25 +4284,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G14" s="30" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -4268,25 +4322,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H15" s="32">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G15" s="30" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H15" s="32">
-        <x:v>46119.729231331</x:v>
-      </x:c>
-      <x:c r="I15" s="32">
-        <x:v>46119.7316308565</x:v>
-      </x:c>
-      <x:c r="J15" s="31" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -4306,25 +4360,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H16" s="32">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="G16" s="30" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H16" s="32">
-        <x:v>46119.5267212153</x:v>
-      </x:c>
-      <x:c r="I16" s="32">
-        <x:v>46119.5274664236</x:v>
-      </x:c>
-      <x:c r="J16" s="31" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -4344,25 +4398,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G17" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>67</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -4382,25 +4436,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G18" s="30" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -4420,25 +4474,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G19" s="30" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -4458,25 +4512,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G20" s="30" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>76</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -4496,25 +4550,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G21" s="30" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -4534,25 +4588,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -4572,25 +4626,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G23" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -4610,25 +4664,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G24" s="30" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -4648,25 +4702,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G25" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -4686,25 +4740,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>43</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -4724,25 +4778,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G27" s="30" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H27" s="32">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="G27" s="30" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="H27" s="32">
-        <x:v>46122.1996025926</x:v>
-      </x:c>
-      <x:c r="I27" s="32">
-        <x:v>46122.2050823032</x:v>
-      </x:c>
-      <x:c r="J27" s="31" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -4762,25 +4816,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G28" s="30" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H28" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I28" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="G28" s="30" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H28" s="32">
-        <x:v>46122.1299166204</x:v>
-      </x:c>
-      <x:c r="I28" s="32">
-        <x:v>46122.2059087963</x:v>
-      </x:c>
-      <x:c r="J28" s="31" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -4800,25 +4854,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G29" s="30" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G29" s="30" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="H29" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>100</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -4838,25 +4892,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G30" s="30" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H30" s="32">
+        <x:v>46120.2374046412</x:v>
+      </x:c>
+      <x:c r="I30" s="32">
+        <x:v>46120.5224942245</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="G30" s="30" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H30" s="32">
-        <x:v>46121.5178724884</x:v>
-      </x:c>
-      <x:c r="I30" s="32">
-        <x:v>46122.2064690394</x:v>
-      </x:c>
-      <x:c r="J30" s="31" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -4876,25 +4930,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G31" s="30" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H31" s="32">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I31" s="32">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="G31" s="30" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H31" s="32">
-        <x:v>46121.5149441551</x:v>
-      </x:c>
-      <x:c r="I31" s="32">
-        <x:v>46122.2067431944</x:v>
-      </x:c>
-      <x:c r="J31" s="31" t="s">
-        <x:v>106</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -4914,25 +4968,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>109</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -4952,25 +5006,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -4990,25 +5044,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>114</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -5028,25 +5082,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>117</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -5066,25 +5120,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G36" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -5104,25 +5158,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G37" s="30" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>122</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -5142,25 +5196,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
-        <x:v>123</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G38" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H38" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I38" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
-        <x:v>90</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -5180,25 +5234,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F39" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G39" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
-        <x:v>90</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -5218,25 +5272,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F40" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G40" s="30" t="s">
-        <x:v>128</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>43</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -5256,25 +5310,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F41" s="30" t="s">
-        <x:v>129</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G41" s="30" t="s">
-        <x:v>130</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -5294,93 +5348,389 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="30" t="s">
-        <x:v>131</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G42" s="30" t="s">
-        <x:v>132</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
-        <x:v>122</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B43" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C43" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D43" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E43" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F43" s="30" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G43" s="30" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H43" s="32">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I43" s="32">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J43" s="31" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="K43" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L43" s="34">
+        <x:v>46122.2310990278</x:v>
+      </x:c>
+      <x:c r="M43" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B44" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C44" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D44" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E44" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F44" s="30" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G44" s="30" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H44" s="32">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I44" s="32">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J44" s="31" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="K44" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L44" s="34">
+        <x:v>46121.4980146875</x:v>
+      </x:c>
+      <x:c r="M44" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C45" s="19" t="s"/>
-      <x:c r="D45" s="19" t="s"/>
-      <x:c r="E45" s="20" t="s"/>
-      <x:c r="F45" s="20" t="s"/>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B46" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C46" s="22" t="s"/>
-      <x:c r="D46" s="22" t="s"/>
-      <x:c r="E46" s="22" t="s"/>
-      <x:c r="F46" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="24" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C47" s="25" t="s"/>
-      <x:c r="D47" s="25" t="s"/>
-      <x:c r="E47" s="25" t="s"/>
-      <x:c r="F47" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="24" t="s">
+      <x:c r="B45" s="30" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C48" s="25" t="s"/>
-      <x:c r="D48" s="25" t="s"/>
-      <x:c r="E48" s="25" t="s"/>
-      <x:c r="F48" s="26" t="n">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B49" s="27" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C49" s="28" t="s"/>
-      <x:c r="D49" s="28" t="s"/>
-      <x:c r="E49" s="28" t="s"/>
-      <x:c r="F49" s="29" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C45" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D45" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E45" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F45" s="30" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G45" s="30" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H45" s="32">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I45" s="32">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J45" s="31" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="K45" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L45" s="34">
+        <x:v>46121.498248206</x:v>
+      </x:c>
+      <x:c r="M45" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B46" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C46" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D46" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E46" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F46" s="30" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G46" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H46" s="32">
+        <x:v>46121.2273626852</x:v>
+      </x:c>
+      <x:c r="I46" s="32">
+        <x:v>46121.228379213</x:v>
+      </x:c>
+      <x:c r="J46" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K46" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L46" s="34">
+        <x:v>46121.2291153125</x:v>
+      </x:c>
+      <x:c r="M46" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B47" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C47" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D47" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E47" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F47" s="30" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G47" s="30" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H47" s="32">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I47" s="32">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J47" s="31" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="K47" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L47" s="34">
+        <x:v>46121.1027298958</x:v>
+      </x:c>
+      <x:c r="M47" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B48" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C48" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D48" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E48" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F48" s="30" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G48" s="30" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H48" s="32">
+        <x:v>46120.7129542245</x:v>
+      </x:c>
+      <x:c r="I48" s="32">
+        <x:v>46121.100944213</x:v>
+      </x:c>
+      <x:c r="J48" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K48" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L48" s="34">
+        <x:v>46121.1029720949</x:v>
+      </x:c>
+      <x:c r="M48" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B49" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C49" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D49" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E49" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F49" s="30" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G49" s="30" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H49" s="32">
+        <x:v>46122.1299166204</x:v>
+      </x:c>
+      <x:c r="I49" s="32">
+        <x:v>46122.2059087963</x:v>
+      </x:c>
+      <x:c r="J49" s="31" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K49" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L49" s="34">
+        <x:v>46122.2086237847</x:v>
+      </x:c>
+      <x:c r="M49" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B50" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C50" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D50" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E50" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F50" s="30" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G50" s="30" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H50" s="32">
+        <x:v>46122.5623107755</x:v>
+      </x:c>
+      <x:c r="I50" s="32">
+        <x:v>46122.5630093981</x:v>
+      </x:c>
+      <x:c r="J50" s="31" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K50" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L50" s="34">
+        <x:v>46122.5634620023</x:v>
+      </x:c>
+      <x:c r="M50" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B53" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C53" s="19" t="s"/>
+      <x:c r="D53" s="19" t="s"/>
+      <x:c r="E53" s="20" t="s"/>
+      <x:c r="F53" s="20" t="s"/>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B54" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C54" s="22" t="s"/>
+      <x:c r="D54" s="22" t="s"/>
+      <x:c r="E54" s="22" t="s"/>
+      <x:c r="F54" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="24" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C55" s="25" t="s"/>
+      <x:c r="D55" s="25" t="s"/>
+      <x:c r="E55" s="25" t="s"/>
+      <x:c r="F55" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C56" s="25" t="s"/>
+      <x:c r="D56" s="25" t="s"/>
+      <x:c r="E56" s="25" t="s"/>
+      <x:c r="F56" s="26" t="n">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B57" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C57" s="28" t="s"/>
+      <x:c r="D57" s="28" t="s"/>
+      <x:c r="E57" s="28" t="s"/>
+      <x:c r="F57" s="29" t="n">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
     <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6323,11 +6673,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B45:F45"/>
-    <x:mergeCell ref="B46:E46"/>
-    <x:mergeCell ref="B47:E47"/>
-    <x:mergeCell ref="B48:E48"/>
-    <x:mergeCell ref="B49:E49"/>
+    <x:mergeCell ref="B53:F53"/>
+    <x:mergeCell ref="B54:E54"/>
+    <x:mergeCell ref="B55:E55"/>
+    <x:mergeCell ref="B56:E56"/>
+    <x:mergeCell ref="B57:E57"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -149,15 +149,36 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
-    <x:t>zxcasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
   </x:si>
   <x:si>
@@ -173,9 +194,6 @@
     <x:t>61-4-2026-1249-913</x:t>
   </x:si>
   <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08097</x:t>
   </x:si>
   <x:si>
@@ -215,12 +233,6 @@
     <x:t>zcx</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08092</x:t>
   </x:si>
   <x:si>
@@ -230,6 +242,15 @@
     <x:t>zsd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
   </x:si>
   <x:si>
@@ -299,13 +320,13 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
@@ -317,19 +338,58 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08173</x:t>
@@ -386,12 +446,6 @@
     <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08153</x:t>
   </x:si>
   <x:si>
@@ -401,6 +455,12 @@
     <x:t>zxcasdadasdxasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08148</x:t>
   </x:si>
   <x:si>
@@ -446,12 +506,6 @@
     <x:t>cxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08134</x:t>
   </x:si>
   <x:si>
@@ -461,22 +515,10 @@
     <x:t>resdxcv</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4100,10 +4142,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>43</x:v>
@@ -4112,7 +4154,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -4138,19 +4180,19 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K10" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -4170,25 +4212,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F11" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="H11" s="32">
+        <x:v>46119.8029380671</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>46120.5237086343</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="H11" s="32">
-        <x:v>46119.7297941435</x:v>
-      </x:c>
-      <x:c r="I11" s="32">
-        <x:v>46119.731450544</x:v>
-      </x:c>
-      <x:c r="J11" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K11" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -4208,25 +4250,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F12" s="30" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H12" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K12" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -4246,25 +4288,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="30" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>46119.8017436343</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>46119.8048384144</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G13" s="30" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H13" s="32">
-        <x:v>46119.7285584838</x:v>
-      </x:c>
-      <x:c r="I13" s="32">
-        <x:v>46119.7318005208</x:v>
-      </x:c>
-      <x:c r="J13" s="31" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="K13" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -4284,25 +4326,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G14" s="30" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -4322,25 +4364,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="H15" s="32">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="H15" s="32">
-        <x:v>46119.5439653357</x:v>
-      </x:c>
-      <x:c r="I15" s="32">
-        <x:v>46119.5452984143</x:v>
-      </x:c>
-      <x:c r="J15" s="31" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -4360,25 +4402,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H16" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -4398,25 +4440,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G17" s="30" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -4436,25 +4478,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H18" s="32">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="G18" s="30" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H18" s="32">
-        <x:v>46119.542956794</x:v>
-      </x:c>
-      <x:c r="I18" s="32">
-        <x:v>46119.5456356481</x:v>
-      </x:c>
-      <x:c r="J18" s="31" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -4474,25 +4516,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G19" s="30" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H19" s="32">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I19" s="32">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="G19" s="30" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H19" s="32">
-        <x:v>46119.5267212153</x:v>
-      </x:c>
-      <x:c r="I19" s="32">
-        <x:v>46119.5274664236</x:v>
-      </x:c>
-      <x:c r="J19" s="31" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -4512,25 +4554,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H20" s="32">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="G20" s="30" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H20" s="32">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I20" s="32">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J20" s="31" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -4550,25 +4592,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G21" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G21" s="30" t="s">
+      <x:c r="H21" s="32">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I21" s="32">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="H21" s="32">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I21" s="32">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J21" s="31" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -4588,25 +4630,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G22" s="30" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G22" s="30" t="s">
+      <x:c r="H22" s="32">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="H22" s="32">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I22" s="32">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J22" s="31" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -4626,25 +4668,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G23" s="30" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="H23" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>81</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -4664,25 +4706,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G24" s="30" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H24" s="32">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I24" s="32">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="G24" s="30" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H24" s="32">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I24" s="32">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J24" s="31" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -4702,25 +4744,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G25" s="30" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H25" s="32">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I25" s="32">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="G25" s="30" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H25" s="32">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I25" s="32">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J25" s="31" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -4740,25 +4782,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G26" s="30" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H26" s="32">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I26" s="32">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="G26" s="30" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H26" s="32">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I26" s="32">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J26" s="31" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -4778,25 +4820,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G27" s="30" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H27" s="32">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="G27" s="30" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H27" s="32">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I27" s="32">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J27" s="31" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -4816,25 +4858,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G28" s="30" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H28" s="32">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I28" s="32">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="G28" s="30" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H28" s="32">
-        <x:v>46118.3446055671</x:v>
-      </x:c>
-      <x:c r="I28" s="32">
-        <x:v>46118.476906412</x:v>
-      </x:c>
-      <x:c r="J28" s="31" t="s">
-        <x:v>96</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -4854,25 +4896,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G29" s="30" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H29" s="32">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I29" s="32">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G29" s="30" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H29" s="32">
-        <x:v>46120.2349196412</x:v>
-      </x:c>
-      <x:c r="I29" s="32">
-        <x:v>46120.5229746296</x:v>
-      </x:c>
-      <x:c r="J29" s="31" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="K29" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -4892,10 +4934,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G30" s="30" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="G30" s="30" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="H30" s="32">
         <x:v>46120.2374046412</x:v>
@@ -4904,7 +4946,7 @@
         <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
@@ -4930,25 +4972,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G31" s="30" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="G31" s="30" t="s">
+      <x:c r="H31" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I31" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="H31" s="32">
-        <x:v>46122.5587807523</x:v>
-      </x:c>
-      <x:c r="I31" s="32">
-        <x:v>46122.5602428125</x:v>
-      </x:c>
-      <x:c r="J31" s="31" t="s">
-        <x:v>104</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -4968,25 +5010,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G32" s="30" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="G32" s="30" t="s">
-        <x:v>106</x:v>
-      </x:c>
       <x:c r="H32" s="32">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46122.398526713</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -5006,25 +5048,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G33" s="30" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G33" s="30" t="s">
-        <x:v>108</x:v>
-      </x:c>
       <x:c r="H33" s="32">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -5044,25 +5086,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G34" s="30" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="G34" s="30" t="s">
+      <x:c r="H34" s="32">
+        <x:v>46122.6819179514</x:v>
+      </x:c>
+      <x:c r="I34" s="32">
+        <x:v>46122.6826717361</x:v>
+      </x:c>
+      <x:c r="J34" s="31" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="H34" s="32">
-        <x:v>46122.3879258681</x:v>
-      </x:c>
-      <x:c r="I34" s="32">
-        <x:v>46122.3894281713</x:v>
-      </x:c>
-      <x:c r="J34" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -5088,19 +5130,19 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>113</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -5120,16 +5162,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G36" s="30" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="G36" s="30" t="s">
-        <x:v>115</x:v>
-      </x:c>
       <x:c r="H36" s="32">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
         <x:v>43</x:v>
@@ -5138,7 +5180,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -5158,16 +5200,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G37" s="30" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G37" s="30" t="s">
-        <x:v>117</x:v>
-      </x:c>
       <x:c r="H37" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
         <x:v>28</x:v>
@@ -5176,7 +5218,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -5196,25 +5238,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G38" s="30" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="G38" s="30" t="s">
+      <x:c r="H38" s="32">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I38" s="32">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="H38" s="32">
-        <x:v>46122.2429836343</x:v>
-      </x:c>
-      <x:c r="I38" s="32">
-        <x:v>46122.244317963</x:v>
-      </x:c>
-      <x:c r="J38" s="31" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -5240,19 +5282,19 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -5278,10 +5320,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
         <x:v>124</x:v>
@@ -5290,7 +5332,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -5316,19 +5358,19 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
-        <x:v>127</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -5348,25 +5390,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="30" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G42" s="30" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G42" s="30" t="s">
-        <x:v>129</x:v>
-      </x:c>
       <x:c r="H42" s="32">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
-        <x:v>130</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -5386,25 +5428,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F43" s="30" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G43" s="30" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>133</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -5424,25 +5466,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F44" s="30" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G44" s="30" t="s">
-        <x:v>135</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -5462,25 +5504,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F45" s="30" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G45" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
-        <x:v>139</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K45" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -5500,16 +5542,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="30" t="s">
-        <x:v>140</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G46" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H46" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
         <x:v>28</x:v>
@@ -5518,7 +5560,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -5538,25 +5580,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="30" t="s">
-        <x:v>142</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G47" s="30" t="s">
-        <x:v>143</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H47" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I47" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
-        <x:v>144</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K47" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -5576,25 +5618,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="30" t="s">
-        <x:v>145</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G48" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H48" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I48" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J48" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -5614,10 +5656,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F49" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G49" s="30" t="s">
-        <x:v>148</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H49" s="32">
         <x:v>46122.1299166204</x:v>
@@ -5626,7 +5668,7 @@
         <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J49" s="31" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
         <x:v>210</x:v>
@@ -5652,91 +5694,313 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G50" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H50" s="32">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I50" s="32">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>70</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B51" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C51" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D51" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E51" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F51" s="30" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G51" s="30" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H51" s="32">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I51" s="32">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J51" s="31" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K51" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L51" s="34">
+        <x:v>46122.230922581</x:v>
+      </x:c>
+      <x:c r="M51" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B52" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C52" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D52" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E52" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F52" s="30" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="G52" s="30" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H52" s="32">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I52" s="32">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J52" s="31" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="K52" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L52" s="34">
+        <x:v>46122.2310990278</x:v>
+      </x:c>
+      <x:c r="M52" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="53" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B53" s="18" t="s">
+      <x:c r="B53" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C53" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D53" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E53" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F53" s="30" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G53" s="30" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H53" s="32">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I53" s="32">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J53" s="31" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="K53" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L53" s="34">
+        <x:v>46121.4980146875</x:v>
+      </x:c>
+      <x:c r="M53" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B54" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C54" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D54" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E54" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F54" s="30" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G54" s="30" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H54" s="32">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I54" s="32">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J54" s="31" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="K54" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L54" s="34">
+        <x:v>46121.498248206</x:v>
+      </x:c>
+      <x:c r="M54" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B55" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C55" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D55" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E55" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F55" s="30" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G55" s="30" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="H55" s="32">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I55" s="32">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J55" s="31" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="K55" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L55" s="34">
+        <x:v>46121.1027298958</x:v>
+      </x:c>
+      <x:c r="M55" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B56" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C56" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D56" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E56" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F56" s="30" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G56" s="30" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H56" s="32">
+        <x:v>46122.7261372338</x:v>
+      </x:c>
+      <x:c r="I56" s="32">
+        <x:v>46122.727234375</x:v>
+      </x:c>
+      <x:c r="J56" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K56" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L56" s="34">
+        <x:v>46122.7277720023</x:v>
+      </x:c>
+      <x:c r="M56" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B59" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C53" s="19" t="s"/>
-      <x:c r="D53" s="19" t="s"/>
-      <x:c r="E53" s="20" t="s"/>
-      <x:c r="F53" s="20" t="s"/>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B54" s="21" t="s">
+      <x:c r="C59" s="19" t="s"/>
+      <x:c r="D59" s="19" t="s"/>
+      <x:c r="E59" s="20" t="s"/>
+      <x:c r="F59" s="20" t="s"/>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B60" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C54" s="22" t="s"/>
-      <x:c r="D54" s="22" t="s"/>
-      <x:c r="E54" s="22" t="s"/>
-      <x:c r="F54" s="23" t="s">
+      <x:c r="C60" s="22" t="s"/>
+      <x:c r="D60" s="22" t="s"/>
+      <x:c r="E60" s="22" t="s"/>
+      <x:c r="F60" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="24" t="s">
+    <x:row r="61" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B61" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C55" s="25" t="s"/>
-      <x:c r="D55" s="25" t="s"/>
-      <x:c r="E55" s="25" t="s"/>
-      <x:c r="F55" s="26" t="n">
+      <x:c r="C61" s="25" t="s"/>
+      <x:c r="D61" s="25" t="s"/>
+      <x:c r="E61" s="25" t="s"/>
+      <x:c r="F61" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="24" t="s">
+    <x:row r="62" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B62" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C56" s="25" t="s"/>
-      <x:c r="D56" s="25" t="s"/>
-      <x:c r="E56" s="25" t="s"/>
-      <x:c r="F56" s="26" t="n">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B57" s="27" t="s">
+      <x:c r="C62" s="25" t="s"/>
+      <x:c r="D62" s="25" t="s"/>
+      <x:c r="E62" s="25" t="s"/>
+      <x:c r="F62" s="26" t="n">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B63" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C57" s="28" t="s"/>
-      <x:c r="D57" s="28" t="s"/>
-      <x:c r="E57" s="28" t="s"/>
-      <x:c r="F57" s="29" t="n">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C63" s="28" t="s"/>
+      <x:c r="D63" s="28" t="s"/>
+      <x:c r="E63" s="28" t="s"/>
+      <x:c r="F63" s="29" t="n">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
     <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6673,11 +6937,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B53:F53"/>
-    <x:mergeCell ref="B54:E54"/>
-    <x:mergeCell ref="B55:E55"/>
-    <x:mergeCell ref="B56:E56"/>
-    <x:mergeCell ref="B57:E57"/>
+    <x:mergeCell ref="B59:F59"/>
+    <x:mergeCell ref="B60:E60"/>
+    <x:mergeCell ref="B61:E61"/>
+    <x:mergeCell ref="B62:E62"/>
+    <x:mergeCell ref="B63:E63"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -149,6 +149,21 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08118</x:t>
   </x:si>
   <x:si>
@@ -320,13 +335,121 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
@@ -338,60 +461,6 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08173</x:t>
   </x:si>
   <x:si>
@@ -401,124 +470,100 @@
     <x:t>zcasdazcxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08172</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1284-135</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4142,19 +4187,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K9" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -4174,25 +4219,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F10" s="30" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="H10" s="32">
+        <x:v>46120.2374046412</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>46120.5224942245</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H10" s="32">
-        <x:v>46120.2349196412</x:v>
-      </x:c>
-      <x:c r="I10" s="32">
-        <x:v>46120.5229746296</x:v>
-      </x:c>
-      <x:c r="J10" s="31" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="K10" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -4218,10 +4263,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>48</x:v>
@@ -4230,7 +4275,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -4256,19 +4301,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="K12" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -4294,10 +4339,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>53</x:v>
@@ -4306,7 +4351,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -4332,19 +4377,19 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -4370,10 +4415,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
         <x:v>58</x:v>
@@ -4382,7 +4427,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -4408,10 +4453,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
         <x:v>48</x:v>
@@ -4420,7 +4465,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -4446,19 +4491,19 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -4478,25 +4523,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G18" s="30" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -4522,19 +4567,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>68</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -4554,25 +4599,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
+      <x:c r="H20" s="32">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="H20" s="32">
-        <x:v>46119.542956794</x:v>
-      </x:c>
-      <x:c r="I20" s="32">
-        <x:v>46119.5456356481</x:v>
-      </x:c>
-      <x:c r="J20" s="31" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -4592,25 +4637,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G21" s="30" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G21" s="30" t="s">
+      <x:c r="H21" s="32">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I21" s="32">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="H21" s="32">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I21" s="32">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J21" s="31" t="s">
-        <x:v>74</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -4630,25 +4675,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G22" s="30" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G22" s="30" t="s">
+      <x:c r="H22" s="32">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="H22" s="32">
-        <x:v>46119.5267212153</x:v>
-      </x:c>
-      <x:c r="I22" s="32">
-        <x:v>46119.5274664236</x:v>
-      </x:c>
-      <x:c r="J22" s="31" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -4668,25 +4713,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G23" s="30" t="s">
+      <x:c r="H23" s="32">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I23" s="32">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="H23" s="32">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I23" s="32">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J23" s="31" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -4712,10 +4757,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
         <x:v>82</x:v>
@@ -4724,7 +4769,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -4750,19 +4795,19 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>85</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -4782,25 +4827,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G26" s="30" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G26" s="30" t="s">
+      <x:c r="H26" s="32">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I26" s="32">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="H26" s="32">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I26" s="32">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J26" s="31" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -4820,25 +4865,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G27" s="30" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G27" s="30" t="s">
+      <x:c r="H27" s="32">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="H27" s="32">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I27" s="32">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J27" s="31" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -4858,25 +4903,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G28" s="30" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G28" s="30" t="s">
+      <x:c r="H28" s="32">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I28" s="32">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="H28" s="32">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I28" s="32">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J28" s="31" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -4896,25 +4941,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G29" s="30" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G29" s="30" t="s">
+      <x:c r="H29" s="32">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I29" s="32">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="H29" s="32">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I29" s="32">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J29" s="31" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -4934,25 +4979,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G30" s="30" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G30" s="30" t="s">
+      <x:c r="H30" s="32">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I30" s="32">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="H30" s="32">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I30" s="32">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J30" s="31" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -4972,25 +5017,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G31" s="30" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G31" s="30" t="s">
+      <x:c r="H31" s="32">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I31" s="32">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="H31" s="32">
-        <x:v>46118.3446055671</x:v>
-      </x:c>
-      <x:c r="I31" s="32">
-        <x:v>46118.476906412</x:v>
-      </x:c>
-      <x:c r="J31" s="31" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -5010,25 +5055,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G32" s="30" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G32" s="30" t="s">
+      <x:c r="H32" s="32">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I32" s="32">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J32" s="31" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="H32" s="32">
-        <x:v>46120.7129542245</x:v>
-      </x:c>
-      <x:c r="I32" s="32">
-        <x:v>46121.100944213</x:v>
-      </x:c>
-      <x:c r="J32" s="31" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -5092,10 +5137,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
         <x:v>110</x:v>
@@ -5104,7 +5149,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -5130,19 +5175,19 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -5162,25 +5207,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G36" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -5200,25 +5245,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G37" s="30" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -5238,25 +5283,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G38" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H38" s="32">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I38" s="32">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -5276,25 +5321,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F39" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G39" s="30" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
-        <x:v>77</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -5314,25 +5359,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F40" s="30" t="s">
-        <x:v>122</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G40" s="30" t="s">
-        <x:v>123</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>124</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -5352,25 +5397,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F41" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G41" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
-        <x:v>43</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -5390,25 +5435,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G42" s="30" t="s">
-        <x:v>128</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
-        <x:v>48</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -5428,25 +5473,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F43" s="30" t="s">
-        <x:v>129</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G43" s="30" t="s">
-        <x:v>130</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -5466,25 +5511,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F44" s="30" t="s">
-        <x:v>131</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G44" s="30" t="s">
-        <x:v>132</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>133</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -5504,25 +5549,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F45" s="30" t="s">
-        <x:v>134</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G45" s="30" t="s">
-        <x:v>135</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
-        <x:v>48</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="K45" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -5542,25 +5587,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="30" t="s">
-        <x:v>136</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G46" s="30" t="s">
-        <x:v>137</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H46" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K46" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -5580,25 +5625,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G47" s="30" t="s">
-        <x:v>139</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H47" s="32">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I47" s="32">
-        <x:v>46122.244317963</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
-        <x:v>100</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K47" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -5618,25 +5663,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="30" t="s">
-        <x:v>140</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G48" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H48" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I48" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J48" s="31" t="s">
-        <x:v>142</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -5656,25 +5701,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F49" s="30" t="s">
-        <x:v>143</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G49" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H49" s="32">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I49" s="32">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J49" s="31" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="34">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M49" s="30" t="s">
         <x:v>21</x:v>
@@ -5694,25 +5739,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="30" t="s">
-        <x:v>145</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G50" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H50" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I50" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>147</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
@@ -5732,25 +5777,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F51" s="30" t="s">
-        <x:v>148</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G51" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H51" s="32">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I51" s="32">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J51" s="31" t="s">
-        <x:v>150</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="K51" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M51" s="30" t="s">
         <x:v>21</x:v>
@@ -5770,25 +5815,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F52" s="30" t="s">
-        <x:v>151</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G52" s="30" t="s">
-        <x:v>152</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H52" s="32">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I52" s="32">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J52" s="31" t="s">
-        <x:v>153</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K52" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M52" s="30" t="s">
         <x:v>21</x:v>
@@ -5808,25 +5853,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="30" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G53" s="30" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H53" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I53" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>156</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -5846,25 +5891,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="30" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G54" s="30" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H54" s="32">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I54" s="32">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J54" s="31" t="s">
-        <x:v>159</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K54" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -5884,25 +5929,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="30" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G55" s="30" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H55" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I55" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J55" s="31" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K55" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -5922,90 +5967,275 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="30" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G56" s="30" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H56" s="32">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I56" s="32">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J56" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K56" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B57" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C57" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D57" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E57" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F57" s="30" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G57" s="30" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H57" s="32">
+        <x:v>46121.5183984954</x:v>
+      </x:c>
+      <x:c r="I57" s="32">
+        <x:v>46122.2061737153</x:v>
+      </x:c>
+      <x:c r="J57" s="31" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="K57" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L57" s="34">
+        <x:v>46122.2307100926</x:v>
+      </x:c>
+      <x:c r="M57" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B58" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C58" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D58" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E58" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F58" s="30" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G58" s="30" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H58" s="32">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I58" s="32">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J58" s="31" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="K58" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L58" s="34">
+        <x:v>46122.230922581</x:v>
+      </x:c>
+      <x:c r="M58" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="59" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B59" s="18" t="s">
+      <x:c r="B59" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C59" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D59" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E59" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F59" s="30" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G59" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H59" s="32">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I59" s="32">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J59" s="31" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="K59" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L59" s="34">
+        <x:v>46122.2310990278</x:v>
+      </x:c>
+      <x:c r="M59" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B60" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C60" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D60" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E60" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F60" s="30" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="G60" s="30" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H60" s="32">
+        <x:v>46122.3974322338</x:v>
+      </x:c>
+      <x:c r="I60" s="32">
+        <x:v>46122.3980999421</x:v>
+      </x:c>
+      <x:c r="J60" s="31" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K60" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L60" s="34">
+        <x:v>46122.398526713</x:v>
+      </x:c>
+      <x:c r="M60" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B61" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C61" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D61" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E61" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F61" s="30" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G61" s="30" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H61" s="32">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I61" s="32">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J61" s="31" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="K61" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L61" s="34">
+        <x:v>46123.4214065278</x:v>
+      </x:c>
+      <x:c r="M61" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B64" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C59" s="19" t="s"/>
-      <x:c r="D59" s="19" t="s"/>
-      <x:c r="E59" s="20" t="s"/>
-      <x:c r="F59" s="20" t="s"/>
-    </x:row>
-    <x:row r="60" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B60" s="21" t="s">
+      <x:c r="C64" s="19" t="s"/>
+      <x:c r="D64" s="19" t="s"/>
+      <x:c r="E64" s="20" t="s"/>
+      <x:c r="F64" s="20" t="s"/>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B65" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C60" s="22" t="s"/>
-      <x:c r="D60" s="22" t="s"/>
-      <x:c r="E60" s="22" t="s"/>
-      <x:c r="F60" s="23" t="s">
+      <x:c r="C65" s="22" t="s"/>
+      <x:c r="D65" s="22" t="s"/>
+      <x:c r="E65" s="22" t="s"/>
+      <x:c r="F65" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B61" s="24" t="s">
+    <x:row r="66" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B66" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C61" s="25" t="s"/>
-      <x:c r="D61" s="25" t="s"/>
-      <x:c r="E61" s="25" t="s"/>
-      <x:c r="F61" s="26" t="n">
+      <x:c r="C66" s="25" t="s"/>
+      <x:c r="D66" s="25" t="s"/>
+      <x:c r="E66" s="25" t="s"/>
+      <x:c r="F66" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B62" s="24" t="s">
+    <x:row r="67" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B67" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C62" s="25" t="s"/>
-      <x:c r="D62" s="25" t="s"/>
-      <x:c r="E62" s="25" t="s"/>
-      <x:c r="F62" s="26" t="n">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B63" s="27" t="s">
+      <x:c r="C67" s="25" t="s"/>
+      <x:c r="D67" s="25" t="s"/>
+      <x:c r="E67" s="25" t="s"/>
+      <x:c r="F67" s="26" t="n">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B68" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C63" s="28" t="s"/>
-      <x:c r="D63" s="28" t="s"/>
-      <x:c r="E63" s="28" t="s"/>
-      <x:c r="F63" s="29" t="n">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C68" s="28" t="s"/>
+      <x:c r="D68" s="28" t="s"/>
+      <x:c r="E68" s="28" t="s"/>
+      <x:c r="F68" s="29" t="n">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
     <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6937,11 +7167,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B59:F59"/>
-    <x:mergeCell ref="B60:E60"/>
-    <x:mergeCell ref="B61:E61"/>
-    <x:mergeCell ref="B62:E62"/>
-    <x:mergeCell ref="B63:E63"/>
+    <x:mergeCell ref="B64:F64"/>
+    <x:mergeCell ref="B65:E65"/>
+    <x:mergeCell ref="B66:E66"/>
+    <x:mergeCell ref="B67:E67"/>
+    <x:mergeCell ref="B68:E68"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="216">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -149,6 +149,66 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
   </x:si>
   <x:si>
@@ -203,12 +263,135 @@
     <x:t>asd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08098</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1249-913</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08097</x:t>
   </x:si>
   <x:si>
@@ -218,154 +401,136 @@
     <x:t>zcasdqwezxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08184</x:t>
@@ -377,6 +542,12 @@
     <x:t>test12</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08183</x:t>
   </x:si>
   <x:si>
@@ -386,6 +557,105 @@
     <x:t>zsdasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08182</x:t>
   </x:si>
   <x:si>
@@ -395,175 +665,13 @@
     <x:t>sdasqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4187,19 +4295,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K9" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -4219,25 +4327,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F10" s="30" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G10" s="30" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K10" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -4257,25 +4365,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F11" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G11" s="30" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K11" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -4295,25 +4403,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F12" s="30" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G12" s="30" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K12" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -4333,25 +4441,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="30" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G13" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K13" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -4371,25 +4479,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G14" s="30" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -4409,25 +4517,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G15" s="30" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -4447,25 +4555,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G16" s="30" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>48</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -4485,25 +4593,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G17" s="30" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -4523,25 +4631,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G18" s="30" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -4561,25 +4669,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G19" s="30" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -4599,25 +4707,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G20" s="30" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -4637,16 +4745,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G21" s="30" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
         <x:v>73</x:v>
@@ -4655,7 +4763,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -4675,25 +4783,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -4713,25 +4821,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G23" s="30" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -4751,25 +4859,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G24" s="30" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
-        <x:v>82</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -4795,19 +4903,19 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -4833,19 +4941,19 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>87</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -4865,25 +4973,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G27" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="G27" s="30" t="s">
+      <x:c r="H27" s="32">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="H27" s="32">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I27" s="32">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J27" s="31" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -4903,25 +5011,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G28" s="30" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G28" s="30" t="s">
+      <x:c r="H28" s="32">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I28" s="32">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="H28" s="32">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I28" s="32">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J28" s="31" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -4941,25 +5049,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G29" s="30" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G29" s="30" t="s">
+      <x:c r="H29" s="32">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I29" s="32">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="H29" s="32">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I29" s="32">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J29" s="31" t="s">
-        <x:v>96</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -4979,25 +5087,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G30" s="30" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G30" s="30" t="s">
+      <x:c r="H30" s="32">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I30" s="32">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="H30" s="32">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I30" s="32">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J30" s="31" t="s">
-        <x:v>99</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -5017,25 +5125,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G31" s="30" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G31" s="30" t="s">
+      <x:c r="H31" s="32">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I31" s="32">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="H31" s="32">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I31" s="32">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J31" s="31" t="s">
-        <x:v>102</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -5055,25 +5163,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G32" s="30" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G32" s="30" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="H32" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>105</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -5093,25 +5201,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G33" s="30" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H33" s="32">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I33" s="32">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J33" s="31" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="G33" s="30" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H33" s="32">
-        <x:v>46121.2273626852</x:v>
-      </x:c>
-      <x:c r="I33" s="32">
-        <x:v>46121.228379213</x:v>
-      </x:c>
-      <x:c r="J33" s="31" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -5131,25 +5239,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G34" s="30" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G34" s="30" t="s">
+      <x:c r="H34" s="32">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I34" s="32">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J34" s="31" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="H34" s="32">
-        <x:v>46121.2464636111</x:v>
-      </x:c>
-      <x:c r="I34" s="32">
-        <x:v>46121.3217277662</x:v>
-      </x:c>
-      <x:c r="J34" s="31" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -5169,25 +5277,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G35" s="30" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G35" s="30" t="s">
+      <x:c r="H35" s="32">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I35" s="32">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J35" s="31" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="H35" s="32">
-        <x:v>46121.4966047917</x:v>
-      </x:c>
-      <x:c r="I35" s="32">
-        <x:v>46121.4974146412</x:v>
-      </x:c>
-      <x:c r="J35" s="31" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -5207,25 +5315,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G36" s="30" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="G36" s="30" t="s">
+      <x:c r="H36" s="32">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I36" s="32">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J36" s="31" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="H36" s="32">
-        <x:v>46123.4162791088</x:v>
-      </x:c>
-      <x:c r="I36" s="32">
-        <x:v>46123.4173169792</x:v>
-      </x:c>
-      <x:c r="J36" s="31" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46123.417862662</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -5245,25 +5353,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G37" s="30" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G37" s="30" t="s">
+      <x:c r="H37" s="32">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I37" s="32">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J37" s="31" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="H37" s="32">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I37" s="32">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J37" s="31" t="s">
-        <x:v>119</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -5283,25 +5391,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G38" s="30" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G38" s="30" t="s">
+      <x:c r="H38" s="32">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I38" s="32">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="H38" s="32">
-        <x:v>46123.0476912847</x:v>
-      </x:c>
-      <x:c r="I38" s="32">
-        <x:v>46123.0484775694</x:v>
-      </x:c>
-      <x:c r="J38" s="31" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46123.049084375</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -5321,25 +5429,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F39" s="30" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G39" s="30" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G39" s="30" t="s">
+      <x:c r="H39" s="32">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I39" s="32">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J39" s="31" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="H39" s="32">
-        <x:v>46122.9452935995</x:v>
-      </x:c>
-      <x:c r="I39" s="32">
-        <x:v>46123.0460683681</x:v>
-      </x:c>
-      <x:c r="J39" s="31" t="s">
-        <x:v>125</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -5359,25 +5467,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F40" s="30" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G40" s="30" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="G40" s="30" t="s">
+      <x:c r="H40" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I40" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J40" s="31" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="H40" s="32">
-        <x:v>46122.7261372338</x:v>
-      </x:c>
-      <x:c r="I40" s="32">
-        <x:v>46122.727234375</x:v>
-      </x:c>
-      <x:c r="J40" s="31" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -5403,10 +5511,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
         <x:v>130</x:v>
@@ -5415,7 +5523,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -5441,10 +5549,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
         <x:v>28</x:v>
@@ -5453,7 +5561,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -5479,19 +5587,19 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>48</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -5511,25 +5619,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F44" s="30" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G44" s="30" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -5549,25 +5657,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F45" s="30" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G45" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
-        <x:v>139</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K45" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -5587,25 +5695,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="30" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G46" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H46" s="32">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
-        <x:v>82</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="K46" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -5625,25 +5733,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="30" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G47" s="30" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H47" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I47" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K47" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -5663,25 +5771,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="30" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G48" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="H48" s="32">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I48" s="32">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J48" s="31" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -5701,25 +5809,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F49" s="30" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G49" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H49" s="32">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I49" s="32">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J49" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="34">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M49" s="30" t="s">
         <x:v>21</x:v>
@@ -5739,25 +5847,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G50" s="30" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H50" s="32">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I50" s="32">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>48</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
@@ -5777,25 +5885,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F51" s="30" t="s">
-        <x:v>152</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G51" s="30" t="s">
-        <x:v>153</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H51" s="32">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I51" s="32">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J51" s="31" t="s">
-        <x:v>154</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K51" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="34">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M51" s="30" t="s">
         <x:v>21</x:v>
@@ -5815,25 +5923,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F52" s="30" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G52" s="30" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H52" s="32">
-        <x:v>46122.36782125</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I52" s="32">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J52" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="K52" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M52" s="30" t="s">
         <x:v>21</x:v>
@@ -5853,25 +5961,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="30" t="s">
-        <x:v>157</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G53" s="30" t="s">
-        <x:v>158</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H53" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I53" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -5891,25 +5999,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G54" s="30" t="s">
-        <x:v>160</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H54" s="32">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I54" s="32">
-        <x:v>46122.244317963</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J54" s="31" t="s">
-        <x:v>45</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="K54" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -5929,25 +6037,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="30" t="s">
-        <x:v>161</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G55" s="30" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H55" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I55" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J55" s="31" t="s">
-        <x:v>163</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="K55" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -5967,25 +6075,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="30" t="s">
-        <x:v>164</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G56" s="30" t="s">
-        <x:v>165</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H56" s="32">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I56" s="32">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J56" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="K56" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
@@ -6005,25 +6113,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G57" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H57" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I57" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J57" s="31" t="s">
-        <x:v>168</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K57" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M57" s="30" t="s">
         <x:v>21</x:v>
@@ -6043,25 +6151,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="30" t="s">
-        <x:v>169</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G58" s="30" t="s">
-        <x:v>170</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H58" s="32">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I58" s="32">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J58" s="31" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K58" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M58" s="30" t="s">
         <x:v>21</x:v>
@@ -6081,25 +6189,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="30" t="s">
-        <x:v>172</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G59" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H59" s="32">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I59" s="32">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J59" s="31" t="s">
-        <x:v>174</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="K59" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M59" s="30" t="s">
         <x:v>21</x:v>
@@ -6119,25 +6227,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="30" t="s">
-        <x:v>175</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G60" s="30" t="s">
-        <x:v>176</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H60" s="32">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I60" s="32">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J60" s="31" t="s">
-        <x:v>48</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K60" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="34">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M60" s="30" t="s">
         <x:v>21</x:v>
@@ -6157,98 +6265,579 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F61" s="30" t="s">
-        <x:v>177</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G61" s="30" t="s">
-        <x:v>178</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H61" s="32">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I61" s="32">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J61" s="31" t="s">
-        <x:v>179</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="K61" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="34">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M61" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B62" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C62" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D62" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E62" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F62" s="30" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G62" s="30" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H62" s="32">
+        <x:v>46122.6795081481</x:v>
+      </x:c>
+      <x:c r="I62" s="32">
+        <x:v>46122.6802186921</x:v>
+      </x:c>
+      <x:c r="J62" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K62" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L62" s="34">
+        <x:v>46122.6809879398</x:v>
+      </x:c>
+      <x:c r="M62" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B63" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C63" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D63" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E63" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F63" s="30" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G63" s="30" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H63" s="32">
+        <x:v>46122.6182774306</x:v>
+      </x:c>
+      <x:c r="I63" s="32">
+        <x:v>46122.6193276968</x:v>
+      </x:c>
+      <x:c r="J63" s="31" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K63" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L63" s="34">
+        <x:v>46122.6199813426</x:v>
+      </x:c>
+      <x:c r="M63" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="64" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B64" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C64" s="19" t="s"/>
-      <x:c r="D64" s="19" t="s"/>
-      <x:c r="E64" s="20" t="s"/>
-      <x:c r="F64" s="20" t="s"/>
-    </x:row>
-    <x:row r="65" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B65" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C65" s="22" t="s"/>
-      <x:c r="D65" s="22" t="s"/>
-      <x:c r="E65" s="22" t="s"/>
-      <x:c r="F65" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B66" s="24" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C66" s="25" t="s"/>
-      <x:c r="D66" s="25" t="s"/>
-      <x:c r="E66" s="25" t="s"/>
-      <x:c r="F66" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B67" s="24" t="s">
+      <x:c r="B64" s="30" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C67" s="25" t="s"/>
-      <x:c r="D67" s="25" t="s"/>
-      <x:c r="E67" s="25" t="s"/>
-      <x:c r="F67" s="26" t="n">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B68" s="27" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C68" s="28" t="s"/>
-      <x:c r="D68" s="28" t="s"/>
-      <x:c r="E68" s="28" t="s"/>
-      <x:c r="F68" s="29" t="n">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C64" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D64" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E64" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F64" s="30" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G64" s="30" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H64" s="32">
+        <x:v>46122.5945434491</x:v>
+      </x:c>
+      <x:c r="I64" s="32">
+        <x:v>46122.5999534606</x:v>
+      </x:c>
+      <x:c r="J64" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K64" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L64" s="34">
+        <x:v>46122.6007489699</x:v>
+      </x:c>
+      <x:c r="M64" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B65" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C65" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D65" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E65" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F65" s="30" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G65" s="30" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H65" s="32">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I65" s="32">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J65" s="31" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="K65" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L65" s="34">
+        <x:v>46122.5928339699</x:v>
+      </x:c>
+      <x:c r="M65" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B66" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C66" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D66" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E66" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F66" s="30" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G66" s="30" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H66" s="32">
+        <x:v>46122.5623107755</x:v>
+      </x:c>
+      <x:c r="I66" s="32">
+        <x:v>46122.5630093981</x:v>
+      </x:c>
+      <x:c r="J66" s="31" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="K66" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L66" s="34">
+        <x:v>46122.5634620023</x:v>
+      </x:c>
+      <x:c r="M66" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B67" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C67" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D67" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E67" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F67" s="30" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G67" s="30" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H67" s="32">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I67" s="32">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J67" s="31" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="K67" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L67" s="34">
+        <x:v>46122.5607516551</x:v>
+      </x:c>
+      <x:c r="M67" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B68" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C68" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D68" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E68" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F68" s="30" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G68" s="30" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H68" s="32">
+        <x:v>46122.3974322338</x:v>
+      </x:c>
+      <x:c r="I68" s="32">
+        <x:v>46122.3980999421</x:v>
+      </x:c>
+      <x:c r="J68" s="31" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K68" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L68" s="34">
+        <x:v>46122.398526713</x:v>
+      </x:c>
+      <x:c r="M68" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B69" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C69" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D69" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E69" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F69" s="30" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G69" s="30" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="H69" s="32">
+        <x:v>46122.3885020718</x:v>
+      </x:c>
+      <x:c r="I69" s="32">
+        <x:v>46122.3892655903</x:v>
+      </x:c>
+      <x:c r="J69" s="31" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K69" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L69" s="34">
+        <x:v>46122.3902404514</x:v>
+      </x:c>
+      <x:c r="M69" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B70" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C70" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D70" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E70" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F70" s="30" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G70" s="30" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H70" s="32">
+        <x:v>46122.3879258681</x:v>
+      </x:c>
+      <x:c r="I70" s="32">
+        <x:v>46122.3894281713</x:v>
+      </x:c>
+      <x:c r="J70" s="31" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K70" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L70" s="34">
+        <x:v>46122.3900310185</x:v>
+      </x:c>
+      <x:c r="M70" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B71" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C71" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D71" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E71" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F71" s="30" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G71" s="30" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H71" s="32">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I71" s="32">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J71" s="31" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="K71" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L71" s="34">
+        <x:v>46122.3780755324</x:v>
+      </x:c>
+      <x:c r="M71" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B72" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C72" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D72" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E72" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F72" s="30" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G72" s="30" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H72" s="32">
+        <x:v>46122.36782125</x:v>
+      </x:c>
+      <x:c r="I72" s="32">
+        <x:v>46122.3686719907</x:v>
+      </x:c>
+      <x:c r="J72" s="31" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K72" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L72" s="34">
+        <x:v>46122.3692180787</x:v>
+      </x:c>
+      <x:c r="M72" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B73" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C73" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D73" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E73" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F73" s="30" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G73" s="30" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H73" s="32">
+        <x:v>46123.0476912847</x:v>
+      </x:c>
+      <x:c r="I73" s="32">
+        <x:v>46123.0484775694</x:v>
+      </x:c>
+      <x:c r="J73" s="31" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="K73" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L73" s="34">
+        <x:v>46123.049084375</x:v>
+      </x:c>
+      <x:c r="M73" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B74" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C74" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D74" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E74" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F74" s="30" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G74" s="30" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H74" s="32">
+        <x:v>46124.7035032407</x:v>
+      </x:c>
+      <x:c r="I74" s="32">
+        <x:v>46124.704475463</x:v>
+      </x:c>
+      <x:c r="J74" s="31" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="K74" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L74" s="34">
+        <x:v>46124.7056197917</x:v>
+      </x:c>
+      <x:c r="M74" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B77" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C77" s="19" t="s"/>
+      <x:c r="D77" s="19" t="s"/>
+      <x:c r="E77" s="20" t="s"/>
+      <x:c r="F77" s="20" t="s"/>
+    </x:row>
+    <x:row r="78" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B78" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C78" s="22" t="s"/>
+      <x:c r="D78" s="22" t="s"/>
+      <x:c r="E78" s="22" t="s"/>
+      <x:c r="F78" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B79" s="24" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C79" s="25" t="s"/>
+      <x:c r="D79" s="25" t="s"/>
+      <x:c r="E79" s="25" t="s"/>
+      <x:c r="F79" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B80" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C80" s="25" t="s"/>
+      <x:c r="D80" s="25" t="s"/>
+      <x:c r="E80" s="25" t="s"/>
+      <x:c r="F80" s="26" t="n">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B81" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C81" s="28" t="s"/>
+      <x:c r="D81" s="28" t="s"/>
+      <x:c r="E81" s="28" t="s"/>
+      <x:c r="F81" s="29" t="n">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
     <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7167,11 +7756,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B64:F64"/>
-    <x:mergeCell ref="B65:E65"/>
-    <x:mergeCell ref="B66:E66"/>
-    <x:mergeCell ref="B67:E67"/>
-    <x:mergeCell ref="B68:E68"/>
+    <x:mergeCell ref="B77:F77"/>
+    <x:mergeCell ref="B78:E78"/>
+    <x:mergeCell ref="B79:E79"/>
+    <x:mergeCell ref="B80:E80"/>
+    <x:mergeCell ref="B81:E81"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="216">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="227">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -149,6 +149,60 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1316-566</x:t>
+  </x:si>
+  <x:si>
+    <x:t>szdasdqweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1323-538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08292</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1322-790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1321-473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08148</x:t>
   </x:si>
   <x:si>
@@ -245,9 +299,6 @@
     <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
-    <x:t>zxcasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
   </x:si>
   <x:si>
@@ -260,13 +311,130 @@
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08098</x:t>
@@ -275,130 +443,133 @@
     <x:t>61-4-2026-1249-913</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
@@ -410,268 +581,130 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08160</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4280,13 +4313,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="30" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="30" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="30" t="s">
         <x:v>41</x:v>
@@ -4295,19 +4328,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46124.9835281713</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46125.0608962963</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="K9" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46126.1641622569</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -4318,13 +4351,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="30" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D10" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="30" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="30" t="s">
         <x:v>44</x:v>
@@ -4333,10 +4366,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>46</x:v>
@@ -4345,7 +4378,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -4356,13 +4389,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="30" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D11" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E11" s="30" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="30" t="s">
         <x:v>47</x:v>
@@ -4371,10 +4404,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>49</x:v>
@@ -4383,7 +4416,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -4394,13 +4427,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="30" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D12" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E12" s="30" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="30" t="s">
         <x:v>50</x:v>
@@ -4409,10 +4442,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>52</x:v>
@@ -4421,7 +4454,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -4447,10 +4480,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>55</x:v>
@@ -4459,7 +4492,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -4485,19 +4518,19 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -4517,25 +4550,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G15" s="30" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -4555,25 +4588,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G16" s="30" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -4593,25 +4626,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G17" s="30" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -4631,25 +4664,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G18" s="30" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -4669,25 +4702,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G19" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -4707,25 +4740,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G20" s="30" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>73</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -4745,25 +4778,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G21" s="30" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -4783,25 +4816,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>78</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -4821,25 +4854,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G23" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>73</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -4859,25 +4892,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G24" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
-        <x:v>68</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -4897,25 +4930,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G25" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>73</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -4935,25 +4968,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>78</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -4973,25 +5006,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G27" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>89</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -5011,25 +5044,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>92</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -5049,25 +5082,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G29" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -5087,25 +5120,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G30" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -5125,25 +5158,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>101</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -5163,25 +5196,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -5201,25 +5234,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -5239,25 +5272,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -5277,25 +5310,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -5315,25 +5348,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G36" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -5353,25 +5386,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G37" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -5391,25 +5424,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G38" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H38" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I38" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
-        <x:v>121</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -5435,10 +5468,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
         <x:v>124</x:v>
@@ -5447,7 +5480,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -5473,10 +5506,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
         <x:v>127</x:v>
@@ -5485,7 +5518,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -5511,10 +5544,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
         <x:v>130</x:v>
@@ -5523,7 +5556,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -5549,19 +5582,19 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -5581,25 +5614,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F43" s="30" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G43" s="30" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -5619,25 +5652,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F44" s="30" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G44" s="30" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>138</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -5663,19 +5696,19 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46124.701771875</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
-        <x:v>73</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K45" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -5701,19 +5734,19 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="H46" s="32">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
-        <x:v>143</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K46" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -5733,25 +5766,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="30" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G47" s="30" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G47" s="30" t="s">
+      <x:c r="H47" s="32">
+        <x:v>46124.7035032407</x:v>
+      </x:c>
+      <x:c r="I47" s="32">
+        <x:v>46124.704475463</x:v>
+      </x:c>
+      <x:c r="J47" s="31" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="H47" s="32">
-        <x:v>46124.6761778356</x:v>
-      </x:c>
-      <x:c r="I47" s="32">
-        <x:v>46124.6772295602</x:v>
-      </x:c>
-      <x:c r="J47" s="31" t="s">
-        <x:v>146</x:v>
       </x:c>
       <x:c r="K47" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -5771,25 +5804,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="30" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G48" s="30" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="G48" s="30" t="s">
+      <x:c r="H48" s="32">
+        <x:v>46124.7029179398</x:v>
+      </x:c>
+      <x:c r="I48" s="32">
+        <x:v>46124.7046092014</x:v>
+      </x:c>
+      <x:c r="J48" s="31" t="s">
         <x:v>148</x:v>
-      </x:c>
-      <x:c r="H48" s="32">
-        <x:v>46124.5490358102</x:v>
-      </x:c>
-      <x:c r="I48" s="32">
-        <x:v>46124.6984689583</x:v>
-      </x:c>
-      <x:c r="J48" s="31" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -5809,25 +5842,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F49" s="30" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G49" s="30" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="G49" s="30" t="s">
+      <x:c r="H49" s="32">
+        <x:v>46124.7023532986</x:v>
+      </x:c>
+      <x:c r="I49" s="32">
+        <x:v>46124.7048005093</x:v>
+      </x:c>
+      <x:c r="J49" s="31" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="H49" s="32">
-        <x:v>46124.1518079282</x:v>
-      </x:c>
-      <x:c r="I49" s="32">
-        <x:v>46124.1529164583</x:v>
-      </x:c>
-      <x:c r="J49" s="31" t="s">
-        <x:v>152</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="34">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M49" s="30" t="s">
         <x:v>21</x:v>
@@ -5847,25 +5880,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="30" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G50" s="30" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G50" s="30" t="s">
-        <x:v>154</x:v>
-      </x:c>
       <x:c r="H50" s="32">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I50" s="32">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>155</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
@@ -5885,25 +5918,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F51" s="30" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G51" s="30" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H51" s="32">
+        <x:v>46124.6975491551</x:v>
+      </x:c>
+      <x:c r="I51" s="32">
+        <x:v>46124.6983328357</x:v>
+      </x:c>
+      <x:c r="J51" s="31" t="s">
         <x:v>156</x:v>
-      </x:c>
-      <x:c r="G51" s="30" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="H51" s="32">
-        <x:v>46124.150742662</x:v>
-      </x:c>
-      <x:c r="I51" s="32">
-        <x:v>46124.153253125</x:v>
-      </x:c>
-      <x:c r="J51" s="31" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="K51" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="34">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M51" s="30" t="s">
         <x:v>21</x:v>
@@ -5923,25 +5956,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F52" s="30" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G52" s="30" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="G52" s="30" t="s">
+      <x:c r="H52" s="32">
+        <x:v>46124.6761778356</x:v>
+      </x:c>
+      <x:c r="I52" s="32">
+        <x:v>46124.6772295602</x:v>
+      </x:c>
+      <x:c r="J52" s="31" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="H52" s="32">
-        <x:v>46124.1487218981</x:v>
-      </x:c>
-      <x:c r="I52" s="32">
-        <x:v>46124.1494313773</x:v>
-      </x:c>
-      <x:c r="J52" s="31" t="s">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="K52" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="34">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M52" s="30" t="s">
         <x:v>21</x:v>
@@ -5961,25 +5994,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="30" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G53" s="30" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="G53" s="30" t="s">
+      <x:c r="H53" s="32">
+        <x:v>46124.5490358102</x:v>
+      </x:c>
+      <x:c r="I53" s="32">
+        <x:v>46124.6984689583</x:v>
+      </x:c>
+      <x:c r="J53" s="31" t="s">
         <x:v>162</x:v>
-      </x:c>
-      <x:c r="H53" s="32">
-        <x:v>46124.1449755903</x:v>
-      </x:c>
-      <x:c r="I53" s="32">
-        <x:v>46124.1465040046</x:v>
-      </x:c>
-      <x:c r="J53" s="31" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -6005,10 +6038,10 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="H54" s="32">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I54" s="32">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J54" s="31" t="s">
         <x:v>165</x:v>
@@ -6017,7 +6050,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -6043,10 +6076,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="H55" s="32">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I55" s="32">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J55" s="31" t="s">
         <x:v>168</x:v>
@@ -6055,7 +6088,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -6081,19 +6114,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="H56" s="32">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I56" s="32">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J56" s="31" t="s">
-        <x:v>171</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K56" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46123.417862662</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
@@ -6113,25 +6146,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="30" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G57" s="30" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="G57" s="30" t="s">
+      <x:c r="H57" s="32">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I57" s="32">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J57" s="31" t="s">
         <x:v>173</x:v>
-      </x:c>
-      <x:c r="H57" s="32">
-        <x:v>46122.2429836343</x:v>
-      </x:c>
-      <x:c r="I57" s="32">
-        <x:v>46122.244317963</x:v>
-      </x:c>
-      <x:c r="J57" s="31" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="K57" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M57" s="30" t="s">
         <x:v>21</x:v>
@@ -6157,19 +6190,19 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="H58" s="32">
-        <x:v>46123.061368912</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I58" s="32">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J58" s="31" t="s">
-        <x:v>176</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K58" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="34">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M58" s="30" t="s">
         <x:v>21</x:v>
@@ -6189,25 +6222,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="30" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G59" s="30" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="G59" s="30" t="s">
+      <x:c r="H59" s="32">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I59" s="32">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J59" s="31" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="H59" s="32">
-        <x:v>46122.9452935995</x:v>
-      </x:c>
-      <x:c r="I59" s="32">
-        <x:v>46123.0460683681</x:v>
-      </x:c>
-      <x:c r="J59" s="31" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="K59" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="34">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M59" s="30" t="s">
         <x:v>21</x:v>
@@ -6227,25 +6260,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="30" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G60" s="30" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="G60" s="30" t="s">
+      <x:c r="H60" s="32">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I60" s="32">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J60" s="31" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="H60" s="32">
-        <x:v>46122.7261372338</x:v>
-      </x:c>
-      <x:c r="I60" s="32">
-        <x:v>46122.727234375</x:v>
-      </x:c>
-      <x:c r="J60" s="31" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K60" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="34">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M60" s="30" t="s">
         <x:v>21</x:v>
@@ -6271,10 +6304,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="H61" s="32">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I61" s="32">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J61" s="31" t="s">
         <x:v>184</x:v>
@@ -6283,7 +6316,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="34">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M61" s="30" t="s">
         <x:v>21</x:v>
@@ -6309,19 +6342,19 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="H62" s="32">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I62" s="32">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J62" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="K62" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="34">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M62" s="30" t="s">
         <x:v>21</x:v>
@@ -6341,25 +6374,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="30" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G63" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H63" s="32">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I63" s="32">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J63" s="31" t="s">
-        <x:v>68</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="K63" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="34">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M63" s="30" t="s">
         <x:v>21</x:v>
@@ -6379,25 +6412,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="30" t="s">
-        <x:v>189</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G64" s="30" t="s">
-        <x:v>190</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H64" s="32">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I64" s="32">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J64" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="K64" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="34">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M64" s="30" t="s">
         <x:v>21</x:v>
@@ -6417,25 +6450,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F65" s="30" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G65" s="30" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H65" s="32">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I65" s="32">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J65" s="31" t="s">
-        <x:v>193</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K65" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="34">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M65" s="30" t="s">
         <x:v>21</x:v>
@@ -6455,25 +6488,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="30" t="s">
-        <x:v>194</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G66" s="30" t="s">
-        <x:v>195</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H66" s="32">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I66" s="32">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J66" s="31" t="s">
-        <x:v>101</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="K66" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M66" s="30" t="s">
         <x:v>21</x:v>
@@ -6493,25 +6526,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="30" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G67" s="30" t="s">
-        <x:v>197</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H67" s="32">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I67" s="32">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J67" s="31" t="s">
-        <x:v>198</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K67" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M67" s="30" t="s">
         <x:v>21</x:v>
@@ -6531,25 +6564,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="30" t="s">
-        <x:v>199</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G68" s="30" t="s">
-        <x:v>200</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H68" s="32">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I68" s="32">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J68" s="31" t="s">
-        <x:v>68</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K68" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="34">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M68" s="30" t="s">
         <x:v>21</x:v>
@@ -6569,25 +6602,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="30" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G69" s="30" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="H69" s="32">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I69" s="32">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J69" s="31" t="s">
-        <x:v>73</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K69" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="34">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M69" s="30" t="s">
         <x:v>21</x:v>
@@ -6607,25 +6640,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="30" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G70" s="30" t="s">
-        <x:v>204</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H70" s="32">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I70" s="32">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J70" s="31" t="s">
-        <x:v>68</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="K70" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="34">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M70" s="30" t="s">
         <x:v>21</x:v>
@@ -6645,25 +6678,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="30" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G71" s="30" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H71" s="32">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I71" s="32">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J71" s="31" t="s">
-        <x:v>207</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K71" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="34">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M71" s="30" t="s">
         <x:v>21</x:v>
@@ -6683,25 +6716,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="30" t="s">
-        <x:v>208</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G72" s="30" t="s">
-        <x:v>209</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H72" s="32">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I72" s="32">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J72" s="31" t="s">
-        <x:v>73</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K72" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M72" s="30" t="s">
         <x:v>21</x:v>
@@ -6721,25 +6754,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F73" s="30" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G73" s="30" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H73" s="32">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I73" s="32">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J73" s="31" t="s">
-        <x:v>212</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K73" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="34">
-        <x:v>46123.049084375</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M73" s="30" t="s">
         <x:v>21</x:v>
@@ -6759,89 +6792,237 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F74" s="30" t="s">
-        <x:v>213</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="G74" s="30" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="H74" s="32">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I74" s="32">
-        <x:v>46124.704475463</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J74" s="31" t="s">
-        <x:v>215</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K74" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="34">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M74" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B75" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C75" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D75" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E75" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F75" s="30" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G75" s="30" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="H75" s="32">
+        <x:v>46122.3879258681</x:v>
+      </x:c>
+      <x:c r="I75" s="32">
+        <x:v>46122.3894281713</x:v>
+      </x:c>
+      <x:c r="J75" s="31" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K75" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L75" s="34">
+        <x:v>46122.3900310185</x:v>
+      </x:c>
+      <x:c r="M75" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B76" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C76" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D76" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E76" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F76" s="30" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G76" s="30" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H76" s="32">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I76" s="32">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J76" s="31" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="K76" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L76" s="34">
+        <x:v>46122.3780755324</x:v>
+      </x:c>
+      <x:c r="M76" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="77" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B77" s="18" t="s">
+      <x:c r="B77" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C77" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D77" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E77" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F77" s="30" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G77" s="30" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H77" s="32">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I77" s="32">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J77" s="31" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="K77" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L77" s="34">
+        <x:v>46123.0628773958</x:v>
+      </x:c>
+      <x:c r="M77" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B78" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C78" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D78" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E78" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F78" s="30" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G78" s="30" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="H78" s="32">
+        <x:v>46122.3569147569</x:v>
+      </x:c>
+      <x:c r="I78" s="32">
+        <x:v>46122.3577305324</x:v>
+      </x:c>
+      <x:c r="J78" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K78" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L78" s="34">
+        <x:v>46122.3582679861</x:v>
+      </x:c>
+      <x:c r="M78" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B81" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C77" s="19" t="s"/>
-      <x:c r="D77" s="19" t="s"/>
-      <x:c r="E77" s="20" t="s"/>
-      <x:c r="F77" s="20" t="s"/>
-    </x:row>
-    <x:row r="78" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B78" s="21" t="s">
+      <x:c r="C81" s="19" t="s"/>
+      <x:c r="D81" s="19" t="s"/>
+      <x:c r="E81" s="20" t="s"/>
+      <x:c r="F81" s="20" t="s"/>
+    </x:row>
+    <x:row r="82" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B82" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C78" s="22" t="s"/>
-      <x:c r="D78" s="22" t="s"/>
-      <x:c r="E78" s="22" t="s"/>
-      <x:c r="F78" s="23" t="s">
+      <x:c r="C82" s="22" t="s"/>
+      <x:c r="D82" s="22" t="s"/>
+      <x:c r="E82" s="22" t="s"/>
+      <x:c r="F82" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B79" s="24" t="s">
+    <x:row r="83" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B83" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C79" s="25" t="s"/>
-      <x:c r="D79" s="25" t="s"/>
-      <x:c r="E79" s="25" t="s"/>
-      <x:c r="F79" s="26" t="n">
+      <x:c r="C83" s="25" t="s"/>
+      <x:c r="D83" s="25" t="s"/>
+      <x:c r="E83" s="25" t="s"/>
+      <x:c r="F83" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B80" s="24" t="s">
+    <x:row r="84" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B84" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C80" s="25" t="s"/>
-      <x:c r="D80" s="25" t="s"/>
-      <x:c r="E80" s="25" t="s"/>
-      <x:c r="F80" s="26" t="n">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B81" s="27" t="s">
+      <x:c r="C84" s="25" t="s"/>
+      <x:c r="D84" s="25" t="s"/>
+      <x:c r="E84" s="25" t="s"/>
+      <x:c r="F84" s="26" t="n">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B85" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C81" s="28" t="s"/>
-      <x:c r="D81" s="28" t="s"/>
-      <x:c r="E81" s="28" t="s"/>
-      <x:c r="F81" s="29" t="n">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C85" s="28" t="s"/>
+      <x:c r="D85" s="28" t="s"/>
+      <x:c r="E85" s="28" t="s"/>
+      <x:c r="F85" s="29" t="n">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
     <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7756,11 +7937,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B77:F77"/>
-    <x:mergeCell ref="B78:E78"/>
-    <x:mergeCell ref="B79:E79"/>
-    <x:mergeCell ref="B80:E80"/>
-    <x:mergeCell ref="B81:E81"/>
+    <x:mergeCell ref="B81:F81"/>
+    <x:mergeCell ref="B82:E82"/>
+    <x:mergeCell ref="B83:E83"/>
+    <x:mergeCell ref="B84:E84"/>
+    <x:mergeCell ref="B85:E85"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="227">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -149,6 +149,78 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1326-920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1325-890</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdxzcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1324-430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wesdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1323-538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08292</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1322-790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1321-473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08219</x:t>
   </x:si>
   <x:si>
@@ -158,31 +230,226 @@
     <x:t>szdasdqweq</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08296</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1323-538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08292</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1322-790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08281</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1321-473</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08043</x:t>
@@ -194,121 +461,22 @@
     <x:t>123wqeasdzxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08153</x:t>
@@ -320,127 +488,205 @@
     <x:t>zxcasdadasdxasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08154</x:t>
@@ -449,154 +695,43 @@
     <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08181</x:t>
@@ -608,39 +743,6 @@
     <x:t>tesg213</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08175</x:t>
   </x:si>
   <x:si>
@@ -650,61 +752,10 @@
     <x:t>zcasdadqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4328,19 +4379,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46124.9835281713</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46125.0608962963</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="K9" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46126.1641622569</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -4366,10 +4417,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>46</x:v>
@@ -4378,7 +4429,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -4404,10 +4455,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>49</x:v>
@@ -4416,7 +4467,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -4442,10 +4493,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46126.4485157523</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46126.4527227431</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>52</x:v>
@@ -4454,7 +4505,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -4465,13 +4516,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="30" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D13" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E13" s="30" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F13" s="30" t="s">
         <x:v>53</x:v>
@@ -4480,10 +4531,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46126.4381590509</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46126.4434486343</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>55</x:v>
@@ -4492,7 +4543,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -4503,13 +4554,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="30" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D14" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="30" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
         <x:v>56</x:v>
@@ -4518,10 +4569,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>58</x:v>
@@ -4530,7 +4581,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -4541,13 +4592,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="30" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D15" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="30" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
         <x:v>59</x:v>
@@ -4556,10 +4607,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
         <x:v>61</x:v>
@@ -4568,7 +4619,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -4579,13 +4630,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="30" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D16" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E16" s="30" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
         <x:v>62</x:v>
@@ -4594,10 +4645,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
         <x:v>64</x:v>
@@ -4606,7 +4657,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -4617,13 +4668,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="30" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D17" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="30" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
         <x:v>65</x:v>
@@ -4632,19 +4683,19 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46124.9835281713</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46125.0608962963</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46126.1641622569</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -4670,10 +4721,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
         <x:v>70</x:v>
@@ -4682,7 +4733,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -4708,19 +4759,19 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -4740,25 +4791,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
+      <x:c r="H20" s="32">
+        <x:v>46120.2349196412</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>46120.5229746296</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="H20" s="32">
-        <x:v>46121.2273626852</x:v>
-      </x:c>
-      <x:c r="I20" s="32">
-        <x:v>46121.228379213</x:v>
-      </x:c>
-      <x:c r="J20" s="31" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="K20" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -4784,19 +4835,19 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -4816,25 +4867,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G22" s="30" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G22" s="30" t="s">
+      <x:c r="H22" s="32">
+        <x:v>46120.2374046412</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46120.5224942245</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="H22" s="32">
-        <x:v>46120.7129542245</x:v>
-      </x:c>
-      <x:c r="I22" s="32">
-        <x:v>46121.100944213</x:v>
-      </x:c>
-      <x:c r="J22" s="31" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -4860,19 +4911,19 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>83</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -4892,25 +4943,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G24" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G24" s="30" t="s">
+      <x:c r="H24" s="32">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I24" s="32">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="H24" s="32">
-        <x:v>46120.2362105324</x:v>
-      </x:c>
-      <x:c r="I24" s="32">
-        <x:v>46120.5226826273</x:v>
-      </x:c>
-      <x:c r="J24" s="31" t="s">
-        <x:v>86</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -4930,25 +4981,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G25" s="30" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G25" s="30" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="H25" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>86</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -4968,25 +5019,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G26" s="30" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G26" s="30" t="s">
+      <x:c r="H26" s="32">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I26" s="32">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="H26" s="32">
-        <x:v>46119.8029380671</x:v>
-      </x:c>
-      <x:c r="I26" s="32">
-        <x:v>46120.5237086343</x:v>
-      </x:c>
-      <x:c r="J26" s="31" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -5012,19 +5063,19 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>58</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -5044,10 +5095,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H28" s="32">
         <x:v>46119.8017436343</x:v>
@@ -5056,7 +5107,7 @@
         <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>52</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
@@ -5082,25 +5133,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G29" s="30" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -5120,25 +5171,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G30" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -5158,25 +5209,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>58</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -5196,25 +5247,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>52</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -5234,25 +5285,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -5272,25 +5323,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>110</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -5310,25 +5361,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>113</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -5354,10 +5405,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
         <x:v>116</x:v>
@@ -5366,7 +5417,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -5392,19 +5443,19 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>119</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -5424,25 +5475,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G38" s="30" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G38" s="30" t="s">
+      <x:c r="H38" s="32">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I38" s="32">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="H38" s="32">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I38" s="32">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J38" s="31" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -5468,10 +5519,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
         <x:v>124</x:v>
@@ -5480,7 +5531,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -5506,10 +5557,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
         <x:v>127</x:v>
@@ -5518,7 +5569,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -5544,19 +5595,19 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
-        <x:v>130</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -5576,25 +5627,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="30" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G42" s="30" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="G42" s="30" t="s">
+      <x:c r="H42" s="32">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I42" s="32">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J42" s="31" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="H42" s="32">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I42" s="32">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J42" s="31" t="s">
-        <x:v>133</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -5614,25 +5665,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F43" s="30" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G43" s="30" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="G43" s="30" t="s">
+      <x:c r="H43" s="32">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I43" s="32">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J43" s="31" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="H43" s="32">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I43" s="32">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J43" s="31" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -5652,25 +5703,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F44" s="30" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G44" s="30" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="G44" s="30" t="s">
+      <x:c r="H44" s="32">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I44" s="32">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J44" s="31" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="H44" s="32">
-        <x:v>46119.7297941435</x:v>
-      </x:c>
-      <x:c r="I44" s="32">
-        <x:v>46119.731450544</x:v>
-      </x:c>
-      <x:c r="J44" s="31" t="s">
-        <x:v>86</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -5696,19 +5747,19 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46122.244317963</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
-        <x:v>83</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K45" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -5728,25 +5779,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G46" s="30" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H46" s="32">
-        <x:v>46122.36782125</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
-        <x:v>58</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K46" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -5766,25 +5817,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="30" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G47" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H47" s="32">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I47" s="32">
-        <x:v>46124.704475463</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="K47" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -5804,25 +5855,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G48" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H48" s="32">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I48" s="32">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J48" s="31" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -5842,25 +5893,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F49" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G49" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H49" s="32">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I49" s="32">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J49" s="31" t="s">
-        <x:v>151</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="34">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M49" s="30" t="s">
         <x:v>21</x:v>
@@ -5880,25 +5931,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="30" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G50" s="30" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H50" s="32">
-        <x:v>46124.701771875</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I50" s="32">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>58</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
@@ -5918,25 +5969,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F51" s="30" t="s">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G51" s="30" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H51" s="32">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I51" s="32">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J51" s="31" t="s">
-        <x:v>156</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K51" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="34">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M51" s="30" t="s">
         <x:v>21</x:v>
@@ -5956,25 +6007,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F52" s="30" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G52" s="30" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H52" s="32">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I52" s="32">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J52" s="31" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="K52" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="34">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M52" s="30" t="s">
         <x:v>21</x:v>
@@ -5994,25 +6045,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="30" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G53" s="30" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H53" s="32">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I53" s="32">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -6032,25 +6083,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="30" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G54" s="30" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H54" s="32">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I54" s="32">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J54" s="31" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="K54" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -6070,25 +6121,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G55" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H55" s="32">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I55" s="32">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J55" s="31" t="s">
-        <x:v>168</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K55" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -6114,19 +6165,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="H56" s="32">
-        <x:v>46124.150742662</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I56" s="32">
-        <x:v>46124.153253125</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J56" s="31" t="s">
-        <x:v>86</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="K56" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
@@ -6146,25 +6197,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="30" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G57" s="30" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H57" s="32">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I57" s="32">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J57" s="31" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="K57" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="34">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M57" s="30" t="s">
         <x:v>21</x:v>
@@ -6184,25 +6235,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="30" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G58" s="30" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H58" s="32">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I58" s="32">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J58" s="31" t="s">
-        <x:v>86</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="K58" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="34">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M58" s="30" t="s">
         <x:v>21</x:v>
@@ -6222,25 +6273,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="30" t="s">
-        <x:v>176</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G59" s="30" t="s">
-        <x:v>177</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H59" s="32">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I59" s="32">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J59" s="31" t="s">
-        <x:v>178</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K59" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="34">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M59" s="30" t="s">
         <x:v>21</x:v>
@@ -6260,25 +6311,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="30" t="s">
-        <x:v>179</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G60" s="30" t="s">
-        <x:v>180</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H60" s="32">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I60" s="32">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J60" s="31" t="s">
-        <x:v>181</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="K60" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="34">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M60" s="30" t="s">
         <x:v>21</x:v>
@@ -6298,25 +6349,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F61" s="30" t="s">
-        <x:v>182</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G61" s="30" t="s">
-        <x:v>183</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H61" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I61" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J61" s="31" t="s">
-        <x:v>184</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K61" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M61" s="30" t="s">
         <x:v>21</x:v>
@@ -6336,25 +6387,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F62" s="30" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G62" s="30" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="H62" s="32">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I62" s="32">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J62" s="31" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="K62" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="34">
-        <x:v>46123.417862662</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M62" s="30" t="s">
         <x:v>21</x:v>
@@ -6374,25 +6425,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G63" s="30" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H63" s="32">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I63" s="32">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J63" s="31" t="s">
-        <x:v>190</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K63" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="34">
-        <x:v>46123.049084375</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M63" s="30" t="s">
         <x:v>21</x:v>
@@ -6418,10 +6469,10 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H64" s="32">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I64" s="32">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J64" s="31" t="s">
         <x:v>193</x:v>
@@ -6430,7 +6481,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="34">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M64" s="30" t="s">
         <x:v>21</x:v>
@@ -6456,19 +6507,19 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="H65" s="32">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I65" s="32">
-        <x:v>46122.727234375</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J65" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="K65" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="34">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M65" s="30" t="s">
         <x:v>21</x:v>
@@ -6488,25 +6539,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="30" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G66" s="30" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H66" s="32">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I66" s="32">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J66" s="31" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="K66" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="34">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M66" s="30" t="s">
         <x:v>21</x:v>
@@ -6526,25 +6577,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="30" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G67" s="30" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="H67" s="32">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I67" s="32">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J67" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="K67" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="34">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M67" s="30" t="s">
         <x:v>21</x:v>
@@ -6564,25 +6615,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="30" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G68" s="30" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="H68" s="32">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I68" s="32">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J68" s="31" t="s">
-        <x:v>86</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="K68" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="34">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M68" s="30" t="s">
         <x:v>21</x:v>
@@ -6602,25 +6653,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="30" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G69" s="30" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H69" s="32">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I69" s="32">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J69" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K69" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="34">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M69" s="30" t="s">
         <x:v>21</x:v>
@@ -6640,25 +6691,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="30" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G70" s="30" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H70" s="32">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I70" s="32">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J70" s="31" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="K70" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="34">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M70" s="30" t="s">
         <x:v>21</x:v>
@@ -6678,25 +6729,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="30" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G71" s="30" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H71" s="32">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I71" s="32">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J71" s="31" t="s">
-        <x:v>119</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K71" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M71" s="30" t="s">
         <x:v>21</x:v>
@@ -6716,25 +6767,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="30" t="s">
-        <x:v>210</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G72" s="30" t="s">
-        <x:v>211</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H72" s="32">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I72" s="32">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J72" s="31" t="s">
-        <x:v>212</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K72" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M72" s="30" t="s">
         <x:v>21</x:v>
@@ -6754,10 +6805,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F73" s="30" t="s">
-        <x:v>213</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="G73" s="30" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="H73" s="32">
         <x:v>46122.3974322338</x:v>
@@ -6766,7 +6817,7 @@
         <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J73" s="31" t="s">
-        <x:v>86</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K73" s="33" t="n">
         <x:v>210</x:v>
@@ -6792,25 +6843,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F74" s="30" t="s">
-        <x:v>215</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G74" s="30" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H74" s="32">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I74" s="32">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J74" s="31" t="s">
-        <x:v>58</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="K74" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="34">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M74" s="30" t="s">
         <x:v>21</x:v>
@@ -6830,25 +6881,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F75" s="30" t="s">
-        <x:v>217</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="G75" s="30" t="s">
-        <x:v>218</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H75" s="32">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I75" s="32">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J75" s="31" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K75" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="34">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M75" s="30" t="s">
         <x:v>21</x:v>
@@ -6868,25 +6919,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F76" s="30" t="s">
-        <x:v>219</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G76" s="30" t="s">
-        <x:v>220</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H76" s="32">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I76" s="32">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J76" s="31" t="s">
-        <x:v>221</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K76" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="34">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M76" s="30" t="s">
         <x:v>21</x:v>
@@ -6906,25 +6957,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F77" s="30" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="G77" s="30" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="H77" s="32">
-        <x:v>46123.061368912</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I77" s="32">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J77" s="31" t="s">
-        <x:v>224</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K77" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="34">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M77" s="30" t="s">
         <x:v>21</x:v>
@@ -6944,91 +6995,313 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F78" s="30" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G78" s="30" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H78" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I78" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J78" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K78" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M78" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B79" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C79" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D79" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E79" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F79" s="30" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G79" s="30" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="H79" s="32">
+        <x:v>46122.6795081481</x:v>
+      </x:c>
+      <x:c r="I79" s="32">
+        <x:v>46122.6802186921</x:v>
+      </x:c>
+      <x:c r="J79" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K79" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L79" s="34">
+        <x:v>46122.6809879398</x:v>
+      </x:c>
+      <x:c r="M79" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B80" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C80" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D80" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E80" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F80" s="30" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G80" s="30" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H80" s="32">
+        <x:v>46122.6819179514</x:v>
+      </x:c>
+      <x:c r="I80" s="32">
+        <x:v>46122.6826717361</x:v>
+      </x:c>
+      <x:c r="J80" s="31" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="K80" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L80" s="34">
+        <x:v>46122.6831438079</x:v>
+      </x:c>
+      <x:c r="M80" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="81" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B81" s="18" t="s">
+      <x:c r="B81" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C81" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D81" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E81" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F81" s="30" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G81" s="30" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="H81" s="32">
+        <x:v>46122.7261372338</x:v>
+      </x:c>
+      <x:c r="I81" s="32">
+        <x:v>46122.727234375</x:v>
+      </x:c>
+      <x:c r="J81" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K81" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L81" s="34">
+        <x:v>46122.7277720023</x:v>
+      </x:c>
+      <x:c r="M81" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B82" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C82" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D82" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E82" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F82" s="30" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G82" s="30" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="H82" s="32">
+        <x:v>46122.9452935995</x:v>
+      </x:c>
+      <x:c r="I82" s="32">
+        <x:v>46123.0460683681</x:v>
+      </x:c>
+      <x:c r="J82" s="31" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="K82" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L82" s="34">
+        <x:v>46123.0466478819</x:v>
+      </x:c>
+      <x:c r="M82" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B83" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C83" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D83" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E83" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F83" s="30" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G83" s="30" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H83" s="32">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I83" s="32">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J83" s="31" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="K83" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L83" s="34">
+        <x:v>46122.5928339699</x:v>
+      </x:c>
+      <x:c r="M83" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B84" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C84" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D84" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E84" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F84" s="30" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G84" s="30" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H84" s="32">
+        <x:v>46126.5341923727</x:v>
+      </x:c>
+      <x:c r="I84" s="32">
+        <x:v>46126.5348242708</x:v>
+      </x:c>
+      <x:c r="J84" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K84" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L84" s="34">
+        <x:v>46126.5353594213</x:v>
+      </x:c>
+      <x:c r="M84" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B87" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C81" s="19" t="s"/>
-      <x:c r="D81" s="19" t="s"/>
-      <x:c r="E81" s="20" t="s"/>
-      <x:c r="F81" s="20" t="s"/>
-    </x:row>
-    <x:row r="82" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B82" s="21" t="s">
+      <x:c r="C87" s="19" t="s"/>
+      <x:c r="D87" s="19" t="s"/>
+      <x:c r="E87" s="20" t="s"/>
+      <x:c r="F87" s="20" t="s"/>
+    </x:row>
+    <x:row r="88" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B88" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C82" s="22" t="s"/>
-      <x:c r="D82" s="22" t="s"/>
-      <x:c r="E82" s="22" t="s"/>
-      <x:c r="F82" s="23" t="s">
+      <x:c r="C88" s="22" t="s"/>
+      <x:c r="D88" s="22" t="s"/>
+      <x:c r="E88" s="22" t="s"/>
+      <x:c r="F88" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B83" s="24" t="s">
+    <x:row r="89" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B89" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C83" s="25" t="s"/>
-      <x:c r="D83" s="25" t="s"/>
-      <x:c r="E83" s="25" t="s"/>
-      <x:c r="F83" s="26" t="n">
+      <x:c r="C89" s="25" t="s"/>
+      <x:c r="D89" s="25" t="s"/>
+      <x:c r="E89" s="25" t="s"/>
+      <x:c r="F89" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B84" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C84" s="25" t="s"/>
-      <x:c r="D84" s="25" t="s"/>
-      <x:c r="E84" s="25" t="s"/>
-      <x:c r="F84" s="26" t="n">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B85" s="27" t="s">
+    <x:row r="90" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B90" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C90" s="25" t="s"/>
+      <x:c r="D90" s="25" t="s"/>
+      <x:c r="E90" s="25" t="s"/>
+      <x:c r="F90" s="26" t="n">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B91" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C85" s="28" t="s"/>
-      <x:c r="D85" s="28" t="s"/>
-      <x:c r="E85" s="28" t="s"/>
-      <x:c r="F85" s="29" t="n">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C91" s="28" t="s"/>
+      <x:c r="D91" s="28" t="s"/>
+      <x:c r="E91" s="28" t="s"/>
+      <x:c r="F91" s="29" t="n">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
     <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7937,11 +8210,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B81:F81"/>
-    <x:mergeCell ref="B82:E82"/>
-    <x:mergeCell ref="B83:E83"/>
-    <x:mergeCell ref="B84:E84"/>
-    <x:mergeCell ref="B85:E85"/>
+    <x:mergeCell ref="B87:F87"/>
+    <x:mergeCell ref="B88:E88"/>
+    <x:mergeCell ref="B89:E89"/>
+    <x:mergeCell ref="B90:E90"/>
+    <x:mergeCell ref="B91:E91"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="246">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -230,58 +230,109 @@
     <x:t>szdasdqweq</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
-    <x:t>zxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08137</x:t>
@@ -290,55 +341,82 @@
     <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08098</x:t>
@@ -347,6 +425,30 @@
     <x:t>61-4-2026-1249-913</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08093</x:t>
   </x:si>
   <x:si>
@@ -356,51 +458,27 @@
     <x:t>zcx</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08096</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
   </x:si>
   <x:si>
@@ -410,82 +488,172 @@
     <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08168</x:t>
@@ -494,145 +662,85 @@
     <x:t>61-4-2026-1282-165</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08160</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1279-279</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08182</x:t>
@@ -644,118 +752,16 @@
     <x:t>sdasqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08176</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1288-384</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4721,10 +4727,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
         <x:v>70</x:v>
@@ -4733,7 +4739,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -4759,19 +4765,19 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -4791,25 +4797,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H20" s="32">
+        <x:v>46120.2362105324</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>46120.5226826273</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H20" s="32">
-        <x:v>46120.2349196412</x:v>
-      </x:c>
-      <x:c r="I20" s="32">
-        <x:v>46120.5229746296</x:v>
-      </x:c>
-      <x:c r="J20" s="31" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="K20" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -4835,19 +4841,19 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -4867,25 +4873,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>80</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -4911,19 +4917,19 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -4943,25 +4949,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G24" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -4981,25 +4987,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G25" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -5019,25 +5025,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -5057,25 +5063,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G27" s="30" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -5095,25 +5101,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>64</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -5133,25 +5139,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G29" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -5171,25 +5177,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G30" s="30" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>101</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -5209,25 +5215,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>104</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -5253,19 +5259,19 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -5291,10 +5297,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
         <x:v>109</x:v>
@@ -5303,7 +5309,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -5329,19 +5335,19 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>70</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -5361,25 +5367,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>64</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -5399,25 +5405,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G36" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -5437,25 +5443,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G37" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>70</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -5475,25 +5481,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G38" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H38" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I38" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -5513,25 +5519,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F39" s="30" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G39" s="30" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -5551,25 +5557,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F40" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G40" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -5589,25 +5595,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F41" s="30" t="s">
-        <x:v>128</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G41" s="30" t="s">
-        <x:v>129</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -5627,25 +5633,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="30" t="s">
-        <x:v>130</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G42" s="30" t="s">
-        <x:v>131</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
-        <x:v>132</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -5665,25 +5671,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F43" s="30" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G43" s="30" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -5703,25 +5709,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F44" s="30" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G44" s="30" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -5741,25 +5747,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F45" s="30" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G45" s="30" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="K45" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -5779,25 +5785,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="30" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G46" s="30" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H46" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K46" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -5817,25 +5823,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="30" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G47" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="H47" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I47" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
-        <x:v>147</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K47" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -5855,25 +5861,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="30" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G48" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H48" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I48" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J48" s="31" t="s">
-        <x:v>150</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -5899,10 +5905,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="H49" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I49" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J49" s="31" t="s">
         <x:v>153</x:v>
@@ -5911,7 +5917,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M49" s="30" t="s">
         <x:v>21</x:v>
@@ -5937,19 +5943,19 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="H50" s="32">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I50" s="32">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
@@ -5975,19 +5981,19 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="H51" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I51" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J51" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K51" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M51" s="30" t="s">
         <x:v>21</x:v>
@@ -6013,19 +6019,19 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="H52" s="32">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I52" s="32">
-        <x:v>46124.704475463</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J52" s="31" t="s">
-        <x:v>160</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K52" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="34">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M52" s="30" t="s">
         <x:v>21</x:v>
@@ -6045,25 +6051,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="30" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G53" s="30" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="G53" s="30" t="s">
-        <x:v>162</x:v>
-      </x:c>
       <x:c r="H53" s="32">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I53" s="32">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>163</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -6083,25 +6089,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="30" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G54" s="30" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H54" s="32">
+        <x:v>46124.7035032407</x:v>
+      </x:c>
+      <x:c r="I54" s="32">
+        <x:v>46124.704475463</x:v>
+      </x:c>
+      <x:c r="J54" s="31" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="G54" s="30" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="H54" s="32">
-        <x:v>46124.7023532986</x:v>
-      </x:c>
-      <x:c r="I54" s="32">
-        <x:v>46124.7048005093</x:v>
-      </x:c>
-      <x:c r="J54" s="31" t="s">
-        <x:v>166</x:v>
       </x:c>
       <x:c r="K54" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -6121,25 +6127,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="30" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G55" s="30" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H55" s="32">
+        <x:v>46124.7029179398</x:v>
+      </x:c>
+      <x:c r="I55" s="32">
+        <x:v>46124.7046092014</x:v>
+      </x:c>
+      <x:c r="J55" s="31" t="s">
         <x:v>167</x:v>
-      </x:c>
-      <x:c r="G55" s="30" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="H55" s="32">
-        <x:v>46124.701771875</x:v>
-      </x:c>
-      <x:c r="I55" s="32">
-        <x:v>46124.7049218519</x:v>
-      </x:c>
-      <x:c r="J55" s="31" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="K55" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -6159,25 +6165,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="30" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G56" s="30" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="G56" s="30" t="s">
+      <x:c r="H56" s="32">
+        <x:v>46124.7023532986</x:v>
+      </x:c>
+      <x:c r="I56" s="32">
+        <x:v>46124.7048005093</x:v>
+      </x:c>
+      <x:c r="J56" s="31" t="s">
         <x:v>170</x:v>
-      </x:c>
-      <x:c r="H56" s="32">
-        <x:v>46124.6975491551</x:v>
-      </x:c>
-      <x:c r="I56" s="32">
-        <x:v>46124.6983328357</x:v>
-      </x:c>
-      <x:c r="J56" s="31" t="s">
-        <x:v>171</x:v>
       </x:c>
       <x:c r="K56" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
@@ -6197,25 +6203,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="30" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G57" s="30" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="G57" s="30" t="s">
-        <x:v>173</x:v>
-      </x:c>
       <x:c r="H57" s="32">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I57" s="32">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J57" s="31" t="s">
-        <x:v>174</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K57" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="34">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M57" s="30" t="s">
         <x:v>21</x:v>
@@ -6235,25 +6241,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G58" s="30" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H58" s="32">
+        <x:v>46124.6975491551</x:v>
+      </x:c>
+      <x:c r="I58" s="32">
+        <x:v>46124.6983328357</x:v>
+      </x:c>
+      <x:c r="J58" s="31" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="G58" s="30" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="H58" s="32">
-        <x:v>46124.5490358102</x:v>
-      </x:c>
-      <x:c r="I58" s="32">
-        <x:v>46124.6984689583</x:v>
-      </x:c>
-      <x:c r="J58" s="31" t="s">
-        <x:v>177</x:v>
       </x:c>
       <x:c r="K58" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="34">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M58" s="30" t="s">
         <x:v>21</x:v>
@@ -6273,25 +6279,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="30" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G59" s="30" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H59" s="32">
+        <x:v>46124.6761778356</x:v>
+      </x:c>
+      <x:c r="I59" s="32">
+        <x:v>46124.6772295602</x:v>
+      </x:c>
+      <x:c r="J59" s="31" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="G59" s="30" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="H59" s="32">
-        <x:v>46124.1518079282</x:v>
-      </x:c>
-      <x:c r="I59" s="32">
-        <x:v>46124.1529164583</x:v>
-      </x:c>
-      <x:c r="J59" s="31" t="s">
-        <x:v>180</x:v>
       </x:c>
       <x:c r="K59" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="34">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M59" s="30" t="s">
         <x:v>21</x:v>
@@ -6311,25 +6317,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="30" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G60" s="30" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H60" s="32">
+        <x:v>46124.5490358102</x:v>
+      </x:c>
+      <x:c r="I60" s="32">
+        <x:v>46124.6984689583</x:v>
+      </x:c>
+      <x:c r="J60" s="31" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="G60" s="30" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="H60" s="32">
-        <x:v>46124.1512647338</x:v>
-      </x:c>
-      <x:c r="I60" s="32">
-        <x:v>46124.1530803935</x:v>
-      </x:c>
-      <x:c r="J60" s="31" t="s">
-        <x:v>183</x:v>
       </x:c>
       <x:c r="K60" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="34">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M60" s="30" t="s">
         <x:v>21</x:v>
@@ -6349,25 +6355,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F61" s="30" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G61" s="30" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H61" s="32">
+        <x:v>46124.1518079282</x:v>
+      </x:c>
+      <x:c r="I61" s="32">
+        <x:v>46124.1529164583</x:v>
+      </x:c>
+      <x:c r="J61" s="31" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="G61" s="30" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H61" s="32">
-        <x:v>46124.150742662</x:v>
-      </x:c>
-      <x:c r="I61" s="32">
-        <x:v>46124.153253125</x:v>
-      </x:c>
-      <x:c r="J61" s="31" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="K61" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="34">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M61" s="30" t="s">
         <x:v>21</x:v>
@@ -6387,25 +6393,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F62" s="30" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G62" s="30" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="G62" s="30" t="s">
+      <x:c r="H62" s="32">
+        <x:v>46124.1512647338</x:v>
+      </x:c>
+      <x:c r="I62" s="32">
+        <x:v>46124.1530803935</x:v>
+      </x:c>
+      <x:c r="J62" s="31" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="H62" s="32">
-        <x:v>46124.1487218981</x:v>
-      </x:c>
-      <x:c r="I62" s="32">
-        <x:v>46124.1494313773</x:v>
-      </x:c>
-      <x:c r="J62" s="31" t="s">
-        <x:v>188</x:v>
       </x:c>
       <x:c r="K62" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="34">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M62" s="30" t="s">
         <x:v>21</x:v>
@@ -6425,25 +6431,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="30" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G63" s="30" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="G63" s="30" t="s">
-        <x:v>190</x:v>
-      </x:c>
       <x:c r="H63" s="32">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I63" s="32">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J63" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K63" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="34">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M63" s="30" t="s">
         <x:v>21</x:v>
@@ -6463,25 +6469,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="30" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G64" s="30" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="G64" s="30" t="s">
+      <x:c r="H64" s="32">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I64" s="32">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J64" s="31" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="H64" s="32">
-        <x:v>46124.1410094907</x:v>
-      </x:c>
-      <x:c r="I64" s="32">
-        <x:v>46124.1426461806</x:v>
-      </x:c>
-      <x:c r="J64" s="31" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="K64" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="34">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M64" s="30" t="s">
         <x:v>21</x:v>
@@ -6501,25 +6507,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F65" s="30" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G65" s="30" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="G65" s="30" t="s">
-        <x:v>195</x:v>
-      </x:c>
       <x:c r="H65" s="32">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I65" s="32">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J65" s="31" t="s">
-        <x:v>196</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K65" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="34">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M65" s="30" t="s">
         <x:v>21</x:v>
@@ -6539,25 +6545,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="30" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G66" s="30" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H66" s="32">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I66" s="32">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J66" s="31" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="G66" s="30" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="H66" s="32">
-        <x:v>46123.4162791088</x:v>
-      </x:c>
-      <x:c r="I66" s="32">
-        <x:v>46123.4173169792</x:v>
-      </x:c>
-      <x:c r="J66" s="31" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="K66" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="34">
-        <x:v>46123.417862662</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M66" s="30" t="s">
         <x:v>21</x:v>
@@ -6577,25 +6583,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="30" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="G67" s="30" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="H67" s="32">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I67" s="32">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J67" s="31" t="s">
         <x:v>200</x:v>
-      </x:c>
-      <x:c r="G67" s="30" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H67" s="32">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I67" s="32">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J67" s="31" t="s">
-        <x:v>202</x:v>
       </x:c>
       <x:c r="K67" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="34">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M67" s="30" t="s">
         <x:v>21</x:v>
@@ -6615,25 +6621,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="30" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G68" s="30" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="H68" s="32">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I68" s="32">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J68" s="31" t="s">
         <x:v>203</x:v>
-      </x:c>
-      <x:c r="G68" s="30" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="H68" s="32">
-        <x:v>46123.0476912847</x:v>
-      </x:c>
-      <x:c r="I68" s="32">
-        <x:v>46123.0484775694</x:v>
-      </x:c>
-      <x:c r="J68" s="31" t="s">
-        <x:v>205</x:v>
       </x:c>
       <x:c r="K68" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="34">
-        <x:v>46123.049084375</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M68" s="30" t="s">
         <x:v>21</x:v>
@@ -6653,25 +6659,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="30" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G69" s="30" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H69" s="32">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I69" s="32">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J69" s="31" t="s">
         <x:v>206</x:v>
-      </x:c>
-      <x:c r="G69" s="30" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="H69" s="32">
-        <x:v>46122.36782125</x:v>
-      </x:c>
-      <x:c r="I69" s="32">
-        <x:v>46122.3686719907</x:v>
-      </x:c>
-      <x:c r="J69" s="31" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="K69" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M69" s="30" t="s">
         <x:v>21</x:v>
@@ -6691,10 +6697,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="30" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G70" s="30" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="G70" s="30" t="s">
-        <x:v>209</x:v>
       </x:c>
       <x:c r="H70" s="32">
         <x:v>46122.3767795718</x:v>
@@ -6703,7 +6709,7 @@
         <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J70" s="31" t="s">
-        <x:v>210</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="K70" s="33" t="n">
         <x:v>210</x:v>
@@ -6729,25 +6735,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="30" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G71" s="30" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="G71" s="30" t="s">
-        <x:v>212</x:v>
-      </x:c>
       <x:c r="H71" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I71" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J71" s="31" t="s">
-        <x:v>213</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K71" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M71" s="30" t="s">
         <x:v>21</x:v>
@@ -6767,25 +6773,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="30" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G72" s="30" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H72" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I72" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J72" s="31" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="G72" s="30" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H72" s="32">
-        <x:v>46122.3885020718</x:v>
-      </x:c>
-      <x:c r="I72" s="32">
-        <x:v>46122.3892655903</x:v>
-      </x:c>
-      <x:c r="J72" s="31" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="K72" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="34">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M72" s="30" t="s">
         <x:v>21</x:v>
@@ -6805,10 +6811,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F73" s="30" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G73" s="30" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="G73" s="30" t="s">
-        <x:v>217</x:v>
       </x:c>
       <x:c r="H73" s="32">
         <x:v>46122.3974322338</x:v>
@@ -6817,7 +6823,7 @@
         <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J73" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K73" s="33" t="n">
         <x:v>210</x:v>
@@ -6843,10 +6849,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F74" s="30" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G74" s="30" t="s">
         <x:v>218</x:v>
-      </x:c>
-      <x:c r="G74" s="30" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="H74" s="32">
         <x:v>46122.5587807523</x:v>
@@ -6855,7 +6861,7 @@
         <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J74" s="31" t="s">
-        <x:v>220</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="K74" s="33" t="n">
         <x:v>210</x:v>
@@ -6881,25 +6887,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F75" s="30" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G75" s="30" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="G75" s="30" t="s">
-        <x:v>222</x:v>
-      </x:c>
       <x:c r="H75" s="32">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I75" s="32">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J75" s="31" t="s">
-        <x:v>80</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K75" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M75" s="30" t="s">
         <x:v>21</x:v>
@@ -6919,25 +6925,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F76" s="30" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G76" s="30" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G76" s="30" t="s">
-        <x:v>224</x:v>
-      </x:c>
       <x:c r="H76" s="32">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I76" s="32">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J76" s="31" t="s">
-        <x:v>127</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K76" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M76" s="30" t="s">
         <x:v>21</x:v>
@@ -6957,25 +6963,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F77" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G77" s="30" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="G77" s="30" t="s">
+      <x:c r="H77" s="32">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I77" s="32">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J77" s="31" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="H77" s="32">
-        <x:v>46122.5945434491</x:v>
-      </x:c>
-      <x:c r="I77" s="32">
-        <x:v>46122.5999534606</x:v>
-      </x:c>
-      <x:c r="J77" s="31" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K77" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="34">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M77" s="30" t="s">
         <x:v>21</x:v>
@@ -7007,7 +7013,7 @@
         <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J78" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K78" s="33" t="n">
         <x:v>210</x:v>
@@ -7191,10 +7197,10 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="H83" s="32">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I83" s="32">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J83" s="31" t="s">
         <x:v>241</x:v>
@@ -7203,7 +7209,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="34">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M83" s="30" t="s">
         <x:v>21</x:v>
@@ -7229,10 +7235,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="H84" s="32">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I84" s="32">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J84" s="31" t="s">
         <x:v>28</x:v>
@@ -7241,68 +7247,105 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="34">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M84" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B85" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C85" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D85" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E85" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F85" s="30" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G85" s="30" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H85" s="32">
+        <x:v>46127.1221474769</x:v>
+      </x:c>
+      <x:c r="I85" s="32">
+        <x:v>46127.1231965625</x:v>
+      </x:c>
+      <x:c r="J85" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K85" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L85" s="34">
+        <x:v>46128.1095700579</x:v>
+      </x:c>
+      <x:c r="M85" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="87" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B87" s="18" t="s">
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B88" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C87" s="19" t="s"/>
-      <x:c r="D87" s="19" t="s"/>
-      <x:c r="E87" s="20" t="s"/>
-      <x:c r="F87" s="20" t="s"/>
-    </x:row>
-    <x:row r="88" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B88" s="21" t="s">
+      <x:c r="C88" s="19" t="s"/>
+      <x:c r="D88" s="19" t="s"/>
+      <x:c r="E88" s="20" t="s"/>
+      <x:c r="F88" s="20" t="s"/>
+    </x:row>
+    <x:row r="89" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B89" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C88" s="22" t="s"/>
-      <x:c r="D88" s="22" t="s"/>
-      <x:c r="E88" s="22" t="s"/>
-      <x:c r="F88" s="23" t="s">
+      <x:c r="C89" s="22" t="s"/>
+      <x:c r="D89" s="22" t="s"/>
+      <x:c r="E89" s="22" t="s"/>
+      <x:c r="F89" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B89" s="24" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C89" s="25" t="s"/>
-      <x:c r="D89" s="25" t="s"/>
-      <x:c r="E89" s="25" t="s"/>
-      <x:c r="F89" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:28" ht="18" customHeight="1">
       <x:c r="B90" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C90" s="25" t="s"/>
       <x:c r="D90" s="25" t="s"/>
       <x:c r="E90" s="25" t="s"/>
       <x:c r="F90" s="26" t="n">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B91" s="27" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B91" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C91" s="25" t="s"/>
+      <x:c r="D91" s="25" t="s"/>
+      <x:c r="E91" s="25" t="s"/>
+      <x:c r="F91" s="26" t="n">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B92" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C91" s="28" t="s"/>
-      <x:c r="D91" s="28" t="s"/>
-      <x:c r="E91" s="28" t="s"/>
-      <x:c r="F91" s="29" t="n">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C92" s="28" t="s"/>
+      <x:c r="D92" s="28" t="s"/>
+      <x:c r="E92" s="28" t="s"/>
+      <x:c r="F92" s="29" t="n">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
     <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8210,11 +8253,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B87:F87"/>
-    <x:mergeCell ref="B88:E88"/>
+    <x:mergeCell ref="B88:F88"/>
     <x:mergeCell ref="B89:E89"/>
     <x:mergeCell ref="B90:E90"/>
     <x:mergeCell ref="B91:E91"/>
+    <x:mergeCell ref="B92:E92"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="246">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="248">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -506,43 +506,115 @@
     <x:t>61-4-2026-1280-364</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08344</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1332-041</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08211</x:t>
@@ -554,70 +626,10 @@
     <x:t>zcasdqwedszxczxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08185</x:t>
@@ -629,6 +641,60 @@
     <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08184</x:t>
   </x:si>
   <x:si>
@@ -638,66 +704,6 @@
     <x:t>test12</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08175</x:t>
   </x:si>
   <x:si>
@@ -758,10 +764,10 @@
     <x:t>61-4-2026-1288-384</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -6057,19 +6063,19 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="H53" s="32">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I53" s="32">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -6095,10 +6101,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="H54" s="32">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I54" s="32">
-        <x:v>46124.704475463</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J54" s="31" t="s">
         <x:v>164</x:v>
@@ -6107,7 +6113,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -6133,19 +6139,19 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="H55" s="32">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I55" s="32">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J55" s="31" t="s">
-        <x:v>167</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K55" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -6165,25 +6171,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="30" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G56" s="30" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G56" s="30" t="s">
+      <x:c r="H56" s="32">
+        <x:v>46124.1512647338</x:v>
+      </x:c>
+      <x:c r="I56" s="32">
+        <x:v>46124.1530803935</x:v>
+      </x:c>
+      <x:c r="J56" s="31" t="s">
         <x:v>169</x:v>
-      </x:c>
-      <x:c r="H56" s="32">
-        <x:v>46124.7023532986</x:v>
-      </x:c>
-      <x:c r="I56" s="32">
-        <x:v>46124.7048005093</x:v>
-      </x:c>
-      <x:c r="J56" s="31" t="s">
-        <x:v>170</x:v>
       </x:c>
       <x:c r="K56" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
@@ -6203,25 +6209,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="30" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G57" s="30" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="G57" s="30" t="s">
+      <x:c r="H57" s="32">
+        <x:v>46124.1518079282</x:v>
+      </x:c>
+      <x:c r="I57" s="32">
+        <x:v>46124.1529164583</x:v>
+      </x:c>
+      <x:c r="J57" s="31" t="s">
         <x:v>172</x:v>
-      </x:c>
-      <x:c r="H57" s="32">
-        <x:v>46124.701771875</x:v>
-      </x:c>
-      <x:c r="I57" s="32">
-        <x:v>46124.7049218519</x:v>
-      </x:c>
-      <x:c r="J57" s="31" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="K57" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="34">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M57" s="30" t="s">
         <x:v>21</x:v>
@@ -6247,10 +6253,10 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="H58" s="32">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I58" s="32">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J58" s="31" t="s">
         <x:v>175</x:v>
@@ -6259,7 +6265,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="34">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M58" s="30" t="s">
         <x:v>21</x:v>
@@ -6285,10 +6291,10 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="H59" s="32">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I59" s="32">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J59" s="31" t="s">
         <x:v>178</x:v>
@@ -6297,7 +6303,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="34">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M59" s="30" t="s">
         <x:v>21</x:v>
@@ -6323,10 +6329,10 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="H60" s="32">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I60" s="32">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J60" s="31" t="s">
         <x:v>181</x:v>
@@ -6335,7 +6341,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="34">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M60" s="30" t="s">
         <x:v>21</x:v>
@@ -6361,19 +6367,19 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="H61" s="32">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I61" s="32">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J61" s="31" t="s">
-        <x:v>184</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K61" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="34">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M61" s="30" t="s">
         <x:v>21</x:v>
@@ -6393,25 +6399,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F62" s="30" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G62" s="30" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="G62" s="30" t="s">
+      <x:c r="H62" s="32">
+        <x:v>46124.7023532986</x:v>
+      </x:c>
+      <x:c r="I62" s="32">
+        <x:v>46124.7048005093</x:v>
+      </x:c>
+      <x:c r="J62" s="31" t="s">
         <x:v>186</x:v>
-      </x:c>
-      <x:c r="H62" s="32">
-        <x:v>46124.1512647338</x:v>
-      </x:c>
-      <x:c r="I62" s="32">
-        <x:v>46124.1530803935</x:v>
-      </x:c>
-      <x:c r="J62" s="31" t="s">
-        <x:v>187</x:v>
       </x:c>
       <x:c r="K62" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="34">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M62" s="30" t="s">
         <x:v>21</x:v>
@@ -6431,25 +6437,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="30" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G63" s="30" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G63" s="30" t="s">
+      <x:c r="H63" s="32">
+        <x:v>46124.7029179398</x:v>
+      </x:c>
+      <x:c r="I63" s="32">
+        <x:v>46124.7046092014</x:v>
+      </x:c>
+      <x:c r="J63" s="31" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="H63" s="32">
-        <x:v>46124.150742662</x:v>
-      </x:c>
-      <x:c r="I63" s="32">
-        <x:v>46124.153253125</x:v>
-      </x:c>
-      <x:c r="J63" s="31" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="K63" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="34">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M63" s="30" t="s">
         <x:v>21</x:v>
@@ -6475,10 +6481,10 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="H64" s="32">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I64" s="32">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J64" s="31" t="s">
         <x:v>192</x:v>
@@ -6487,7 +6493,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="34">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M64" s="30" t="s">
         <x:v>21</x:v>
@@ -6513,19 +6519,19 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="H65" s="32">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I65" s="32">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J65" s="31" t="s">
-        <x:v>73</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K65" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="34">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M65" s="30" t="s">
         <x:v>21</x:v>
@@ -6551,19 +6557,19 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="H66" s="32">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I66" s="32">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J66" s="31" t="s">
-        <x:v>197</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K66" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="34">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M66" s="30" t="s">
         <x:v>21</x:v>
@@ -6583,25 +6589,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="30" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G67" s="30" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="G67" s="30" t="s">
+      <x:c r="H67" s="32">
+        <x:v>46124.6975491551</x:v>
+      </x:c>
+      <x:c r="I67" s="32">
+        <x:v>46124.6983328357</x:v>
+      </x:c>
+      <x:c r="J67" s="31" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="H67" s="32">
-        <x:v>46123.4191184375</x:v>
-      </x:c>
-      <x:c r="I67" s="32">
-        <x:v>46123.4205974074</x:v>
-      </x:c>
-      <x:c r="J67" s="31" t="s">
-        <x:v>200</x:v>
       </x:c>
       <x:c r="K67" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="34">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M67" s="30" t="s">
         <x:v>21</x:v>
@@ -6621,25 +6627,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="30" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G68" s="30" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="G68" s="30" t="s">
-        <x:v>202</x:v>
-      </x:c>
       <x:c r="H68" s="32">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I68" s="32">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J68" s="31" t="s">
-        <x:v>203</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K68" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="34">
-        <x:v>46123.417862662</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M68" s="30" t="s">
         <x:v>21</x:v>
@@ -6659,25 +6665,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="30" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G69" s="30" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H69" s="32">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I69" s="32">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J69" s="31" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="G69" s="30" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H69" s="32">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I69" s="32">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J69" s="31" t="s">
-        <x:v>206</x:v>
       </x:c>
       <x:c r="K69" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="34">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M69" s="30" t="s">
         <x:v>21</x:v>
@@ -6697,25 +6703,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="30" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G70" s="30" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H70" s="32">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I70" s="32">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J70" s="31" t="s">
         <x:v>207</x:v>
-      </x:c>
-      <x:c r="G70" s="30" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H70" s="32">
-        <x:v>46122.3767795718</x:v>
-      </x:c>
-      <x:c r="I70" s="32">
-        <x:v>46122.3776183449</x:v>
-      </x:c>
-      <x:c r="J70" s="31" t="s">
-        <x:v>209</x:v>
       </x:c>
       <x:c r="K70" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="34">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M70" s="30" t="s">
         <x:v>21</x:v>
@@ -6735,25 +6741,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="30" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G71" s="30" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H71" s="32">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I71" s="32">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J71" s="31" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="G71" s="30" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="H71" s="32">
-        <x:v>46122.3879258681</x:v>
-      </x:c>
-      <x:c r="I71" s="32">
-        <x:v>46122.3894281713</x:v>
-      </x:c>
-      <x:c r="J71" s="31" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="K71" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="34">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M71" s="30" t="s">
         <x:v>21</x:v>
@@ -6773,25 +6779,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="30" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G72" s="30" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="G72" s="30" t="s">
-        <x:v>213</x:v>
-      </x:c>
       <x:c r="H72" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I72" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J72" s="31" t="s">
-        <x:v>214</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K72" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M72" s="30" t="s">
         <x:v>21</x:v>
@@ -6811,25 +6817,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F73" s="30" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G73" s="30" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H73" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I73" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J73" s="31" t="s">
         <x:v>215</x:v>
-      </x:c>
-      <x:c r="G73" s="30" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H73" s="32">
-        <x:v>46122.3974322338</x:v>
-      </x:c>
-      <x:c r="I73" s="32">
-        <x:v>46122.3980999421</x:v>
-      </x:c>
-      <x:c r="J73" s="31" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="K73" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="34">
-        <x:v>46122.398526713</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M73" s="30" t="s">
         <x:v>21</x:v>
@@ -6849,25 +6855,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F74" s="30" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G74" s="30" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="G74" s="30" t="s">
-        <x:v>218</x:v>
-      </x:c>
       <x:c r="H74" s="32">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I74" s="32">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J74" s="31" t="s">
-        <x:v>219</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K74" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M74" s="30" t="s">
         <x:v>21</x:v>
@@ -6887,25 +6893,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F75" s="30" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G75" s="30" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H75" s="32">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I75" s="32">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J75" s="31" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="G75" s="30" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="H75" s="32">
-        <x:v>46122.5623107755</x:v>
-      </x:c>
-      <x:c r="I75" s="32">
-        <x:v>46122.5630093981</x:v>
-      </x:c>
-      <x:c r="J75" s="31" t="s">
-        <x:v>153</x:v>
       </x:c>
       <x:c r="K75" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M75" s="30" t="s">
         <x:v>21</x:v>
@@ -6925,25 +6931,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F76" s="30" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G76" s="30" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="G76" s="30" t="s">
-        <x:v>223</x:v>
-      </x:c>
       <x:c r="H76" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I76" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J76" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K76" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M76" s="30" t="s">
         <x:v>21</x:v>
@@ -6963,25 +6969,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F77" s="30" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G77" s="30" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G77" s="30" t="s">
+      <x:c r="H77" s="32">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I77" s="32">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J77" s="31" t="s">
         <x:v>225</x:v>
-      </x:c>
-      <x:c r="H77" s="32">
-        <x:v>46122.5911383796</x:v>
-      </x:c>
-      <x:c r="I77" s="32">
-        <x:v>46122.5921380556</x:v>
-      </x:c>
-      <x:c r="J77" s="31" t="s">
-        <x:v>226</x:v>
       </x:c>
       <x:c r="K77" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="34">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M77" s="30" t="s">
         <x:v>21</x:v>
@@ -7001,25 +7007,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F78" s="30" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G78" s="30" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="G78" s="30" t="s">
+      <x:c r="H78" s="32">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I78" s="32">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J78" s="31" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="H78" s="32">
-        <x:v>46122.6182774306</x:v>
-      </x:c>
-      <x:c r="I78" s="32">
-        <x:v>46122.6193276968</x:v>
-      </x:c>
-      <x:c r="J78" s="31" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="K78" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="34">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M78" s="30" t="s">
         <x:v>21</x:v>
@@ -7045,19 +7051,19 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="H79" s="32">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I79" s="32">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J79" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K79" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="34">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M79" s="30" t="s">
         <x:v>21</x:v>
@@ -7083,19 +7089,19 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="H80" s="32">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I80" s="32">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J80" s="31" t="s">
-        <x:v>233</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K80" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="34">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M80" s="30" t="s">
         <x:v>21</x:v>
@@ -7115,25 +7121,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F81" s="30" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G81" s="30" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="G81" s="30" t="s">
+      <x:c r="H81" s="32">
+        <x:v>46122.6819179514</x:v>
+      </x:c>
+      <x:c r="I81" s="32">
+        <x:v>46122.6826717361</x:v>
+      </x:c>
+      <x:c r="J81" s="31" t="s">
         <x:v>235</x:v>
-      </x:c>
-      <x:c r="H81" s="32">
-        <x:v>46122.7261372338</x:v>
-      </x:c>
-      <x:c r="I81" s="32">
-        <x:v>46122.727234375</x:v>
-      </x:c>
-      <x:c r="J81" s="31" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K81" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="34">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M81" s="30" t="s">
         <x:v>21</x:v>
@@ -7159,19 +7165,19 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="H82" s="32">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I82" s="32">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J82" s="31" t="s">
-        <x:v>238</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K82" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="34">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M82" s="30" t="s">
         <x:v>21</x:v>
@@ -7191,25 +7197,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F83" s="30" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G83" s="30" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="G83" s="30" t="s">
+      <x:c r="H83" s="32">
+        <x:v>46122.9452935995</x:v>
+      </x:c>
+      <x:c r="I83" s="32">
+        <x:v>46123.0460683681</x:v>
+      </x:c>
+      <x:c r="J83" s="31" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="H83" s="32">
-        <x:v>46123.0476912847</x:v>
-      </x:c>
-      <x:c r="I83" s="32">
-        <x:v>46123.0484775694</x:v>
-      </x:c>
-      <x:c r="J83" s="31" t="s">
-        <x:v>241</x:v>
       </x:c>
       <x:c r="K83" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="34">
-        <x:v>46123.049084375</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M83" s="30" t="s">
         <x:v>21</x:v>
@@ -7229,25 +7235,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F84" s="30" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G84" s="30" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="G84" s="30" t="s">
+      <x:c r="H84" s="32">
+        <x:v>46123.0476912847</x:v>
+      </x:c>
+      <x:c r="I84" s="32">
+        <x:v>46123.0484775694</x:v>
+      </x:c>
+      <x:c r="J84" s="31" t="s">
         <x:v>243</x:v>
-      </x:c>
-      <x:c r="H84" s="32">
-        <x:v>46122.5945434491</x:v>
-      </x:c>
-      <x:c r="I84" s="32">
-        <x:v>46122.5999534606</x:v>
-      </x:c>
-      <x:c r="J84" s="31" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K84" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="34">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M84" s="30" t="s">
         <x:v>21</x:v>
@@ -7273,10 +7279,10 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="H85" s="32">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I85" s="32">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J85" s="31" t="s">
         <x:v>28</x:v>
@@ -7285,68 +7291,105 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="34">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M85" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B86" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C86" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D86" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E86" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F86" s="30" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G86" s="30" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H86" s="32">
+        <x:v>46128.4605351157</x:v>
+      </x:c>
+      <x:c r="I86" s="32">
+        <x:v>46128.4612873727</x:v>
+      </x:c>
+      <x:c r="J86" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K86" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L86" s="34">
+        <x:v>46128.4617054051</x:v>
+      </x:c>
+      <x:c r="M86" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="88" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B88" s="18" t="s">
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B89" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C88" s="19" t="s"/>
-      <x:c r="D88" s="19" t="s"/>
-      <x:c r="E88" s="20" t="s"/>
-      <x:c r="F88" s="20" t="s"/>
-    </x:row>
-    <x:row r="89" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B89" s="21" t="s">
+      <x:c r="C89" s="19" t="s"/>
+      <x:c r="D89" s="19" t="s"/>
+      <x:c r="E89" s="20" t="s"/>
+      <x:c r="F89" s="20" t="s"/>
+    </x:row>
+    <x:row r="90" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B90" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C89" s="22" t="s"/>
-      <x:c r="D89" s="22" t="s"/>
-      <x:c r="E89" s="22" t="s"/>
-      <x:c r="F89" s="23" t="s">
+      <x:c r="C90" s="22" t="s"/>
+      <x:c r="D90" s="22" t="s"/>
+      <x:c r="E90" s="22" t="s"/>
+      <x:c r="F90" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B90" s="24" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C90" s="25" t="s"/>
-      <x:c r="D90" s="25" t="s"/>
-      <x:c r="E90" s="25" t="s"/>
-      <x:c r="F90" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:28" ht="18" customHeight="1">
       <x:c r="B91" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C91" s="25" t="s"/>
       <x:c r="D91" s="25" t="s"/>
       <x:c r="E91" s="25" t="s"/>
       <x:c r="F91" s="26" t="n">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B92" s="27" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B92" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C92" s="25" t="s"/>
+      <x:c r="D92" s="25" t="s"/>
+      <x:c r="E92" s="25" t="s"/>
+      <x:c r="F92" s="26" t="n">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B93" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C92" s="28" t="s"/>
-      <x:c r="D92" s="28" t="s"/>
-      <x:c r="E92" s="28" t="s"/>
-      <x:c r="F92" s="29" t="n">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C93" s="28" t="s"/>
+      <x:c r="D93" s="28" t="s"/>
+      <x:c r="E93" s="28" t="s"/>
+      <x:c r="F93" s="29" t="n">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
     <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8253,11 +8296,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B88:F88"/>
-    <x:mergeCell ref="B89:E89"/>
+    <x:mergeCell ref="B89:F89"/>
     <x:mergeCell ref="B90:E90"/>
     <x:mergeCell ref="B91:E91"/>
     <x:mergeCell ref="B92:E92"/>
+    <x:mergeCell ref="B93:E93"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -779,7 +779,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -819,14 +819,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1106,7 +1098,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="30">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1117,16 +1109,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1138,65 +1127,65 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1231,99 +1220,95 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1625,17 +1610,17 @@
       <x:c r="B5" s="12">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1658,80 +1643,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="15">
         <x:v>46049.5726010069</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="15">
         <x:v>46049.5726341898</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="15">
         <x:v>46049.5962660532</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1751,44 +1736,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2894,17 +2879,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2927,238 +2912,238 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>46106.5066742245</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>46106.5082381134</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>46106.5099302546</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>46105.676846794</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>46106.5084437037</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>46106.5101144792</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="B10" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="s">
+      <x:c r="D10" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="E10" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H10" s="32">
+      <x:c r="H10" s="31">
         <x:v>46105.6741278125</x:v>
       </x:c>
-      <x:c r="I10" s="32">
+      <x:c r="I10" s="31">
         <x:v>46106.5086548727</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K10" s="33" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="34">
+      <x:c r="L10" s="33">
         <x:v>46106.5103567593</x:v>
       </x:c>
-      <x:c r="M10" s="30" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="B11" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H11" s="32">
+      <x:c r="H11" s="31">
         <x:v>46078.2888967361</x:v>
       </x:c>
-      <x:c r="I11" s="32">
+      <x:c r="I11" s="31">
         <x:v>46078.2901145602</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K11" s="33" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="34">
+      <x:c r="L11" s="33">
         <x:v>46089.2508762037</x:v>
       </x:c>
-      <x:c r="M11" s="30" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="18" t="s">
+      <x:c r="B14" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C14" s="19" t="s"/>
-      <x:c r="D14" s="19" t="s"/>
-      <x:c r="E14" s="20" t="s"/>
-      <x:c r="F14" s="20" t="s"/>
+      <x:c r="C14" s="18" t="s"/>
+      <x:c r="D14" s="18" t="s"/>
+      <x:c r="E14" s="19" t="s"/>
+      <x:c r="F14" s="19" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="21" t="s">
+      <x:c r="B15" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="s">
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="B16" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="27" t="s">
+      <x:c r="B17" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -4261,17 +4246,17 @@
       <x:c r="B5" s="12">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4294,3099 +4279,3099 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>46118.3222074537</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>46118.3241166898</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>46126.4798427199</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>46126.4809562153</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>46126.4814216667</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="B10" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="s">
+      <x:c r="D10" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="E10" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H10" s="32">
+      <x:c r="H10" s="31">
         <x:v>46126.4716621296</x:v>
       </x:c>
-      <x:c r="I10" s="32">
+      <x:c r="I10" s="31">
         <x:v>46126.4737503704</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="K10" s="33" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="34">
+      <x:c r="L10" s="33">
         <x:v>46126.4748429977</x:v>
       </x:c>
-      <x:c r="M10" s="30" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="B11" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H11" s="32">
+      <x:c r="H11" s="31">
         <x:v>46126.455832662</x:v>
       </x:c>
-      <x:c r="I11" s="32">
+      <x:c r="I11" s="31">
         <x:v>46126.4740829051</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="K11" s="33" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="34">
+      <x:c r="L11" s="33">
         <x:v>46126.4751368866</x:v>
       </x:c>
-      <x:c r="M11" s="30" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="30" t="s">
+      <x:c r="B12" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="s">
+      <x:c r="D12" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="s">
+      <x:c r="E12" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F12" s="30" t="s">
+      <x:c r="F12" s="29" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="G12" s="29" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H12" s="32">
+      <x:c r="H12" s="31">
         <x:v>46126.4485157523</x:v>
       </x:c>
-      <x:c r="I12" s="32">
+      <x:c r="I12" s="31">
         <x:v>46126.4527227431</x:v>
       </x:c>
-      <x:c r="J12" s="31" t="s">
+      <x:c r="J12" s="30" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K12" s="33" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="34">
+      <x:c r="L12" s="33">
         <x:v>46126.4533495949</x:v>
       </x:c>
-      <x:c r="M12" s="30" t="s">
+      <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="30" t="s">
+      <x:c r="B13" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D13" s="31" t="s">
+      <x:c r="D13" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="30" t="s">
+      <x:c r="E13" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F13" s="30" t="s">
+      <x:c r="F13" s="29" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G13" s="30" t="s">
+      <x:c r="G13" s="29" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H13" s="32">
+      <x:c r="H13" s="31">
         <x:v>46126.4381590509</x:v>
       </x:c>
-      <x:c r="I13" s="32">
+      <x:c r="I13" s="31">
         <x:v>46126.4434486343</x:v>
       </x:c>
-      <x:c r="J13" s="31" t="s">
+      <x:c r="J13" s="30" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K13" s="33" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L13" s="34">
+      <x:c r="L13" s="33">
         <x:v>46126.444417662</x:v>
       </x:c>
-      <x:c r="M13" s="30" t="s">
+      <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="30" t="s">
+      <x:c r="B14" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D14" s="31" t="s">
+      <x:c r="D14" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="30" t="s">
+      <x:c r="E14" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F14" s="30" t="s">
+      <x:c r="F14" s="29" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G14" s="30" t="s">
+      <x:c r="G14" s="29" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H14" s="32">
+      <x:c r="H14" s="31">
         <x:v>46126.2608066551</x:v>
       </x:c>
-      <x:c r="I14" s="32">
+      <x:c r="I14" s="31">
         <x:v>46126.2618529282</x:v>
       </x:c>
-      <x:c r="J14" s="31" t="s">
+      <x:c r="J14" s="30" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K14" s="33" t="n">
+      <x:c r="K14" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L14" s="34">
+      <x:c r="L14" s="33">
         <x:v>46126.2624254167</x:v>
       </x:c>
-      <x:c r="M14" s="30" t="s">
+      <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="30" t="s">
+      <x:c r="B15" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D15" s="31" t="s">
+      <x:c r="D15" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E15" s="30" t="s">
+      <x:c r="E15" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F15" s="30" t="s">
+      <x:c r="F15" s="29" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="G15" s="29" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H15" s="32">
+      <x:c r="H15" s="31">
         <x:v>46126.1914900926</x:v>
       </x:c>
-      <x:c r="I15" s="32">
+      <x:c r="I15" s="31">
         <x:v>46126.2594011574</x:v>
       </x:c>
-      <x:c r="J15" s="31" t="s">
+      <x:c r="J15" s="30" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="K15" s="33" t="n">
+      <x:c r="K15" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L15" s="34">
+      <x:c r="L15" s="33">
         <x:v>46126.2601296875</x:v>
       </x:c>
-      <x:c r="M15" s="30" t="s">
+      <x:c r="M15" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s">
+      <x:c r="B16" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D16" s="31" t="s">
+      <x:c r="D16" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E16" s="30" t="s">
+      <x:c r="E16" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F16" s="30" t="s">
+      <x:c r="F16" s="29" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
+      <x:c r="G16" s="29" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H16" s="32">
+      <x:c r="H16" s="31">
         <x:v>46126.1388059144</x:v>
       </x:c>
-      <x:c r="I16" s="32">
+      <x:c r="I16" s="31">
         <x:v>46126.1498425347</x:v>
       </x:c>
-      <x:c r="J16" s="31" t="s">
+      <x:c r="J16" s="30" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="K16" s="33" t="n">
+      <x:c r="K16" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L16" s="34">
+      <x:c r="L16" s="33">
         <x:v>46126.176386169</x:v>
       </x:c>
-      <x:c r="M16" s="30" t="s">
+      <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" s="30" t="s">
+      <x:c r="B17" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D17" s="31" t="s">
+      <x:c r="D17" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E17" s="30" t="s">
+      <x:c r="E17" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F17" s="30" t="s">
+      <x:c r="F17" s="29" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G17" s="30" t="s">
+      <x:c r="G17" s="29" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="H17" s="32">
+      <x:c r="H17" s="31">
         <x:v>46124.9835281713</x:v>
       </x:c>
-      <x:c r="I17" s="32">
+      <x:c r="I17" s="31">
         <x:v>46125.0608962963</x:v>
       </x:c>
-      <x:c r="J17" s="31" t="s">
+      <x:c r="J17" s="30" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="K17" s="33" t="n">
+      <x:c r="K17" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L17" s="34">
+      <x:c r="L17" s="33">
         <x:v>46126.1641622569</x:v>
       </x:c>
-      <x:c r="M17" s="30" t="s">
+      <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C18" s="30" t="s">
+      <x:c r="B18" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D18" s="31" t="s">
+      <x:c r="D18" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E18" s="30" t="s">
+      <x:c r="E18" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F18" s="30" t="s">
+      <x:c r="F18" s="29" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G18" s="30" t="s">
+      <x:c r="G18" s="29" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H18" s="32">
+      <x:c r="H18" s="31">
         <x:v>46119.8029380671</x:v>
       </x:c>
-      <x:c r="I18" s="32">
+      <x:c r="I18" s="31">
         <x:v>46120.5237086343</x:v>
       </x:c>
-      <x:c r="J18" s="31" t="s">
+      <x:c r="J18" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K18" s="33" t="n">
+      <x:c r="K18" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L18" s="34">
+      <x:c r="L18" s="33">
         <x:v>46120.5257164468</x:v>
       </x:c>
-      <x:c r="M18" s="30" t="s">
+      <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C19" s="30" t="s">
+      <x:c r="B19" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D19" s="31" t="s">
+      <x:c r="D19" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E19" s="30" t="s">
+      <x:c r="E19" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F19" s="30" t="s">
+      <x:c r="F19" s="29" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G19" s="30" t="s">
+      <x:c r="G19" s="29" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H19" s="32">
+      <x:c r="H19" s="31">
         <x:v>46120.2349196412</x:v>
       </x:c>
-      <x:c r="I19" s="32">
+      <x:c r="I19" s="31">
         <x:v>46120.5229746296</x:v>
       </x:c>
-      <x:c r="J19" s="31" t="s">
+      <x:c r="J19" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K19" s="33" t="n">
+      <x:c r="K19" s="32" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="34">
+      <x:c r="L19" s="33">
         <x:v>46120.5255047106</x:v>
       </x:c>
-      <x:c r="M19" s="30" t="s">
+      <x:c r="M19" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C20" s="30" t="s">
+      <x:c r="B20" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D20" s="31" t="s">
+      <x:c r="D20" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E20" s="30" t="s">
+      <x:c r="E20" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F20" s="30" t="s">
+      <x:c r="F20" s="29" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
+      <x:c r="G20" s="29" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="H20" s="32">
+      <x:c r="H20" s="31">
         <x:v>46120.2362105324</x:v>
       </x:c>
-      <x:c r="I20" s="32">
+      <x:c r="I20" s="31">
         <x:v>46120.5226826273</x:v>
       </x:c>
-      <x:c r="J20" s="31" t="s">
+      <x:c r="J20" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K20" s="33" t="n">
+      <x:c r="K20" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L20" s="34">
+      <x:c r="L20" s="33">
         <x:v>46120.5252627315</x:v>
       </x:c>
-      <x:c r="M20" s="30" t="s">
+      <x:c r="M20" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C21" s="30" t="s">
+      <x:c r="B21" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D21" s="31" t="s">
+      <x:c r="D21" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E21" s="30" t="s">
+      <x:c r="E21" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F21" s="30" t="s">
+      <x:c r="F21" s="29" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G21" s="30" t="s">
+      <x:c r="G21" s="29" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="H21" s="32">
+      <x:c r="H21" s="31">
         <x:v>46120.2374046412</x:v>
       </x:c>
-      <x:c r="I21" s="32">
+      <x:c r="I21" s="31">
         <x:v>46120.5224942245</x:v>
       </x:c>
-      <x:c r="J21" s="31" t="s">
+      <x:c r="J21" s="30" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="K21" s="33" t="n">
+      <x:c r="K21" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L21" s="34">
+      <x:c r="L21" s="33">
         <x:v>46120.5250032292</x:v>
       </x:c>
-      <x:c r="M21" s="30" t="s">
+      <x:c r="M21" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C22" s="30" t="s">
+      <x:c r="B22" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C22" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D22" s="31" t="s">
+      <x:c r="D22" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E22" s="30" t="s">
+      <x:c r="E22" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F22" s="30" t="s">
+      <x:c r="F22" s="29" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G22" s="30" t="s">
+      <x:c r="G22" s="29" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H22" s="32">
+      <x:c r="H22" s="31">
         <x:v>46120.7129542245</x:v>
       </x:c>
-      <x:c r="I22" s="32">
+      <x:c r="I22" s="31">
         <x:v>46121.100944213</x:v>
       </x:c>
-      <x:c r="J22" s="31" t="s">
+      <x:c r="J22" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K22" s="33" t="n">
+      <x:c r="K22" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L22" s="34">
+      <x:c r="L22" s="33">
         <x:v>46121.1029720949</x:v>
       </x:c>
-      <x:c r="M22" s="30" t="s">
+      <x:c r="M22" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C23" s="30" t="s">
+      <x:c r="B23" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C23" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D23" s="31" t="s">
+      <x:c r="D23" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E23" s="30" t="s">
+      <x:c r="E23" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F23" s="30" t="s">
+      <x:c r="F23" s="29" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G23" s="30" t="s">
+      <x:c r="G23" s="29" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="H23" s="32">
+      <x:c r="H23" s="31">
         <x:v>46121.0999663542</x:v>
       </x:c>
-      <x:c r="I23" s="32">
+      <x:c r="I23" s="31">
         <x:v>46121.1007466204</x:v>
       </x:c>
-      <x:c r="J23" s="31" t="s">
+      <x:c r="J23" s="30" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="K23" s="33" t="n">
+      <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L23" s="34">
+      <x:c r="L23" s="33">
         <x:v>46121.1027298958</x:v>
       </x:c>
-      <x:c r="M23" s="30" t="s">
+      <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C24" s="30" t="s">
+      <x:c r="B24" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C24" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D24" s="31" t="s">
+      <x:c r="D24" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E24" s="30" t="s">
+      <x:c r="E24" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F24" s="30" t="s">
+      <x:c r="F24" s="29" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G24" s="30" t="s">
+      <x:c r="G24" s="29" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="H24" s="32">
+      <x:c r="H24" s="31">
         <x:v>46121.5178724884</x:v>
       </x:c>
-      <x:c r="I24" s="32">
+      <x:c r="I24" s="31">
         <x:v>46122.2064690394</x:v>
       </x:c>
-      <x:c r="J24" s="31" t="s">
+      <x:c r="J24" s="30" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="K24" s="33" t="n">
+      <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L24" s="34">
+      <x:c r="L24" s="33">
         <x:v>46122.230922581</x:v>
       </x:c>
-      <x:c r="M24" s="30" t="s">
+      <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C25" s="30" t="s">
+      <x:c r="B25" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C25" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D25" s="31" t="s">
+      <x:c r="D25" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E25" s="30" t="s">
+      <x:c r="E25" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F25" s="30" t="s">
+      <x:c r="F25" s="29" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G25" s="30" t="s">
+      <x:c r="G25" s="29" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="H25" s="32">
+      <x:c r="H25" s="31">
         <x:v>46121.2464636111</x:v>
       </x:c>
-      <x:c r="I25" s="32">
+      <x:c r="I25" s="31">
         <x:v>46121.3217277662</x:v>
       </x:c>
-      <x:c r="J25" s="31" t="s">
+      <x:c r="J25" s="30" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="K25" s="33" t="n">
+      <x:c r="K25" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L25" s="34">
+      <x:c r="L25" s="33">
         <x:v>46121.498248206</x:v>
       </x:c>
-      <x:c r="M25" s="30" t="s">
+      <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C26" s="30" t="s">
+      <x:c r="B26" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C26" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="s">
+      <x:c r="D26" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E26" s="30" t="s">
+      <x:c r="E26" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F26" s="30" t="s">
+      <x:c r="F26" s="29" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G26" s="30" t="s">
+      <x:c r="G26" s="29" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="H26" s="32">
+      <x:c r="H26" s="31">
         <x:v>46121.4966047917</x:v>
       </x:c>
-      <x:c r="I26" s="32">
+      <x:c r="I26" s="31">
         <x:v>46121.4974146412</x:v>
       </x:c>
-      <x:c r="J26" s="31" t="s">
+      <x:c r="J26" s="30" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="K26" s="33" t="n">
+      <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L26" s="34">
+      <x:c r="L26" s="33">
         <x:v>46121.4980146875</x:v>
       </x:c>
-      <x:c r="M26" s="30" t="s">
+      <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C27" s="30" t="s">
+      <x:c r="B27" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C27" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D27" s="31" t="s">
+      <x:c r="D27" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E27" s="30" t="s">
+      <x:c r="E27" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F27" s="30" t="s">
+      <x:c r="F27" s="29" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G27" s="30" t="s">
+      <x:c r="G27" s="29" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="H27" s="32">
+      <x:c r="H27" s="31">
         <x:v>46121.5149441551</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="31">
         <x:v>46122.2067431944</x:v>
       </x:c>
-      <x:c r="J27" s="31" t="s">
+      <x:c r="J27" s="30" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="K27" s="33" t="n">
+      <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L27" s="34">
+      <x:c r="L27" s="33">
         <x:v>46122.2310990278</x:v>
       </x:c>
-      <x:c r="M27" s="30" t="s">
+      <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C28" s="30" t="s">
+      <x:c r="B28" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C28" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D28" s="31" t="s">
+      <x:c r="D28" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E28" s="30" t="s">
+      <x:c r="E28" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F28" s="30" t="s">
+      <x:c r="F28" s="29" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G28" s="30" t="s">
+      <x:c r="G28" s="29" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="H28" s="32">
+      <x:c r="H28" s="31">
         <x:v>46119.8023724884</x:v>
       </x:c>
-      <x:c r="I28" s="32">
+      <x:c r="I28" s="31">
         <x:v>46119.8046602662</x:v>
       </x:c>
-      <x:c r="J28" s="31" t="s">
+      <x:c r="J28" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K28" s="33" t="n">
+      <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L28" s="34">
+      <x:c r="L28" s="33">
         <x:v>46119.8055532407</x:v>
       </x:c>
-      <x:c r="M28" s="30" t="s">
+      <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C29" s="30" t="s">
+      <x:c r="B29" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C29" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D29" s="31" t="s">
+      <x:c r="D29" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E29" s="30" t="s">
+      <x:c r="E29" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F29" s="30" t="s">
+      <x:c r="F29" s="29" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G29" s="30" t="s">
+      <x:c r="G29" s="29" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H29" s="32">
+      <x:c r="H29" s="31">
         <x:v>46121.5183984954</x:v>
       </x:c>
-      <x:c r="I29" s="32">
+      <x:c r="I29" s="31">
         <x:v>46122.2061737153</x:v>
       </x:c>
-      <x:c r="J29" s="31" t="s">
+      <x:c r="J29" s="30" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="K29" s="33" t="n">
+      <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L29" s="34">
+      <x:c r="L29" s="33">
         <x:v>46122.2307100926</x:v>
       </x:c>
-      <x:c r="M29" s="30" t="s">
+      <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C30" s="30" t="s">
+      <x:c r="B30" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C30" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D30" s="31" t="s">
+      <x:c r="D30" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E30" s="30" t="s">
+      <x:c r="E30" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F30" s="30" t="s">
+      <x:c r="F30" s="29" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G30" s="30" t="s">
+      <x:c r="G30" s="29" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="H30" s="32">
+      <x:c r="H30" s="31">
         <x:v>46122.1299166204</x:v>
       </x:c>
-      <x:c r="I30" s="32">
+      <x:c r="I30" s="31">
         <x:v>46122.2059087963</x:v>
       </x:c>
-      <x:c r="J30" s="31" t="s">
+      <x:c r="J30" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K30" s="33" t="n">
+      <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L30" s="34">
+      <x:c r="L30" s="33">
         <x:v>46122.2086237847</x:v>
       </x:c>
-      <x:c r="M30" s="30" t="s">
+      <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C31" s="30" t="s">
+      <x:c r="B31" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C31" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D31" s="31" t="s">
+      <x:c r="D31" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E31" s="30" t="s">
+      <x:c r="E31" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F31" s="30" t="s">
+      <x:c r="F31" s="29" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G31" s="30" t="s">
+      <x:c r="G31" s="29" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="H31" s="32">
+      <x:c r="H31" s="31">
         <x:v>46121.2273626852</x:v>
       </x:c>
-      <x:c r="I31" s="32">
+      <x:c r="I31" s="31">
         <x:v>46121.228379213</x:v>
       </x:c>
-      <x:c r="J31" s="31" t="s">
+      <x:c r="J31" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K31" s="33" t="n">
+      <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L31" s="34">
+      <x:c r="L31" s="33">
         <x:v>46121.2291153125</x:v>
       </x:c>
-      <x:c r="M31" s="30" t="s">
+      <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B32" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C32" s="30" t="s">
+      <x:c r="B32" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C32" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D32" s="31" t="s">
+      <x:c r="D32" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E32" s="30" t="s">
+      <x:c r="E32" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F32" s="30" t="s">
+      <x:c r="F32" s="29" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="G32" s="30" t="s">
+      <x:c r="G32" s="29" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="H32" s="32">
+      <x:c r="H32" s="31">
         <x:v>46119.8017436343</x:v>
       </x:c>
-      <x:c r="I32" s="32">
+      <x:c r="I32" s="31">
         <x:v>46119.8048384144</x:v>
       </x:c>
-      <x:c r="J32" s="31" t="s">
+      <x:c r="J32" s="30" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="K32" s="33" t="n">
+      <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L32" s="34">
+      <x:c r="L32" s="33">
         <x:v>46119.8080510417</x:v>
       </x:c>
-      <x:c r="M32" s="30" t="s">
+      <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C33" s="30" t="s">
+      <x:c r="B33" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C33" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D33" s="31" t="s">
+      <x:c r="D33" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E33" s="30" t="s">
+      <x:c r="E33" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F33" s="30" t="s">
+      <x:c r="F33" s="29" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G33" s="30" t="s">
+      <x:c r="G33" s="29" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="H33" s="32">
+      <x:c r="H33" s="31">
         <x:v>46119.5439653357</x:v>
       </x:c>
-      <x:c r="I33" s="32">
+      <x:c r="I33" s="31">
         <x:v>46119.5452984143</x:v>
       </x:c>
-      <x:c r="J33" s="31" t="s">
+      <x:c r="J33" s="30" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="K33" s="33" t="n">
+      <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L33" s="34">
+      <x:c r="L33" s="33">
         <x:v>46119.5467543982</x:v>
       </x:c>
-      <x:c r="M33" s="30" t="s">
+      <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B34" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C34" s="30" t="s">
+      <x:c r="B34" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C34" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D34" s="31" t="s">
+      <x:c r="D34" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E34" s="30" t="s">
+      <x:c r="E34" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F34" s="30" t="s">
+      <x:c r="F34" s="29" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="G34" s="30" t="s">
+      <x:c r="G34" s="29" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="H34" s="32">
+      <x:c r="H34" s="31">
         <x:v>46119.729231331</x:v>
       </x:c>
-      <x:c r="I34" s="32">
+      <x:c r="I34" s="31">
         <x:v>46119.7316308565</x:v>
       </x:c>
-      <x:c r="J34" s="31" t="s">
+      <x:c r="J34" s="30" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="K34" s="33" t="n">
+      <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L34" s="34">
+      <x:c r="L34" s="33">
         <x:v>46119.7327704398</x:v>
       </x:c>
-      <x:c r="M34" s="30" t="s">
+      <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B35" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C35" s="30" t="s">
+      <x:c r="B35" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C35" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D35" s="31" t="s">
+      <x:c r="D35" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E35" s="30" t="s">
+      <x:c r="E35" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F35" s="30" t="s">
+      <x:c r="F35" s="29" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G35" s="30" t="s">
+      <x:c r="G35" s="29" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="H35" s="32">
+      <x:c r="H35" s="31">
         <x:v>46118.4219285995</x:v>
       </x:c>
-      <x:c r="I35" s="32">
+      <x:c r="I35" s="31">
         <x:v>46118.4229350116</x:v>
       </x:c>
-      <x:c r="J35" s="31" t="s">
+      <x:c r="J35" s="30" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="K35" s="33" t="n">
+      <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L35" s="34">
+      <x:c r="L35" s="33">
         <x:v>46118.4241364815</x:v>
       </x:c>
-      <x:c r="M35" s="30" t="s">
+      <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B36" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C36" s="30" t="s">
+      <x:c r="B36" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C36" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D36" s="31" t="s">
+      <x:c r="D36" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E36" s="30" t="s">
+      <x:c r="E36" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F36" s="30" t="s">
+      <x:c r="F36" s="29" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G36" s="30" t="s">
+      <x:c r="G36" s="29" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="H36" s="32">
+      <x:c r="H36" s="31">
         <x:v>46118.7424944097</x:v>
       </x:c>
-      <x:c r="I36" s="32">
+      <x:c r="I36" s="31">
         <x:v>46118.7432728009</x:v>
       </x:c>
-      <x:c r="J36" s="31" t="s">
+      <x:c r="J36" s="30" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="K36" s="33" t="n">
+      <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L36" s="34">
+      <x:c r="L36" s="33">
         <x:v>46118.743899213</x:v>
       </x:c>
-      <x:c r="M36" s="30" t="s">
+      <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C37" s="30" t="s">
+      <x:c r="B37" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C37" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D37" s="31" t="s">
+      <x:c r="D37" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E37" s="30" t="s">
+      <x:c r="E37" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F37" s="30" t="s">
+      <x:c r="F37" s="29" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G37" s="30" t="s">
+      <x:c r="G37" s="29" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H37" s="32">
+      <x:c r="H37" s="31">
         <x:v>46118.7562945255</x:v>
       </x:c>
-      <x:c r="I37" s="32">
+      <x:c r="I37" s="31">
         <x:v>46118.7571720255</x:v>
       </x:c>
-      <x:c r="J37" s="31" t="s">
+      <x:c r="J37" s="30" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="K37" s="33" t="n">
+      <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L37" s="34">
+      <x:c r="L37" s="33">
         <x:v>46118.7577859143</x:v>
       </x:c>
-      <x:c r="M37" s="30" t="s">
+      <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B38" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C38" s="30" t="s">
+      <x:c r="B38" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C38" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D38" s="31" t="s">
+      <x:c r="D38" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E38" s="30" t="s">
+      <x:c r="E38" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F38" s="30" t="s">
+      <x:c r="F38" s="29" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="G38" s="30" t="s">
+      <x:c r="G38" s="29" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="H38" s="32">
+      <x:c r="H38" s="31">
         <x:v>46119.0668949653</x:v>
       </x:c>
-      <x:c r="I38" s="32">
+      <x:c r="I38" s="31">
         <x:v>46119.0755180324</x:v>
       </x:c>
-      <x:c r="J38" s="31" t="s">
+      <x:c r="J38" s="30" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="K38" s="33" t="n">
+      <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L38" s="34">
+      <x:c r="L38" s="33">
         <x:v>46119.076169375</x:v>
       </x:c>
-      <x:c r="M38" s="30" t="s">
+      <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B39" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C39" s="30" t="s">
+      <x:c r="B39" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C39" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D39" s="31" t="s">
+      <x:c r="D39" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E39" s="30" t="s">
+      <x:c r="E39" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F39" s="30" t="s">
+      <x:c r="F39" s="29" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="G39" s="30" t="s">
+      <x:c r="G39" s="29" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="H39" s="32">
+      <x:c r="H39" s="31">
         <x:v>46119.0739296412</x:v>
       </x:c>
-      <x:c r="I39" s="32">
+      <x:c r="I39" s="31">
         <x:v>46119.0753097685</x:v>
       </x:c>
-      <x:c r="J39" s="31" t="s">
+      <x:c r="J39" s="30" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="K39" s="33" t="n">
+      <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L39" s="34">
+      <x:c r="L39" s="33">
         <x:v>46119.0764109954</x:v>
       </x:c>
-      <x:c r="M39" s="30" t="s">
+      <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B40" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C40" s="30" t="s">
+      <x:c r="B40" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C40" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D40" s="31" t="s">
+      <x:c r="D40" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E40" s="30" t="s">
+      <x:c r="E40" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F40" s="30" t="s">
+      <x:c r="F40" s="29" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G40" s="30" t="s">
+      <x:c r="G40" s="29" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="H40" s="32">
+      <x:c r="H40" s="31">
         <x:v>46119.1921340856</x:v>
       </x:c>
-      <x:c r="I40" s="32">
+      <x:c r="I40" s="31">
         <x:v>46119.1932160417</x:v>
       </x:c>
-      <x:c r="J40" s="31" t="s">
+      <x:c r="J40" s="30" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="K40" s="33" t="n">
+      <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L40" s="34">
+      <x:c r="L40" s="33">
         <x:v>46119.193627581</x:v>
       </x:c>
-      <x:c r="M40" s="30" t="s">
+      <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B41" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C41" s="30" t="s">
+      <x:c r="B41" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C41" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D41" s="31" t="s">
+      <x:c r="D41" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E41" s="30" t="s">
+      <x:c r="E41" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F41" s="30" t="s">
+      <x:c r="F41" s="29" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="G41" s="30" t="s">
+      <x:c r="G41" s="29" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="H41" s="32">
+      <x:c r="H41" s="31">
         <x:v>46119.7297941435</x:v>
       </x:c>
-      <x:c r="I41" s="32">
+      <x:c r="I41" s="31">
         <x:v>46119.731450544</x:v>
       </x:c>
-      <x:c r="J41" s="31" t="s">
+      <x:c r="J41" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K41" s="33" t="n">
+      <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L41" s="34">
+      <x:c r="L41" s="33">
         <x:v>46119.7324832755</x:v>
       </x:c>
-      <x:c r="M41" s="30" t="s">
+      <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B42" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C42" s="30" t="s">
+      <x:c r="B42" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C42" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D42" s="31" t="s">
+      <x:c r="D42" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E42" s="30" t="s">
+      <x:c r="E42" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F42" s="30" t="s">
+      <x:c r="F42" s="29" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G42" s="30" t="s">
+      <x:c r="G42" s="29" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="H42" s="32">
+      <x:c r="H42" s="31">
         <x:v>46119.4681336458</x:v>
       </x:c>
-      <x:c r="I42" s="32">
+      <x:c r="I42" s="31">
         <x:v>46119.4697068056</x:v>
       </x:c>
-      <x:c r="J42" s="31" t="s">
+      <x:c r="J42" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K42" s="33" t="n">
+      <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L42" s="34">
+      <x:c r="L42" s="33">
         <x:v>46119.470392037</x:v>
       </x:c>
-      <x:c r="M42" s="30" t="s">
+      <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B43" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C43" s="30" t="s">
+      <x:c r="B43" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C43" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D43" s="31" t="s">
+      <x:c r="D43" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E43" s="30" t="s">
+      <x:c r="E43" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F43" s="30" t="s">
+      <x:c r="F43" s="29" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="G43" s="30" t="s">
+      <x:c r="G43" s="29" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="H43" s="32">
+      <x:c r="H43" s="31">
         <x:v>46119.5424612384</x:v>
       </x:c>
-      <x:c r="I43" s="32">
+      <x:c r="I43" s="31">
         <x:v>46119.5457934491</x:v>
       </x:c>
-      <x:c r="J43" s="31" t="s">
+      <x:c r="J43" s="30" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="K43" s="33" t="n">
+      <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L43" s="34">
+      <x:c r="L43" s="33">
         <x:v>46119.5465567708</x:v>
       </x:c>
-      <x:c r="M43" s="30" t="s">
+      <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B44" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C44" s="30" t="s">
+      <x:c r="B44" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C44" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D44" s="31" t="s">
+      <x:c r="D44" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E44" s="30" t="s">
+      <x:c r="E44" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F44" s="30" t="s">
+      <x:c r="F44" s="29" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="G44" s="30" t="s">
+      <x:c r="G44" s="29" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="H44" s="32">
+      <x:c r="H44" s="31">
         <x:v>46119.542956794</x:v>
       </x:c>
-      <x:c r="I44" s="32">
+      <x:c r="I44" s="31">
         <x:v>46119.5456356481</x:v>
       </x:c>
-      <x:c r="J44" s="31" t="s">
+      <x:c r="J44" s="30" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="K44" s="33" t="n">
+      <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L44" s="34">
+      <x:c r="L44" s="33">
         <x:v>46119.5477968982</x:v>
       </x:c>
-      <x:c r="M44" s="30" t="s">
+      <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C45" s="30" t="s">
+      <x:c r="B45" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C45" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D45" s="31" t="s">
+      <x:c r="D45" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E45" s="30" t="s">
+      <x:c r="E45" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F45" s="30" t="s">
+      <x:c r="F45" s="29" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="G45" s="30" t="s">
+      <x:c r="G45" s="29" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="H45" s="32">
+      <x:c r="H45" s="31">
         <x:v>46119.5434206134</x:v>
       </x:c>
-      <x:c r="I45" s="32">
+      <x:c r="I45" s="31">
         <x:v>46119.545474919</x:v>
       </x:c>
-      <x:c r="J45" s="31" t="s">
+      <x:c r="J45" s="30" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="K45" s="33" t="n">
+      <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L45" s="34">
+      <x:c r="L45" s="33">
         <x:v>46119.5469447569</x:v>
       </x:c>
-      <x:c r="M45" s="30" t="s">
+      <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C46" s="30" t="s">
+      <x:c r="B46" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C46" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D46" s="31" t="s">
+      <x:c r="D46" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E46" s="30" t="s">
+      <x:c r="E46" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F46" s="30" t="s">
+      <x:c r="F46" s="29" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G46" s="30" t="s">
+      <x:c r="G46" s="29" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="H46" s="32">
+      <x:c r="H46" s="31">
         <x:v>46122.1996025926</x:v>
       </x:c>
-      <x:c r="I46" s="32">
+      <x:c r="I46" s="31">
         <x:v>46122.2050823032</x:v>
       </x:c>
-      <x:c r="J46" s="31" t="s">
+      <x:c r="J46" s="30" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="K46" s="33" t="n">
+      <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L46" s="34">
+      <x:c r="L46" s="33">
         <x:v>46122.2083635185</x:v>
       </x:c>
-      <x:c r="M46" s="30" t="s">
+      <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B47" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C47" s="30" t="s">
+      <x:c r="B47" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C47" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D47" s="31" t="s">
+      <x:c r="D47" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E47" s="30" t="s">
+      <x:c r="E47" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F47" s="30" t="s">
+      <x:c r="F47" s="29" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="G47" s="30" t="s">
+      <x:c r="G47" s="29" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="H47" s="32">
+      <x:c r="H47" s="31">
         <x:v>46119.7254171991</x:v>
       </x:c>
-      <x:c r="I47" s="32">
+      <x:c r="I47" s="31">
         <x:v>46119.7262936574</x:v>
       </x:c>
-      <x:c r="J47" s="31" t="s">
+      <x:c r="J47" s="30" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="K47" s="33" t="n">
+      <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L47" s="34">
+      <x:c r="L47" s="33">
         <x:v>46119.7267657407</x:v>
       </x:c>
-      <x:c r="M47" s="30" t="s">
+      <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B48" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C48" s="30" t="s">
+      <x:c r="B48" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C48" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D48" s="31" t="s">
+      <x:c r="D48" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E48" s="30" t="s">
+      <x:c r="E48" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F48" s="30" t="s">
+      <x:c r="F48" s="29" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="G48" s="30" t="s">
+      <x:c r="G48" s="29" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="H48" s="32">
+      <x:c r="H48" s="31">
         <x:v>46119.7285584838</x:v>
       </x:c>
-      <x:c r="I48" s="32">
+      <x:c r="I48" s="31">
         <x:v>46119.7318005208</x:v>
       </x:c>
-      <x:c r="J48" s="31" t="s">
+      <x:c r="J48" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K48" s="33" t="n">
+      <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L48" s="34">
+      <x:c r="L48" s="33">
         <x:v>46119.7339888773</x:v>
       </x:c>
-      <x:c r="M48" s="30" t="s">
+      <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B49" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C49" s="30" t="s">
+      <x:c r="B49" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C49" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D49" s="31" t="s">
+      <x:c r="D49" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E49" s="30" t="s">
+      <x:c r="E49" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F49" s="30" t="s">
+      <x:c r="F49" s="29" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="G49" s="30" t="s">
+      <x:c r="G49" s="29" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="H49" s="32">
+      <x:c r="H49" s="31">
         <x:v>46119.5267212153</x:v>
       </x:c>
-      <x:c r="I49" s="32">
+      <x:c r="I49" s="31">
         <x:v>46119.5274664236</x:v>
       </x:c>
-      <x:c r="J49" s="31" t="s">
+      <x:c r="J49" s="30" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="K49" s="33" t="n">
+      <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L49" s="34">
+      <x:c r="L49" s="33">
         <x:v>46119.5279398495</x:v>
       </x:c>
-      <x:c r="M49" s="30" t="s">
+      <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B50" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C50" s="30" t="s">
+      <x:c r="B50" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C50" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D50" s="31" t="s">
+      <x:c r="D50" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E50" s="30" t="s">
+      <x:c r="E50" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F50" s="30" t="s">
+      <x:c r="F50" s="29" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="G50" s="30" t="s">
+      <x:c r="G50" s="29" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="H50" s="32">
+      <x:c r="H50" s="31">
         <x:v>46122.2429836343</x:v>
       </x:c>
-      <x:c r="I50" s="32">
+      <x:c r="I50" s="31">
         <x:v>46122.244317963</x:v>
       </x:c>
-      <x:c r="J50" s="31" t="s">
+      <x:c r="J50" s="30" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="K50" s="33" t="n">
+      <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L50" s="34">
+      <x:c r="L50" s="33">
         <x:v>46122.2448800694</x:v>
       </x:c>
-      <x:c r="M50" s="30" t="s">
+      <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B51" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C51" s="30" t="s">
+      <x:c r="B51" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C51" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D51" s="31" t="s">
+      <x:c r="D51" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E51" s="30" t="s">
+      <x:c r="E51" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F51" s="30" t="s">
+      <x:c r="F51" s="29" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="G51" s="30" t="s">
+      <x:c r="G51" s="29" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="H51" s="32">
+      <x:c r="H51" s="31">
         <x:v>46122.3885020718</x:v>
       </x:c>
-      <x:c r="I51" s="32">
+      <x:c r="I51" s="31">
         <x:v>46122.3892655903</x:v>
       </x:c>
-      <x:c r="J51" s="31" t="s">
+      <x:c r="J51" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K51" s="33" t="n">
+      <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L51" s="34">
+      <x:c r="L51" s="33">
         <x:v>46122.3902404514</x:v>
       </x:c>
-      <x:c r="M51" s="30" t="s">
+      <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B52" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C52" s="30" t="s">
+      <x:c r="B52" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C52" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D52" s="31" t="s">
+      <x:c r="D52" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E52" s="30" t="s">
+      <x:c r="E52" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F52" s="30" t="s">
+      <x:c r="F52" s="29" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="G52" s="30" t="s">
+      <x:c r="G52" s="29" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="H52" s="32">
+      <x:c r="H52" s="31">
         <x:v>46122.36782125</x:v>
       </x:c>
-      <x:c r="I52" s="32">
+      <x:c r="I52" s="31">
         <x:v>46122.3686719907</x:v>
       </x:c>
-      <x:c r="J52" s="31" t="s">
+      <x:c r="J52" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K52" s="33" t="n">
+      <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L52" s="34">
+      <x:c r="L52" s="33">
         <x:v>46122.3692180787</x:v>
       </x:c>
-      <x:c r="M52" s="30" t="s">
+      <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B53" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C53" s="30" t="s">
+      <x:c r="B53" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C53" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D53" s="31" t="s">
+      <x:c r="D53" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E53" s="30" t="s">
+      <x:c r="E53" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F53" s="30" t="s">
+      <x:c r="F53" s="29" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="G53" s="30" t="s">
+      <x:c r="G53" s="29" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="H53" s="32">
+      <x:c r="H53" s="31">
         <x:v>46124.1449755903</x:v>
       </x:c>
-      <x:c r="I53" s="32">
+      <x:c r="I53" s="31">
         <x:v>46124.1465040046</x:v>
       </x:c>
-      <x:c r="J53" s="31" t="s">
+      <x:c r="J53" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K53" s="33" t="n">
+      <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L53" s="34">
+      <x:c r="L53" s="33">
         <x:v>46124.1471056481</x:v>
       </x:c>
-      <x:c r="M53" s="30" t="s">
+      <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B54" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C54" s="30" t="s">
+      <x:c r="B54" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C54" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D54" s="31" t="s">
+      <x:c r="D54" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E54" s="30" t="s">
+      <x:c r="E54" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F54" s="30" t="s">
+      <x:c r="F54" s="29" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G54" s="30" t="s">
+      <x:c r="G54" s="29" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="H54" s="32">
+      <x:c r="H54" s="31">
         <x:v>46124.1487218981</x:v>
       </x:c>
-      <x:c r="I54" s="32">
+      <x:c r="I54" s="31">
         <x:v>46124.1494313773</x:v>
       </x:c>
-      <x:c r="J54" s="31" t="s">
+      <x:c r="J54" s="30" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="K54" s="33" t="n">
+      <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L54" s="34">
+      <x:c r="L54" s="33">
         <x:v>46124.1498205093</x:v>
       </x:c>
-      <x:c r="M54" s="30" t="s">
+      <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B55" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C55" s="30" t="s">
+      <x:c r="B55" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C55" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D55" s="31" t="s">
+      <x:c r="D55" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E55" s="30" t="s">
+      <x:c r="E55" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F55" s="30" t="s">
+      <x:c r="F55" s="29" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="G55" s="30" t="s">
+      <x:c r="G55" s="29" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="H55" s="32">
+      <x:c r="H55" s="31">
         <x:v>46124.150742662</x:v>
       </x:c>
-      <x:c r="I55" s="32">
+      <x:c r="I55" s="31">
         <x:v>46124.153253125</x:v>
       </x:c>
-      <x:c r="J55" s="31" t="s">
+      <x:c r="J55" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K55" s="33" t="n">
+      <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L55" s="34">
+      <x:c r="L55" s="33">
         <x:v>46124.1542643171</x:v>
       </x:c>
-      <x:c r="M55" s="30" t="s">
+      <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B56" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C56" s="30" t="s">
+      <x:c r="B56" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C56" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D56" s="31" t="s">
+      <x:c r="D56" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E56" s="30" t="s">
+      <x:c r="E56" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F56" s="30" t="s">
+      <x:c r="F56" s="29" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="G56" s="30" t="s">
+      <x:c r="G56" s="29" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="H56" s="32">
+      <x:c r="H56" s="31">
         <x:v>46124.1512647338</x:v>
       </x:c>
-      <x:c r="I56" s="32">
+      <x:c r="I56" s="31">
         <x:v>46124.1530803935</x:v>
       </x:c>
-      <x:c r="J56" s="31" t="s">
+      <x:c r="J56" s="30" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="K56" s="33" t="n">
+      <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L56" s="34">
+      <x:c r="L56" s="33">
         <x:v>46124.1540594444</x:v>
       </x:c>
-      <x:c r="M56" s="30" t="s">
+      <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B57" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C57" s="30" t="s">
+      <x:c r="B57" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C57" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D57" s="31" t="s">
+      <x:c r="D57" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E57" s="30" t="s">
+      <x:c r="E57" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F57" s="30" t="s">
+      <x:c r="F57" s="29" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="G57" s="30" t="s">
+      <x:c r="G57" s="29" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="H57" s="32">
+      <x:c r="H57" s="31">
         <x:v>46124.1518079282</x:v>
       </x:c>
-      <x:c r="I57" s="32">
+      <x:c r="I57" s="31">
         <x:v>46124.1529164583</x:v>
       </x:c>
-      <x:c r="J57" s="31" t="s">
+      <x:c r="J57" s="30" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="K57" s="33" t="n">
+      <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L57" s="34">
+      <x:c r="L57" s="33">
         <x:v>46124.1538595949</x:v>
       </x:c>
-      <x:c r="M57" s="30" t="s">
+      <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B58" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C58" s="30" t="s">
+      <x:c r="B58" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C58" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D58" s="31" t="s">
+      <x:c r="D58" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E58" s="30" t="s">
+      <x:c r="E58" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F58" s="30" t="s">
+      <x:c r="F58" s="29" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G58" s="30" t="s">
+      <x:c r="G58" s="29" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="H58" s="32">
+      <x:c r="H58" s="31">
         <x:v>46124.5490358102</x:v>
       </x:c>
-      <x:c r="I58" s="32">
+      <x:c r="I58" s="31">
         <x:v>46124.6984689583</x:v>
       </x:c>
-      <x:c r="J58" s="31" t="s">
+      <x:c r="J58" s="30" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="K58" s="33" t="n">
+      <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L58" s="34">
+      <x:c r="L58" s="33">
         <x:v>46124.6992754861</x:v>
       </x:c>
-      <x:c r="M58" s="30" t="s">
+      <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B59" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C59" s="30" t="s">
+      <x:c r="B59" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C59" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D59" s="31" t="s">
+      <x:c r="D59" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E59" s="30" t="s">
+      <x:c r="E59" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F59" s="30" t="s">
+      <x:c r="F59" s="29" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="G59" s="30" t="s">
+      <x:c r="G59" s="29" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="H59" s="32">
+      <x:c r="H59" s="31">
         <x:v>46124.1410094907</x:v>
       </x:c>
-      <x:c r="I59" s="32">
+      <x:c r="I59" s="31">
         <x:v>46124.1426461806</x:v>
       </x:c>
-      <x:c r="J59" s="31" t="s">
+      <x:c r="J59" s="30" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="K59" s="33" t="n">
+      <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L59" s="34">
+      <x:c r="L59" s="33">
         <x:v>46124.1434541782</x:v>
       </x:c>
-      <x:c r="M59" s="30" t="s">
+      <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B60" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C60" s="30" t="s">
+      <x:c r="B60" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C60" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D60" s="31" t="s">
+      <x:c r="D60" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E60" s="30" t="s">
+      <x:c r="E60" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F60" s="30" t="s">
+      <x:c r="F60" s="29" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="G60" s="30" t="s">
+      <x:c r="G60" s="29" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H60" s="32">
+      <x:c r="H60" s="31">
         <x:v>46124.6761778356</x:v>
       </x:c>
-      <x:c r="I60" s="32">
+      <x:c r="I60" s="31">
         <x:v>46124.6772295602</x:v>
       </x:c>
-      <x:c r="J60" s="31" t="s">
+      <x:c r="J60" s="30" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="K60" s="33" t="n">
+      <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L60" s="34">
+      <x:c r="L60" s="33">
         <x:v>46124.6777516435</x:v>
       </x:c>
-      <x:c r="M60" s="30" t="s">
+      <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B61" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C61" s="30" t="s">
+      <x:c r="B61" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C61" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D61" s="31" t="s">
+      <x:c r="D61" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E61" s="30" t="s">
+      <x:c r="E61" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F61" s="30" t="s">
+      <x:c r="F61" s="29" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="G61" s="30" t="s">
+      <x:c r="G61" s="29" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="H61" s="32">
+      <x:c r="H61" s="31">
         <x:v>46124.701771875</x:v>
       </x:c>
-      <x:c r="I61" s="32">
+      <x:c r="I61" s="31">
         <x:v>46124.7049218519</x:v>
       </x:c>
-      <x:c r="J61" s="31" t="s">
+      <x:c r="J61" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K61" s="33" t="n">
+      <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L61" s="34">
+      <x:c r="L61" s="33">
         <x:v>46124.7061899306</x:v>
       </x:c>
-      <x:c r="M61" s="30" t="s">
+      <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B62" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C62" s="30" t="s">
+      <x:c r="B62" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C62" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D62" s="31" t="s">
+      <x:c r="D62" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E62" s="30" t="s">
+      <x:c r="E62" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F62" s="30" t="s">
+      <x:c r="F62" s="29" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="G62" s="30" t="s">
+      <x:c r="G62" s="29" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="H62" s="32">
+      <x:c r="H62" s="31">
         <x:v>46124.7023532986</x:v>
       </x:c>
-      <x:c r="I62" s="32">
+      <x:c r="I62" s="31">
         <x:v>46124.7048005093</x:v>
       </x:c>
-      <x:c r="J62" s="31" t="s">
+      <x:c r="J62" s="30" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="K62" s="33" t="n">
+      <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L62" s="34">
+      <x:c r="L62" s="33">
         <x:v>46124.7059938426</x:v>
       </x:c>
-      <x:c r="M62" s="30" t="s">
+      <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B63" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C63" s="30" t="s">
+      <x:c r="B63" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C63" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D63" s="31" t="s">
+      <x:c r="D63" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E63" s="30" t="s">
+      <x:c r="E63" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F63" s="30" t="s">
+      <x:c r="F63" s="29" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="G63" s="30" t="s">
+      <x:c r="G63" s="29" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="H63" s="32">
+      <x:c r="H63" s="31">
         <x:v>46124.7029179398</x:v>
       </x:c>
-      <x:c r="I63" s="32">
+      <x:c r="I63" s="31">
         <x:v>46124.7046092014</x:v>
       </x:c>
-      <x:c r="J63" s="31" t="s">
+      <x:c r="J63" s="30" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="K63" s="33" t="n">
+      <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L63" s="34">
+      <x:c r="L63" s="33">
         <x:v>46124.7058091204</x:v>
       </x:c>
-      <x:c r="M63" s="30" t="s">
+      <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B64" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C64" s="30" t="s">
+      <x:c r="B64" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C64" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D64" s="31" t="s">
+      <x:c r="D64" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E64" s="30" t="s">
+      <x:c r="E64" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F64" s="30" t="s">
+      <x:c r="F64" s="29" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="G64" s="30" t="s">
+      <x:c r="G64" s="29" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="H64" s="32">
+      <x:c r="H64" s="31">
         <x:v>46124.7035032407</x:v>
       </x:c>
-      <x:c r="I64" s="32">
+      <x:c r="I64" s="31">
         <x:v>46124.704475463</x:v>
       </x:c>
-      <x:c r="J64" s="31" t="s">
+      <x:c r="J64" s="30" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="K64" s="33" t="n">
+      <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L64" s="34">
+      <x:c r="L64" s="33">
         <x:v>46124.7056197917</x:v>
       </x:c>
-      <x:c r="M64" s="30" t="s">
+      <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B65" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C65" s="30" t="s">
+      <x:c r="B65" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C65" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D65" s="31" t="s">
+      <x:c r="D65" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E65" s="30" t="s">
+      <x:c r="E65" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F65" s="30" t="s">
+      <x:c r="F65" s="29" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="G65" s="30" t="s">
+      <x:c r="G65" s="29" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="H65" s="32">
+      <x:c r="H65" s="31">
         <x:v>46126.5341923727</x:v>
       </x:c>
-      <x:c r="I65" s="32">
+      <x:c r="I65" s="31">
         <x:v>46126.5348242708</x:v>
       </x:c>
-      <x:c r="J65" s="31" t="s">
+      <x:c r="J65" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K65" s="33" t="n">
+      <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L65" s="34">
+      <x:c r="L65" s="33">
         <x:v>46126.5353594213</x:v>
       </x:c>
-      <x:c r="M65" s="30" t="s">
+      <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B66" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C66" s="30" t="s">
+      <x:c r="B66" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C66" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D66" s="31" t="s">
+      <x:c r="D66" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E66" s="30" t="s">
+      <x:c r="E66" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F66" s="30" t="s">
+      <x:c r="F66" s="29" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="G66" s="30" t="s">
+      <x:c r="G66" s="29" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="H66" s="32">
+      <x:c r="H66" s="31">
         <x:v>46127.1221474769</x:v>
       </x:c>
-      <x:c r="I66" s="32">
+      <x:c r="I66" s="31">
         <x:v>46127.1231965625</x:v>
       </x:c>
-      <x:c r="J66" s="31" t="s">
+      <x:c r="J66" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K66" s="33" t="n">
+      <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L66" s="34">
+      <x:c r="L66" s="33">
         <x:v>46128.1095700579</x:v>
       </x:c>
-      <x:c r="M66" s="30" t="s">
+      <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B67" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C67" s="30" t="s">
+      <x:c r="B67" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C67" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D67" s="31" t="s">
+      <x:c r="D67" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E67" s="30" t="s">
+      <x:c r="E67" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F67" s="30" t="s">
+      <x:c r="F67" s="29" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="G67" s="30" t="s">
+      <x:c r="G67" s="29" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="H67" s="32">
+      <x:c r="H67" s="31">
         <x:v>46124.6975491551</x:v>
       </x:c>
-      <x:c r="I67" s="32">
+      <x:c r="I67" s="31">
         <x:v>46124.6983328357</x:v>
       </x:c>
-      <x:c r="J67" s="31" t="s">
+      <x:c r="J67" s="30" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="K67" s="33" t="n">
+      <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L67" s="34">
+      <x:c r="L67" s="33">
         <x:v>46124.6990752199</x:v>
       </x:c>
-      <x:c r="M67" s="30" t="s">
+      <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B68" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C68" s="30" t="s">
+      <x:c r="B68" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C68" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D68" s="31" t="s">
+      <x:c r="D68" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E68" s="30" t="s">
+      <x:c r="E68" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F68" s="30" t="s">
+      <x:c r="F68" s="29" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G68" s="30" t="s">
+      <x:c r="G68" s="29" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="H68" s="32">
+      <x:c r="H68" s="31">
         <x:v>46122.3569147569</x:v>
       </x:c>
-      <x:c r="I68" s="32">
+      <x:c r="I68" s="31">
         <x:v>46122.3577305324</x:v>
       </x:c>
-      <x:c r="J68" s="31" t="s">
+      <x:c r="J68" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K68" s="33" t="n">
+      <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L68" s="34">
+      <x:c r="L68" s="33">
         <x:v>46122.3582679861</x:v>
       </x:c>
-      <x:c r="M68" s="30" t="s">
+      <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B69" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C69" s="30" t="s">
+      <x:c r="B69" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C69" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D69" s="31" t="s">
+      <x:c r="D69" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E69" s="30" t="s">
+      <x:c r="E69" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F69" s="30" t="s">
+      <x:c r="F69" s="29" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="G69" s="30" t="s">
+      <x:c r="G69" s="29" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="H69" s="32">
+      <x:c r="H69" s="31">
         <x:v>46123.4191184375</x:v>
       </x:c>
-      <x:c r="I69" s="32">
+      <x:c r="I69" s="31">
         <x:v>46123.4205974074</x:v>
       </x:c>
-      <x:c r="J69" s="31" t="s">
+      <x:c r="J69" s="30" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="K69" s="33" t="n">
+      <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L69" s="34">
+      <x:c r="L69" s="33">
         <x:v>46123.4214065278</x:v>
       </x:c>
-      <x:c r="M69" s="30" t="s">
+      <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B70" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C70" s="30" t="s">
+      <x:c r="B70" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C70" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D70" s="31" t="s">
+      <x:c r="D70" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E70" s="30" t="s">
+      <x:c r="E70" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F70" s="30" t="s">
+      <x:c r="F70" s="29" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="G70" s="30" t="s">
+      <x:c r="G70" s="29" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="H70" s="32">
+      <x:c r="H70" s="31">
         <x:v>46123.061368912</x:v>
       </x:c>
-      <x:c r="I70" s="32">
+      <x:c r="I70" s="31">
         <x:v>46123.0623472106</x:v>
       </x:c>
-      <x:c r="J70" s="31" t="s">
+      <x:c r="J70" s="30" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="K70" s="33" t="n">
+      <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L70" s="34">
+      <x:c r="L70" s="33">
         <x:v>46123.0628773958</x:v>
       </x:c>
-      <x:c r="M70" s="30" t="s">
+      <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B71" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C71" s="30" t="s">
+      <x:c r="B71" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C71" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D71" s="31" t="s">
+      <x:c r="D71" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E71" s="30" t="s">
+      <x:c r="E71" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F71" s="30" t="s">
+      <x:c r="F71" s="29" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G71" s="30" t="s">
+      <x:c r="G71" s="29" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="H71" s="32">
+      <x:c r="H71" s="31">
         <x:v>46122.3767795718</x:v>
       </x:c>
-      <x:c r="I71" s="32">
+      <x:c r="I71" s="31">
         <x:v>46122.3776183449</x:v>
       </x:c>
-      <x:c r="J71" s="31" t="s">
+      <x:c r="J71" s="30" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="K71" s="33" t="n">
+      <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L71" s="34">
+      <x:c r="L71" s="33">
         <x:v>46122.3780755324</x:v>
       </x:c>
-      <x:c r="M71" s="30" t="s">
+      <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B72" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C72" s="30" t="s">
+      <x:c r="B72" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C72" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D72" s="31" t="s">
+      <x:c r="D72" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E72" s="30" t="s">
+      <x:c r="E72" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F72" s="30" t="s">
+      <x:c r="F72" s="29" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="G72" s="30" t="s">
+      <x:c r="G72" s="29" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="H72" s="32">
+      <x:c r="H72" s="31">
         <x:v>46122.3879258681</x:v>
       </x:c>
-      <x:c r="I72" s="32">
+      <x:c r="I72" s="31">
         <x:v>46122.3894281713</x:v>
       </x:c>
-      <x:c r="J72" s="31" t="s">
+      <x:c r="J72" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K72" s="33" t="n">
+      <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L72" s="34">
+      <x:c r="L72" s="33">
         <x:v>46122.3900310185</x:v>
       </x:c>
-      <x:c r="M72" s="30" t="s">
+      <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B73" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C73" s="30" t="s">
+      <x:c r="B73" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C73" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D73" s="31" t="s">
+      <x:c r="D73" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E73" s="30" t="s">
+      <x:c r="E73" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F73" s="30" t="s">
+      <x:c r="F73" s="29" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="G73" s="30" t="s">
+      <x:c r="G73" s="29" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="H73" s="32">
+      <x:c r="H73" s="31">
         <x:v>46118.3446055671</x:v>
       </x:c>
-      <x:c r="I73" s="32">
+      <x:c r="I73" s="31">
         <x:v>46118.476906412</x:v>
       </x:c>
-      <x:c r="J73" s="31" t="s">
+      <x:c r="J73" s="30" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="K73" s="33" t="n">
+      <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L73" s="34">
+      <x:c r="L73" s="33">
         <x:v>46118.3476865394</x:v>
       </x:c>
-      <x:c r="M73" s="30" t="s">
+      <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B74" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C74" s="30" t="s">
+      <x:c r="B74" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C74" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D74" s="31" t="s">
+      <x:c r="D74" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E74" s="30" t="s">
+      <x:c r="E74" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F74" s="30" t="s">
+      <x:c r="F74" s="29" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="G74" s="30" t="s">
+      <x:c r="G74" s="29" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="H74" s="32">
+      <x:c r="H74" s="31">
         <x:v>46122.3974322338</x:v>
       </x:c>
-      <x:c r="I74" s="32">
+      <x:c r="I74" s="31">
         <x:v>46122.3980999421</x:v>
       </x:c>
-      <x:c r="J74" s="31" t="s">
+      <x:c r="J74" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K74" s="33" t="n">
+      <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L74" s="34">
+      <x:c r="L74" s="33">
         <x:v>46122.398526713</x:v>
       </x:c>
-      <x:c r="M74" s="30" t="s">
+      <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B75" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C75" s="30" t="s">
+      <x:c r="B75" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C75" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D75" s="31" t="s">
+      <x:c r="D75" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E75" s="30" t="s">
+      <x:c r="E75" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F75" s="30" t="s">
+      <x:c r="F75" s="29" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="G75" s="30" t="s">
+      <x:c r="G75" s="29" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="H75" s="32">
+      <x:c r="H75" s="31">
         <x:v>46122.5587807523</x:v>
       </x:c>
-      <x:c r="I75" s="32">
+      <x:c r="I75" s="31">
         <x:v>46122.5602428125</x:v>
       </x:c>
-      <x:c r="J75" s="31" t="s">
+      <x:c r="J75" s="30" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="K75" s="33" t="n">
+      <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L75" s="34">
+      <x:c r="L75" s="33">
         <x:v>46122.5607516551</x:v>
       </x:c>
-      <x:c r="M75" s="30" t="s">
+      <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B76" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C76" s="30" t="s">
+      <x:c r="B76" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C76" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D76" s="31" t="s">
+      <x:c r="D76" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E76" s="30" t="s">
+      <x:c r="E76" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F76" s="30" t="s">
+      <x:c r="F76" s="29" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="G76" s="30" t="s">
+      <x:c r="G76" s="29" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="H76" s="32">
+      <x:c r="H76" s="31">
         <x:v>46122.5623107755</x:v>
       </x:c>
-      <x:c r="I76" s="32">
+      <x:c r="I76" s="31">
         <x:v>46122.5630093981</x:v>
       </x:c>
-      <x:c r="J76" s="31" t="s">
+      <x:c r="J76" s="30" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="K76" s="33" t="n">
+      <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L76" s="34">
+      <x:c r="L76" s="33">
         <x:v>46122.5634620023</x:v>
       </x:c>
-      <x:c r="M76" s="30" t="s">
+      <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B77" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C77" s="30" t="s">
+      <x:c r="B77" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C77" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D77" s="31" t="s">
+      <x:c r="D77" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E77" s="30" t="s">
+      <x:c r="E77" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F77" s="30" t="s">
+      <x:c r="F77" s="29" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G77" s="30" t="s">
+      <x:c r="G77" s="29" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="H77" s="32">
+      <x:c r="H77" s="31">
         <x:v>46123.4162791088</x:v>
       </x:c>
-      <x:c r="I77" s="32">
+      <x:c r="I77" s="31">
         <x:v>46123.4173169792</x:v>
       </x:c>
-      <x:c r="J77" s="31" t="s">
+      <x:c r="J77" s="30" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="K77" s="33" t="n">
+      <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L77" s="34">
+      <x:c r="L77" s="33">
         <x:v>46123.417862662</x:v>
       </x:c>
-      <x:c r="M77" s="30" t="s">
+      <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B78" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C78" s="30" t="s">
+      <x:c r="B78" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C78" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D78" s="31" t="s">
+      <x:c r="D78" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E78" s="30" t="s">
+      <x:c r="E78" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F78" s="30" t="s">
+      <x:c r="F78" s="29" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="G78" s="30" t="s">
+      <x:c r="G78" s="29" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="H78" s="32">
+      <x:c r="H78" s="31">
         <x:v>46122.5911383796</x:v>
       </x:c>
-      <x:c r="I78" s="32">
+      <x:c r="I78" s="31">
         <x:v>46122.5921380556</x:v>
       </x:c>
-      <x:c r="J78" s="31" t="s">
+      <x:c r="J78" s="30" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="K78" s="33" t="n">
+      <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L78" s="34">
+      <x:c r="L78" s="33">
         <x:v>46122.5928339699</x:v>
       </x:c>
-      <x:c r="M78" s="30" t="s">
+      <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B79" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C79" s="30" t="s">
+      <x:c r="B79" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C79" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D79" s="31" t="s">
+      <x:c r="D79" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E79" s="30" t="s">
+      <x:c r="E79" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F79" s="30" t="s">
+      <x:c r="F79" s="29" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="G79" s="30" t="s">
+      <x:c r="G79" s="29" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="H79" s="32">
+      <x:c r="H79" s="31">
         <x:v>46122.6182774306</x:v>
       </x:c>
-      <x:c r="I79" s="32">
+      <x:c r="I79" s="31">
         <x:v>46122.6193276968</x:v>
       </x:c>
-      <x:c r="J79" s="31" t="s">
+      <x:c r="J79" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K79" s="33" t="n">
+      <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L79" s="34">
+      <x:c r="L79" s="33">
         <x:v>46122.6199813426</x:v>
       </x:c>
-      <x:c r="M79" s="30" t="s">
+      <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B80" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C80" s="30" t="s">
+      <x:c r="B80" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C80" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D80" s="31" t="s">
+      <x:c r="D80" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E80" s="30" t="s">
+      <x:c r="E80" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F80" s="30" t="s">
+      <x:c r="F80" s="29" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="G80" s="30" t="s">
+      <x:c r="G80" s="29" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="H80" s="32">
+      <x:c r="H80" s="31">
         <x:v>46122.6795081481</x:v>
       </x:c>
-      <x:c r="I80" s="32">
+      <x:c r="I80" s="31">
         <x:v>46122.6802186921</x:v>
       </x:c>
-      <x:c r="J80" s="31" t="s">
+      <x:c r="J80" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K80" s="33" t="n">
+      <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L80" s="34">
+      <x:c r="L80" s="33">
         <x:v>46122.6809879398</x:v>
       </x:c>
-      <x:c r="M80" s="30" t="s">
+      <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B81" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C81" s="30" t="s">
+      <x:c r="B81" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C81" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D81" s="31" t="s">
+      <x:c r="D81" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E81" s="30" t="s">
+      <x:c r="E81" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F81" s="30" t="s">
+      <x:c r="F81" s="29" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="G81" s="30" t="s">
+      <x:c r="G81" s="29" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="H81" s="32">
+      <x:c r="H81" s="31">
         <x:v>46122.6819179514</x:v>
       </x:c>
-      <x:c r="I81" s="32">
+      <x:c r="I81" s="31">
         <x:v>46122.6826717361</x:v>
       </x:c>
-      <x:c r="J81" s="31" t="s">
+      <x:c r="J81" s="30" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="K81" s="33" t="n">
+      <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L81" s="34">
+      <x:c r="L81" s="33">
         <x:v>46122.6831438079</x:v>
       </x:c>
-      <x:c r="M81" s="30" t="s">
+      <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B82" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C82" s="30" t="s">
+      <x:c r="B82" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C82" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D82" s="31" t="s">
+      <x:c r="D82" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E82" s="30" t="s">
+      <x:c r="E82" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F82" s="30" t="s">
+      <x:c r="F82" s="29" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="G82" s="30" t="s">
+      <x:c r="G82" s="29" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="H82" s="32">
+      <x:c r="H82" s="31">
         <x:v>46122.7261372338</x:v>
       </x:c>
-      <x:c r="I82" s="32">
+      <x:c r="I82" s="31">
         <x:v>46122.727234375</x:v>
       </x:c>
-      <x:c r="J82" s="31" t="s">
+      <x:c r="J82" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K82" s="33" t="n">
+      <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L82" s="34">
+      <x:c r="L82" s="33">
         <x:v>46122.7277720023</x:v>
       </x:c>
-      <x:c r="M82" s="30" t="s">
+      <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B83" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C83" s="30" t="s">
+      <x:c r="B83" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C83" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D83" s="31" t="s">
+      <x:c r="D83" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E83" s="30" t="s">
+      <x:c r="E83" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F83" s="30" t="s">
+      <x:c r="F83" s="29" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="G83" s="30" t="s">
+      <x:c r="G83" s="29" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="H83" s="32">
+      <x:c r="H83" s="31">
         <x:v>46122.9452935995</x:v>
       </x:c>
-      <x:c r="I83" s="32">
+      <x:c r="I83" s="31">
         <x:v>46123.0460683681</x:v>
       </x:c>
-      <x:c r="J83" s="31" t="s">
+      <x:c r="J83" s="30" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="K83" s="33" t="n">
+      <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L83" s="34">
+      <x:c r="L83" s="33">
         <x:v>46123.0466478819</x:v>
       </x:c>
-      <x:c r="M83" s="30" t="s">
+      <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B84" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C84" s="30" t="s">
+      <x:c r="B84" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C84" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D84" s="31" t="s">
+      <x:c r="D84" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E84" s="30" t="s">
+      <x:c r="E84" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F84" s="30" t="s">
+      <x:c r="F84" s="29" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="G84" s="30" t="s">
+      <x:c r="G84" s="29" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="H84" s="32">
+      <x:c r="H84" s="31">
         <x:v>46123.0476912847</x:v>
       </x:c>
-      <x:c r="I84" s="32">
+      <x:c r="I84" s="31">
         <x:v>46123.0484775694</x:v>
       </x:c>
-      <x:c r="J84" s="31" t="s">
+      <x:c r="J84" s="30" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="K84" s="33" t="n">
+      <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L84" s="34">
+      <x:c r="L84" s="33">
         <x:v>46123.049084375</x:v>
       </x:c>
-      <x:c r="M84" s="30" t="s">
+      <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B85" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C85" s="30" t="s">
+      <x:c r="B85" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C85" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D85" s="31" t="s">
+      <x:c r="D85" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E85" s="30" t="s">
+      <x:c r="E85" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F85" s="30" t="s">
+      <x:c r="F85" s="29" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="G85" s="30" t="s">
+      <x:c r="G85" s="29" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="H85" s="32">
+      <x:c r="H85" s="31">
         <x:v>46122.5945434491</x:v>
       </x:c>
-      <x:c r="I85" s="32">
+      <x:c r="I85" s="31">
         <x:v>46122.5999534606</x:v>
       </x:c>
-      <x:c r="J85" s="31" t="s">
+      <x:c r="J85" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K85" s="33" t="n">
+      <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L85" s="34">
+      <x:c r="L85" s="33">
         <x:v>46122.6007489699</x:v>
       </x:c>
-      <x:c r="M85" s="30" t="s">
+      <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B86" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C86" s="30" t="s">
+      <x:c r="B86" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C86" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D86" s="31" t="s">
+      <x:c r="D86" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E86" s="30" t="s">
+      <x:c r="E86" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F86" s="30" t="s">
+      <x:c r="F86" s="29" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="G86" s="30" t="s">
+      <x:c r="G86" s="29" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="H86" s="32">
+      <x:c r="H86" s="31">
         <x:v>46128.4605351157</x:v>
       </x:c>
-      <x:c r="I86" s="32">
+      <x:c r="I86" s="31">
         <x:v>46128.4612873727</x:v>
       </x:c>
-      <x:c r="J86" s="31" t="s">
+      <x:c r="J86" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K86" s="33" t="n">
+      <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L86" s="34">
+      <x:c r="L86" s="33">
         <x:v>46128.4617054051</x:v>
       </x:c>
-      <x:c r="M86" s="30" t="s">
+      <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="89" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B89" s="18" t="s">
+      <x:c r="B89" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C89" s="19" t="s"/>
-      <x:c r="D89" s="19" t="s"/>
-      <x:c r="E89" s="20" t="s"/>
-      <x:c r="F89" s="20" t="s"/>
+      <x:c r="C89" s="18" t="s"/>
+      <x:c r="D89" s="18" t="s"/>
+      <x:c r="E89" s="19" t="s"/>
+      <x:c r="F89" s="19" t="s"/>
     </x:row>
     <x:row r="90" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B90" s="21" t="s">
+      <x:c r="B90" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C90" s="22" t="s"/>
-      <x:c r="D90" s="22" t="s"/>
-      <x:c r="E90" s="22" t="s"/>
-      <x:c r="F90" s="23" t="s">
+      <x:c r="C90" s="21" t="s"/>
+      <x:c r="D90" s="21" t="s"/>
+      <x:c r="E90" s="21" t="s"/>
+      <x:c r="F90" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B91" s="24" t="s">
+      <x:c r="B91" s="23" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C91" s="25" t="s"/>
-      <x:c r="D91" s="25" t="s"/>
-      <x:c r="E91" s="25" t="s"/>
-      <x:c r="F91" s="26" t="n">
+      <x:c r="C91" s="24" t="s"/>
+      <x:c r="D91" s="24" t="s"/>
+      <x:c r="E91" s="24" t="s"/>
+      <x:c r="F91" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B92" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C92" s="25" t="s"/>
-      <x:c r="D92" s="25" t="s"/>
-      <x:c r="E92" s="25" t="s"/>
-      <x:c r="F92" s="26" t="n">
+      <x:c r="B92" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C92" s="24" t="s"/>
+      <x:c r="D92" s="24" t="s"/>
+      <x:c r="E92" s="24" t="s"/>
+      <x:c r="F92" s="25" t="n">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B93" s="27" t="s">
+      <x:c r="B93" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C93" s="28" t="s"/>
-      <x:c r="D93" s="28" t="s"/>
-      <x:c r="E93" s="28" t="s"/>
-      <x:c r="F93" s="29" t="n">
+      <x:c r="C93" s="27" t="s"/>
+      <x:c r="D93" s="27" t="s"/>
+      <x:c r="E93" s="27" t="s"/>
+      <x:c r="F93" s="28" t="n">
         <x:v>79</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="248">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="250">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -149,6 +149,69 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1321-473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08292</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1322-790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1323-538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1324-430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wesdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1325-890</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdxzcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1316-566</x:t>
+  </x:si>
+  <x:si>
+    <x:t>szdasdqweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08340</x:t>
   </x:si>
   <x:si>
@@ -158,15 +221,6 @@
     <x:t>aszxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1327-230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qweasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08338</x:t>
   </x:si>
   <x:si>
@@ -176,60 +230,6 @@
     <x:t>asdqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1325-890</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdxzcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08335</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1324-430</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wesdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08296</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1323-538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08292</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1322-790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08281</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1321-473</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08219</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1316-566</x:t>
-  </x:si>
-  <x:si>
-    <x:t>szdasdqweq</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
   </x:si>
   <x:si>
@@ -278,6 +278,30 @@
     <x:t>resdxcv</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08147</x:t>
   </x:si>
   <x:si>
@@ -287,13 +311,34 @@
     <x:t>zxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08145</x:t>
@@ -305,42 +350,6 @@
     <x:t>sdf</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
   </x:si>
   <x:si>
@@ -458,13 +467,10 @@
     <x:t>zcx</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08095</x:t>
@@ -488,10 +494,172 @@
     <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08169</x:t>
@@ -500,136 +668,37 @@
     <x:t>61-4-2026-1283-909</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08185</x:t>
@@ -641,6 +710,51 @@
     <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08183</x:t>
   </x:si>
   <x:si>
@@ -650,124 +764,16 @@
     <x:t>zsdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08177</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1289-340</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4376,10 +4382,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="31">
-        <x:v>46126.4798427199</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I9" s="31">
-        <x:v>46126.4809562153</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J9" s="30" t="s">
         <x:v>43</x:v>
@@ -4388,7 +4394,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
@@ -4414,10 +4420,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I10" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J10" s="30" t="s">
         <x:v>46</x:v>
@@ -4426,7 +4432,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
@@ -4452,10 +4458,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46126.455832662</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I11" s="31">
-        <x:v>46126.4740829051</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J11" s="30" t="s">
         <x:v>49</x:v>
@@ -4464,7 +4470,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
@@ -4490,10 +4496,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46126.4485157523</x:v>
+        <x:v>46126.4381590509</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>46126.4527227431</x:v>
+        <x:v>46126.4434486343</x:v>
       </x:c>
       <x:c r="J12" s="30" t="s">
         <x:v>52</x:v>
@@ -4502,7 +4508,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46126.4533495949</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
@@ -4528,10 +4534,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>46126.4381590509</x:v>
+        <x:v>46126.4485157523</x:v>
       </x:c>
       <x:c r="I13" s="31">
-        <x:v>46126.4434486343</x:v>
+        <x:v>46126.4527227431</x:v>
       </x:c>
       <x:c r="J13" s="30" t="s">
         <x:v>55</x:v>
@@ -4540,7 +4546,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>46126.444417662</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
@@ -4566,19 +4572,19 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H14" s="31">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46124.9835281713</x:v>
       </x:c>
       <x:c r="I14" s="31">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46125.0608962963</x:v>
       </x:c>
       <x:c r="J14" s="30" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="K14" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L14" s="33">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.1641622569</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
@@ -4604,10 +4610,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I15" s="31">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J15" s="30" t="s">
         <x:v>61</x:v>
@@ -4616,7 +4622,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
         <x:v>21</x:v>
@@ -4642,10 +4648,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J16" s="30" t="s">
         <x:v>64</x:v>
@@ -4654,7 +4660,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
@@ -4680,19 +4686,19 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46124.9835281713</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>46125.0608962963</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="K17" s="32" t="n">
-        <x:v>240</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46126.1641622569</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
@@ -4946,19 +4952,19 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>86</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
@@ -4978,10 +4984,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="29" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G25" s="29" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="G25" s="29" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="H25" s="31">
         <x:v>46121.2464636111</x:v>
@@ -4990,7 +4996,7 @@
         <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
         <x:v>210</x:v>
@@ -5016,25 +5022,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="29" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G26" s="29" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G26" s="29" t="s">
+      <x:c r="H26" s="31">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I26" s="31">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J26" s="30" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H26" s="31">
-        <x:v>46121.4966047917</x:v>
-      </x:c>
-      <x:c r="I26" s="31">
-        <x:v>46121.4974146412</x:v>
-      </x:c>
-      <x:c r="J26" s="30" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -5054,25 +5060,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="29" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G27" s="29" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G27" s="29" t="s">
+      <x:c r="H27" s="31">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I27" s="31">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J27" s="30" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="H27" s="31">
-        <x:v>46121.5149441551</x:v>
-      </x:c>
-      <x:c r="I27" s="31">
-        <x:v>46122.2067431944</x:v>
-      </x:c>
-      <x:c r="J27" s="30" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -5092,10 +5098,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="29" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G28" s="29" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="G28" s="29" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="H28" s="31">
         <x:v>46119.8023724884</x:v>
@@ -5130,25 +5136,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="29" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G29" s="29" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G29" s="29" t="s">
+      <x:c r="H29" s="31">
+        <x:v>46122.1996025926</x:v>
+      </x:c>
+      <x:c r="I29" s="31">
+        <x:v>46122.2050823032</x:v>
+      </x:c>
+      <x:c r="J29" s="30" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="H29" s="31">
-        <x:v>46121.5183984954</x:v>
-      </x:c>
-      <x:c r="I29" s="31">
-        <x:v>46122.2061737153</x:v>
-      </x:c>
-      <x:c r="J29" s="30" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -5168,10 +5174,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="29" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G30" s="29" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="G30" s="29" t="s">
-        <x:v>102</x:v>
       </x:c>
       <x:c r="H30" s="31">
         <x:v>46122.1299166204</x:v>
@@ -5206,25 +5212,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G31" s="29" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G31" s="29" t="s">
+      <x:c r="H31" s="31">
+        <x:v>46121.5183984954</x:v>
+      </x:c>
+      <x:c r="I31" s="31">
+        <x:v>46122.2061737153</x:v>
+      </x:c>
+      <x:c r="J31" s="30" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="H31" s="31">
-        <x:v>46121.2273626852</x:v>
-      </x:c>
-      <x:c r="I31" s="31">
-        <x:v>46121.228379213</x:v>
-      </x:c>
-      <x:c r="J31" s="30" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -5250,19 +5256,19 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
-        <x:v>64</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
@@ -5282,25 +5288,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="29" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G33" s="29" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
-        <x:v>109</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -5326,10 +5332,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
         <x:v>112</x:v>
@@ -5338,7 +5344,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -5364,10 +5370,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
         <x:v>115</x:v>
@@ -5376,7 +5382,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
@@ -5402,10 +5408,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
         <x:v>118</x:v>
@@ -5414,7 +5420,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -5440,10 +5446,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
         <x:v>121</x:v>
@@ -5452,7 +5458,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
@@ -5478,10 +5484,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="H38" s="31">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I38" s="31">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
         <x:v>124</x:v>
@@ -5490,7 +5496,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
@@ -5516,10 +5522,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
         <x:v>127</x:v>
@@ -5528,7 +5534,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
@@ -5554,10 +5560,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="H40" s="31">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I40" s="31">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
         <x:v>130</x:v>
@@ -5566,7 +5572,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
@@ -5592,19 +5598,19 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H41" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I41" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
@@ -5624,25 +5630,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G42" s="29" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H42" s="31">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I42" s="31">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -5662,25 +5668,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G43" s="29" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H43" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I43" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
-        <x:v>137</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -5706,10 +5712,10 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="H44" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I44" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
         <x:v>140</x:v>
@@ -5718,7 +5724,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -5744,10 +5750,10 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="H45" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I45" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J45" s="30" t="s">
         <x:v>143</x:v>
@@ -5756,7 +5762,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -5782,10 +5788,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="H46" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
         <x:v>146</x:v>
@@ -5794,7 +5800,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
@@ -5820,19 +5826,19 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="H47" s="31">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I47" s="31">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J47" s="30" t="s">
-        <x:v>64</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -5858,19 +5864,19 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -5896,19 +5902,19 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -5928,25 +5934,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="29" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G50" s="29" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="G50" s="29" t="s">
+      <x:c r="H50" s="31">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I50" s="31">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J50" s="30" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="H50" s="31">
-        <x:v>46122.2429836343</x:v>
-      </x:c>
-      <x:c r="I50" s="31">
-        <x:v>46122.244317963</x:v>
-      </x:c>
-      <x:c r="J50" s="30" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -5972,19 +5978,19 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -6010,19 +6016,19 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -6048,19 +6054,19 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -6080,10 +6086,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="29" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G54" s="29" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H54" s="31">
         <x:v>46124.1487218981</x:v>
@@ -6092,7 +6098,7 @@
         <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
@@ -6118,10 +6124,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="29" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G55" s="29" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H55" s="31">
         <x:v>46124.150742662</x:v>
@@ -6156,10 +6162,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G56" s="29" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H56" s="31">
         <x:v>46124.1512647338</x:v>
@@ -6168,7 +6174,7 @@
         <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
@@ -6194,10 +6200,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="29" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G57" s="29" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H57" s="31">
         <x:v>46124.1518079282</x:v>
@@ -6206,7 +6212,7 @@
         <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
@@ -6232,10 +6238,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G58" s="29" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H58" s="31">
         <x:v>46124.5490358102</x:v>
@@ -6244,7 +6250,7 @@
         <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
@@ -6270,25 +6276,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="29" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G59" s="29" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -6308,25 +6314,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G60" s="29" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
-        <x:v>181</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -6352,19 +6358,19 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -6384,10 +6390,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F62" s="29" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G62" s="29" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H62" s="31">
         <x:v>46124.7023532986</x:v>
@@ -6396,7 +6402,7 @@
         <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
@@ -6422,10 +6428,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="29" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G63" s="29" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H63" s="31">
         <x:v>46124.7029179398</x:v>
@@ -6434,7 +6440,7 @@
         <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
@@ -6460,10 +6466,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G64" s="29" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H64" s="31">
         <x:v>46124.7035032407</x:v>
@@ -6472,7 +6478,7 @@
         <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
@@ -6498,10 +6504,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F65" s="29" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G65" s="29" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H65" s="31">
         <x:v>46126.5341923727</x:v>
@@ -6536,10 +6542,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="29" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G66" s="29" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H66" s="31">
         <x:v>46127.1221474769</x:v>
@@ -6574,25 +6580,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="29" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G67" s="29" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
-        <x:v>199</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -6618,19 +6624,19 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -6656,19 +6662,19 @@
         <x:v>203</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
-        <x:v>204</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -6688,25 +6694,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G70" s="29" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="G70" s="29" t="s">
+      <x:c r="H70" s="31">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I70" s="31">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J70" s="30" t="s">
         <x:v>206</x:v>
-      </x:c>
-      <x:c r="H70" s="31">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I70" s="31">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J70" s="30" t="s">
-        <x:v>207</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -6726,25 +6732,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="29" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G71" s="29" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G71" s="29" t="s">
+      <x:c r="H71" s="31">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I71" s="31">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J71" s="30" t="s">
         <x:v>209</x:v>
-      </x:c>
-      <x:c r="H71" s="31">
-        <x:v>46122.3767795718</x:v>
-      </x:c>
-      <x:c r="I71" s="31">
-        <x:v>46122.3776183449</x:v>
-      </x:c>
-      <x:c r="J71" s="30" t="s">
-        <x:v>210</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -6764,10 +6770,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G72" s="29" t="s">
         <x:v>211</x:v>
-      </x:c>
-      <x:c r="G72" s="29" t="s">
-        <x:v>212</x:v>
       </x:c>
       <x:c r="H72" s="31">
         <x:v>46122.3879258681</x:v>
@@ -6802,25 +6808,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G73" s="29" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="G73" s="29" t="s">
-        <x:v>214</x:v>
-      </x:c>
       <x:c r="H73" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>215</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -6840,25 +6846,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G74" s="29" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H74" s="31">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I74" s="31">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J74" s="30" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="G74" s="29" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="H74" s="31">
-        <x:v>46122.3974322338</x:v>
-      </x:c>
-      <x:c r="I74" s="31">
-        <x:v>46122.3980999421</x:v>
-      </x:c>
-      <x:c r="J74" s="30" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -6878,10 +6884,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G75" s="29" t="s">
         <x:v>218</x:v>
-      </x:c>
-      <x:c r="G75" s="29" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="H75" s="31">
         <x:v>46122.5587807523</x:v>
@@ -6890,7 +6896,7 @@
         <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>220</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
@@ -6916,10 +6922,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F76" s="29" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G76" s="29" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="G76" s="29" t="s">
-        <x:v>222</x:v>
       </x:c>
       <x:c r="H76" s="31">
         <x:v>46122.5623107755</x:v>
@@ -6928,7 +6934,7 @@
         <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
@@ -6954,25 +6960,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G77" s="29" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G77" s="29" t="s">
+      <x:c r="H77" s="31">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I77" s="31">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J77" s="30" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="H77" s="31">
-        <x:v>46123.4162791088</x:v>
-      </x:c>
-      <x:c r="I77" s="31">
-        <x:v>46123.4173169792</x:v>
-      </x:c>
-      <x:c r="J77" s="30" t="s">
-        <x:v>225</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -6992,25 +6998,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G78" s="29" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="G78" s="29" t="s">
+      <x:c r="H78" s="31">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I78" s="31">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J78" s="30" t="s">
         <x:v>227</x:v>
-      </x:c>
-      <x:c r="H78" s="31">
-        <x:v>46122.5911383796</x:v>
-      </x:c>
-      <x:c r="I78" s="31">
-        <x:v>46122.5921380556</x:v>
-      </x:c>
-      <x:c r="J78" s="30" t="s">
-        <x:v>228</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -7030,25 +7036,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G79" s="29" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="G79" s="29" t="s">
-        <x:v>230</x:v>
-      </x:c>
       <x:c r="H79" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I79" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J79" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -7068,10 +7074,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G80" s="29" t="s">
         <x:v>231</x:v>
-      </x:c>
-      <x:c r="G80" s="29" t="s">
-        <x:v>232</x:v>
       </x:c>
       <x:c r="H80" s="31">
         <x:v>46122.6795081481</x:v>
@@ -7106,10 +7112,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G81" s="29" t="s">
         <x:v>233</x:v>
-      </x:c>
-      <x:c r="G81" s="29" t="s">
-        <x:v>234</x:v>
       </x:c>
       <x:c r="H81" s="31">
         <x:v>46122.6819179514</x:v>
@@ -7118,7 +7124,7 @@
         <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>235</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
@@ -7144,10 +7150,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G82" s="29" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="G82" s="29" t="s">
-        <x:v>237</x:v>
       </x:c>
       <x:c r="H82" s="31">
         <x:v>46122.7261372338</x:v>
@@ -7182,10 +7188,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G83" s="29" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="G83" s="29" t="s">
-        <x:v>239</x:v>
       </x:c>
       <x:c r="H83" s="31">
         <x:v>46122.9452935995</x:v>
@@ -7194,7 +7200,7 @@
         <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
@@ -7220,10 +7226,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G84" s="29" t="s">
         <x:v>241</x:v>
-      </x:c>
-      <x:c r="G84" s="29" t="s">
-        <x:v>242</x:v>
       </x:c>
       <x:c r="H84" s="31">
         <x:v>46123.0476912847</x:v>
@@ -7232,7 +7238,7 @@
         <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
-        <x:v>243</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
@@ -7258,25 +7264,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G85" s="29" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="G85" s="29" t="s">
+      <x:c r="H85" s="31">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I85" s="31">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J85" s="30" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="H85" s="31">
-        <x:v>46122.5945434491</x:v>
-      </x:c>
-      <x:c r="I85" s="31">
-        <x:v>46122.5999534606</x:v>
-      </x:c>
-      <x:c r="J85" s="30" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -7302,80 +7308,117 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B87" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C87" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D87" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E87" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F87" s="29" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G87" s="29" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="H87" s="31">
+        <x:v>46132.4200429282</x:v>
+      </x:c>
+      <x:c r="I87" s="31">
+        <x:v>46132.4214079282</x:v>
+      </x:c>
+      <x:c r="J87" s="30" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K87" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L87" s="33">
+        <x:v>46132.422405787</x:v>
+      </x:c>
+      <x:c r="M87" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="89" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B89" s="17" t="s">
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B90" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C89" s="18" t="s"/>
-      <x:c r="D89" s="18" t="s"/>
-      <x:c r="E89" s="19" t="s"/>
-      <x:c r="F89" s="19" t="s"/>
-    </x:row>
-    <x:row r="90" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B90" s="20" t="s">
+      <x:c r="C90" s="18" t="s"/>
+      <x:c r="D90" s="18" t="s"/>
+      <x:c r="E90" s="19" t="s"/>
+      <x:c r="F90" s="19" t="s"/>
+    </x:row>
+    <x:row r="91" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B91" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C90" s="21" t="s"/>
-      <x:c r="D90" s="21" t="s"/>
-      <x:c r="E90" s="21" t="s"/>
-      <x:c r="F90" s="22" t="s">
+      <x:c r="C91" s="21" t="s"/>
+      <x:c r="D91" s="21" t="s"/>
+      <x:c r="E91" s="21" t="s"/>
+      <x:c r="F91" s="22" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B91" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C91" s="24" t="s"/>
-      <x:c r="D91" s="24" t="s"/>
-      <x:c r="E91" s="24" t="s"/>
-      <x:c r="F91" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:28" ht="18" customHeight="1">
       <x:c r="B92" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C92" s="24" t="s"/>
       <x:c r="D92" s="24" t="s"/>
       <x:c r="E92" s="24" t="s"/>
       <x:c r="F92" s="25" t="n">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B93" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B93" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C93" s="24" t="s"/>
+      <x:c r="D93" s="24" t="s"/>
+      <x:c r="E93" s="24" t="s"/>
+      <x:c r="F93" s="25" t="n">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B94" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C93" s="27" t="s"/>
-      <x:c r="D93" s="27" t="s"/>
-      <x:c r="E93" s="27" t="s"/>
-      <x:c r="F93" s="28" t="n">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C94" s="27" t="s"/>
+      <x:c r="D94" s="27" t="s"/>
+      <x:c r="E94" s="27" t="s"/>
+      <x:c r="F94" s="28" t="n">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
     <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8281,11 +8324,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B89:F89"/>
-    <x:mergeCell ref="B90:E90"/>
+    <x:mergeCell ref="B90:F90"/>
     <x:mergeCell ref="B91:E91"/>
     <x:mergeCell ref="B92:E92"/>
     <x:mergeCell ref="B93:E93"/>
+    <x:mergeCell ref="B94:E94"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="250">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="252">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -149,6 +149,15 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1316-566</x:t>
+  </x:si>
+  <x:si>
+    <x:t>szdasdqweq</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08281</x:t>
   </x:si>
   <x:si>
@@ -194,13 +203,10 @@
     <x:t>asdxzcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08219</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1316-566</x:t>
-  </x:si>
-  <x:si>
-    <x:t>szdasdqweq</x:t>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08339</x:t>
@@ -212,6 +218,15 @@
     <x:t>123qweasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1326-920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08340</x:t>
   </x:si>
   <x:si>
@@ -221,13 +236,49 @@
     <x:t>aszxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08338</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1326-920</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe</x:t>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
@@ -239,51 +290,6 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08138</x:t>
   </x:si>
   <x:si>
@@ -311,43 +317,187 @@
     <x:t>zxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
@@ -356,424 +506,280 @@
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08172</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08625</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1344-095</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4382,19 +4388,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="31">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46124.9835281713</x:v>
       </x:c>
       <x:c r="I9" s="31">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46125.0608962963</x:v>
       </x:c>
       <x:c r="J9" s="30" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="K9" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L9" s="33">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.1641622569</x:v>
       </x:c>
       <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
@@ -4420,10 +4426,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I10" s="31">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J10" s="30" t="s">
         <x:v>46</x:v>
@@ -4432,7 +4438,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
@@ -4458,10 +4464,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I11" s="31">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J11" s="30" t="s">
         <x:v>49</x:v>
@@ -4470,7 +4476,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
@@ -4496,10 +4502,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46126.4381590509</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>46126.4434486343</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J12" s="30" t="s">
         <x:v>52</x:v>
@@ -4508,7 +4514,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46126.444417662</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
@@ -4534,10 +4540,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>46126.4485157523</x:v>
+        <x:v>46126.4381590509</x:v>
       </x:c>
       <x:c r="I13" s="31">
-        <x:v>46126.4527227431</x:v>
+        <x:v>46126.4434486343</x:v>
       </x:c>
       <x:c r="J13" s="30" t="s">
         <x:v>55</x:v>
@@ -4546,7 +4552,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>46126.4533495949</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
@@ -4572,19 +4578,19 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H14" s="31">
-        <x:v>46124.9835281713</x:v>
+        <x:v>46126.4485157523</x:v>
       </x:c>
       <x:c r="I14" s="31">
-        <x:v>46125.0608962963</x:v>
+        <x:v>46126.4527227431</x:v>
       </x:c>
       <x:c r="J14" s="30" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="K14" s="32" t="n">
-        <x:v>240</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="33">
-        <x:v>46126.1641622569</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
@@ -4610,19 +4616,19 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46133.5419909606</x:v>
       </x:c>
       <x:c r="I15" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46133.5429334722</x:v>
       </x:c>
       <x:c r="J15" s="30" t="s">
-        <x:v>61</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K15" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46133.5457238194</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
         <x:v>21</x:v>
@@ -4642,25 +4648,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="29" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G16" s="29" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G16" s="29" t="s">
+      <x:c r="H16" s="31">
+        <x:v>46126.4716621296</x:v>
+      </x:c>
+      <x:c r="I16" s="31">
+        <x:v>46126.4737503704</x:v>
+      </x:c>
+      <x:c r="J16" s="30" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="H16" s="31">
-        <x:v>46126.4798427199</x:v>
-      </x:c>
-      <x:c r="I16" s="31">
-        <x:v>46126.4809562153</x:v>
-      </x:c>
-      <x:c r="J16" s="30" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="K16" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
@@ -4680,10 +4686,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="29" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G17" s="29" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="G17" s="29" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="H17" s="31">
         <x:v>46126.455832662</x:v>
@@ -4692,7 +4698,7 @@
         <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K17" s="32" t="n">
         <x:v>210</x:v>
@@ -4709,34 +4715,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D18" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="29" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G18" s="29" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G18" s="29" t="s">
+      <x:c r="H18" s="31">
+        <x:v>46126.4798427199</x:v>
+      </x:c>
+      <x:c r="I18" s="31">
+        <x:v>46126.4809562153</x:v>
+      </x:c>
+      <x:c r="J18" s="30" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="H18" s="31">
-        <x:v>46119.8029380671</x:v>
-      </x:c>
-      <x:c r="I18" s="31">
-        <x:v>46120.5237086343</x:v>
-      </x:c>
-      <x:c r="J18" s="30" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
@@ -4756,10 +4762,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="29" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G19" s="29" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="G19" s="29" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="H19" s="31">
         <x:v>46120.2349196412</x:v>
@@ -4768,7 +4774,7 @@
         <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J19" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K19" s="32" t="n">
         <x:v>0</x:v>
@@ -4794,10 +4800,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="29" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G20" s="29" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="G20" s="29" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="H20" s="31">
         <x:v>46120.2362105324</x:v>
@@ -4806,7 +4812,7 @@
         <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J20" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K20" s="32" t="n">
         <x:v>210</x:v>
@@ -4832,10 +4838,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G21" s="29" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="G21" s="29" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="31">
         <x:v>46120.2374046412</x:v>
@@ -4844,7 +4850,7 @@
         <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
         <x:v>210</x:v>
@@ -4870,10 +4876,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G22" s="29" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="G22" s="29" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="H22" s="31">
         <x:v>46120.7129542245</x:v>
@@ -4908,10 +4914,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G23" s="29" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="G23" s="29" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="H23" s="31">
         <x:v>46121.0999663542</x:v>
@@ -4920,7 +4926,7 @@
         <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J23" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
@@ -4946,10 +4952,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F24" s="29" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G24" s="29" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="G24" s="29" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="H24" s="31">
         <x:v>46121.2273626852</x:v>
@@ -4984,25 +4990,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="29" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G25" s="29" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G25" s="29" t="s">
+      <x:c r="H25" s="31">
+        <x:v>46119.8029380671</x:v>
+      </x:c>
+      <x:c r="I25" s="31">
+        <x:v>46120.5237086343</x:v>
+      </x:c>
+      <x:c r="J25" s="30" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="H25" s="31">
-        <x:v>46121.2464636111</x:v>
-      </x:c>
-      <x:c r="I25" s="31">
-        <x:v>46121.3217277662</x:v>
-      </x:c>
-      <x:c r="J25" s="30" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -5022,25 +5028,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="29" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G26" s="29" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G26" s="29" t="s">
+      <x:c r="H26" s="31">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I26" s="31">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J26" s="30" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="H26" s="31">
-        <x:v>46121.5149441551</x:v>
-      </x:c>
-      <x:c r="I26" s="31">
-        <x:v>46122.2067431944</x:v>
-      </x:c>
-      <x:c r="J26" s="30" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -5060,25 +5066,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="29" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G27" s="29" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G27" s="29" t="s">
+      <x:c r="H27" s="31">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I27" s="31">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J27" s="30" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="H27" s="31">
-        <x:v>46121.5178724884</x:v>
-      </x:c>
-      <x:c r="I27" s="31">
-        <x:v>46122.2064690394</x:v>
-      </x:c>
-      <x:c r="J27" s="30" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -5098,25 +5104,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="29" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G28" s="29" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G28" s="29" t="s">
+      <x:c r="H28" s="31">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I28" s="31">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J28" s="30" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="H28" s="31">
-        <x:v>46119.8023724884</x:v>
-      </x:c>
-      <x:c r="I28" s="31">
-        <x:v>46119.8046602662</x:v>
-      </x:c>
-      <x:c r="J28" s="30" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -5142,10 +5148,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="H29" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I29" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
         <x:v>99</x:v>
@@ -5154,7 +5160,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -5186,7 +5192,7 @@
         <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
@@ -5218,10 +5224,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H31" s="31">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
         <x:v>104</x:v>
@@ -5230,7 +5236,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -5256,19 +5262,19 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
-        <x:v>107</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
@@ -5288,25 +5294,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="29" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G33" s="29" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G33" s="29" t="s">
+      <x:c r="H33" s="31">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I33" s="31">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J33" s="30" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="H33" s="31">
-        <x:v>46119.8017436343</x:v>
-      </x:c>
-      <x:c r="I33" s="31">
-        <x:v>46119.8048384144</x:v>
-      </x:c>
-      <x:c r="J33" s="30" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -5332,10 +5338,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
         <x:v>112</x:v>
@@ -5344,7 +5350,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -5370,19 +5376,19 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
@@ -5402,25 +5408,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="29" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G36" s="29" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G36" s="29" t="s">
-        <x:v>117</x:v>
-      </x:c>
       <x:c r="H36" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -5440,10 +5446,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F37" s="29" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G37" s="29" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H37" s="31">
         <x:v>46118.7424944097</x:v>
@@ -5452,7 +5458,7 @@
         <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
@@ -5478,10 +5484,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G38" s="29" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H38" s="31">
         <x:v>46118.7562945255</x:v>
@@ -5490,7 +5496,7 @@
         <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
@@ -5516,10 +5522,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G39" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H39" s="31">
         <x:v>46119.0668949653</x:v>
@@ -5528,7 +5534,7 @@
         <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
@@ -5554,10 +5560,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G40" s="29" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H40" s="31">
         <x:v>46119.0739296412</x:v>
@@ -5566,7 +5572,7 @@
         <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
@@ -5592,10 +5598,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G41" s="29" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H41" s="31">
         <x:v>46119.1921340856</x:v>
@@ -5604,7 +5610,7 @@
         <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
@@ -5630,25 +5636,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G42" s="29" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H42" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I42" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -5668,16 +5674,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G43" s="29" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H43" s="31">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I43" s="31">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
         <x:v>28</x:v>
@@ -5686,7 +5692,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -5706,25 +5712,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G44" s="29" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H44" s="31">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I44" s="31">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J44" s="30" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="G44" s="29" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H44" s="31">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I44" s="31">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J44" s="30" t="s">
-        <x:v>140</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -5744,10 +5750,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F45" s="29" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G45" s="29" t="s">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H45" s="31">
         <x:v>46119.542956794</x:v>
@@ -5756,7 +5762,7 @@
         <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J45" s="30" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
@@ -5782,10 +5788,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="29" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G46" s="29" t="s">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H46" s="31">
         <x:v>46119.5434206134</x:v>
@@ -5794,7 +5800,7 @@
         <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
@@ -5820,25 +5826,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="29" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G47" s="29" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H47" s="31">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I47" s="31">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J47" s="30" t="s">
         <x:v>147</x:v>
-      </x:c>
-      <x:c r="G47" s="29" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="H47" s="31">
-        <x:v>46122.2429836343</x:v>
-      </x:c>
-      <x:c r="I47" s="31">
-        <x:v>46122.244317963</x:v>
-      </x:c>
-      <x:c r="J47" s="30" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -5858,10 +5864,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="29" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G48" s="29" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="G48" s="29" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="H48" s="31">
         <x:v>46119.7254171991</x:v>
@@ -5870,7 +5876,7 @@
         <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
@@ -5896,10 +5902,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F49" s="29" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G49" s="29" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="G49" s="29" t="s">
-        <x:v>152</x:v>
       </x:c>
       <x:c r="H49" s="31">
         <x:v>46119.7285584838</x:v>
@@ -5908,7 +5914,7 @@
         <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
@@ -5934,25 +5940,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="29" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G50" s="29" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G50" s="29" t="s">
+      <x:c r="H50" s="31">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I50" s="31">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J50" s="30" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="H50" s="31">
-        <x:v>46119.5267212153</x:v>
-      </x:c>
-      <x:c r="I50" s="31">
-        <x:v>46119.5274664236</x:v>
-      </x:c>
-      <x:c r="J50" s="30" t="s">
-        <x:v>155</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -5972,25 +5978,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F51" s="29" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G51" s="29" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="G51" s="29" t="s">
+      <x:c r="H51" s="31">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I51" s="31">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J51" s="30" t="s">
         <x:v>157</x:v>
-      </x:c>
-      <x:c r="H51" s="31">
-        <x:v>46122.3569147569</x:v>
-      </x:c>
-      <x:c r="I51" s="31">
-        <x:v>46122.3577305324</x:v>
-      </x:c>
-      <x:c r="J51" s="30" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -6016,19 +6022,19 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -6054,19 +6060,19 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>162</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -6086,25 +6092,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="29" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G54" s="29" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="G54" s="29" t="s">
-        <x:v>164</x:v>
-      </x:c>
       <x:c r="H54" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>165</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
@@ -6124,10 +6130,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="29" t="s">
-        <x:v>166</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G55" s="29" t="s">
-        <x:v>167</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H55" s="31">
         <x:v>46124.150742662</x:v>
@@ -6136,7 +6142,7 @@
         <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
@@ -6162,10 +6168,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
-        <x:v>168</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G56" s="29" t="s">
-        <x:v>169</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H56" s="31">
         <x:v>46124.1512647338</x:v>
@@ -6174,7 +6180,7 @@
         <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
@@ -6200,10 +6206,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="29" t="s">
-        <x:v>171</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G57" s="29" t="s">
-        <x:v>172</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H57" s="31">
         <x:v>46124.1518079282</x:v>
@@ -6212,7 +6218,7 @@
         <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
@@ -6238,10 +6244,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="29" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G58" s="29" t="s">
-        <x:v>175</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H58" s="31">
         <x:v>46124.5490358102</x:v>
@@ -6250,7 +6256,7 @@
         <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>176</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
@@ -6276,10 +6282,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="29" t="s">
-        <x:v>177</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G59" s="29" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H59" s="31">
         <x:v>46124.6761778356</x:v>
@@ -6288,7 +6294,7 @@
         <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>179</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
@@ -6314,25 +6320,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G60" s="29" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H60" s="31">
+        <x:v>46124.6975491551</x:v>
+      </x:c>
+      <x:c r="I60" s="31">
+        <x:v>46124.6983328357</x:v>
+      </x:c>
+      <x:c r="J60" s="30" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="G60" s="29" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="H60" s="31">
-        <x:v>46124.1449755903</x:v>
-      </x:c>
-      <x:c r="I60" s="31">
-        <x:v>46124.1465040046</x:v>
-      </x:c>
-      <x:c r="J60" s="30" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -6352,25 +6358,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F61" s="29" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G61" s="29" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="G61" s="29" t="s">
+      <x:c r="H61" s="31">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I61" s="31">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J61" s="30" t="s">
         <x:v>183</x:v>
-      </x:c>
-      <x:c r="H61" s="31">
-        <x:v>46124.6975491551</x:v>
-      </x:c>
-      <x:c r="I61" s="31">
-        <x:v>46124.6983328357</x:v>
-      </x:c>
-      <x:c r="J61" s="30" t="s">
-        <x:v>184</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -6390,25 +6396,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F62" s="29" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G62" s="29" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="G62" s="29" t="s">
-        <x:v>186</x:v>
-      </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
-        <x:v>187</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -6428,10 +6434,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="29" t="s">
-        <x:v>188</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G63" s="29" t="s">
-        <x:v>189</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="H63" s="31">
         <x:v>46124.7029179398</x:v>
@@ -6440,7 +6446,7 @@
         <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
-        <x:v>190</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
@@ -6466,10 +6472,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
-        <x:v>191</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G64" s="29" t="s">
-        <x:v>192</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H64" s="31">
         <x:v>46124.7035032407</x:v>
@@ -6478,7 +6484,7 @@
         <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
-        <x:v>193</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
@@ -6504,25 +6510,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F65" s="29" t="s">
-        <x:v>194</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="G65" s="29" t="s">
-        <x:v>195</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H65" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I65" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J65" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
@@ -6542,16 +6548,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="29" t="s">
-        <x:v>196</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G66" s="29" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
         <x:v>28</x:v>
@@ -6560,7 +6566,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -6580,16 +6586,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="29" t="s">
-        <x:v>198</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G67" s="29" t="s">
-        <x:v>199</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
         <x:v>28</x:v>
@@ -6598,7 +6604,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -6618,25 +6624,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="29" t="s">
-        <x:v>200</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G68" s="29" t="s">
-        <x:v>201</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -6656,25 +6662,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="29" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G69" s="29" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H69" s="31">
+        <x:v>46124.7023532986</x:v>
+      </x:c>
+      <x:c r="I69" s="31">
+        <x:v>46124.7048005093</x:v>
+      </x:c>
+      <x:c r="J69" s="30" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="G69" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="H69" s="31">
-        <x:v>46122.36782125</x:v>
-      </x:c>
-      <x:c r="I69" s="31">
-        <x:v>46122.3686719907</x:v>
-      </x:c>
-      <x:c r="J69" s="30" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -6694,25 +6700,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G70" s="29" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="G70" s="29" t="s">
+      <x:c r="H70" s="31">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I70" s="31">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J70" s="30" t="s">
         <x:v>205</x:v>
-      </x:c>
-      <x:c r="H70" s="31">
-        <x:v>46124.1410094907</x:v>
-      </x:c>
-      <x:c r="I70" s="31">
-        <x:v>46124.1426461806</x:v>
-      </x:c>
-      <x:c r="J70" s="30" t="s">
-        <x:v>206</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -6732,25 +6738,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="29" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G71" s="29" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="G71" s="29" t="s">
-        <x:v>208</x:v>
-      </x:c>
       <x:c r="H71" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
-        <x:v>209</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -6770,25 +6776,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G72" s="29" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H72" s="31">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I72" s="31">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J72" s="30" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="G72" s="29" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="H72" s="31">
-        <x:v>46122.3879258681</x:v>
-      </x:c>
-      <x:c r="I72" s="31">
-        <x:v>46122.3894281713</x:v>
-      </x:c>
-      <x:c r="J72" s="30" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
@@ -6808,10 +6814,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G73" s="29" t="s">
         <x:v>212</x:v>
-      </x:c>
-      <x:c r="G73" s="29" t="s">
-        <x:v>213</x:v>
       </x:c>
       <x:c r="H73" s="31">
         <x:v>46122.3885020718</x:v>
@@ -6820,7 +6826,7 @@
         <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
@@ -6846,10 +6852,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G74" s="29" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="G74" s="29" t="s">
-        <x:v>215</x:v>
       </x:c>
       <x:c r="H74" s="31">
         <x:v>46118.3446055671</x:v>
@@ -6858,7 +6864,7 @@
         <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
@@ -6884,10 +6890,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G75" s="29" t="s">
         <x:v>217</x:v>
-      </x:c>
-      <x:c r="G75" s="29" t="s">
-        <x:v>218</x:v>
       </x:c>
       <x:c r="H75" s="31">
         <x:v>46122.5587807523</x:v>
@@ -6896,7 +6902,7 @@
         <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>219</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
@@ -6922,10 +6928,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F76" s="29" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G76" s="29" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="G76" s="29" t="s">
-        <x:v>221</x:v>
       </x:c>
       <x:c r="H76" s="31">
         <x:v>46122.5623107755</x:v>
@@ -6934,7 +6940,7 @@
         <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>155</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
@@ -6960,10 +6966,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G77" s="29" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="G77" s="29" t="s">
-        <x:v>223</x:v>
       </x:c>
       <x:c r="H77" s="31">
         <x:v>46122.5911383796</x:v>
@@ -6972,7 +6978,7 @@
         <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
@@ -6998,25 +7004,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G78" s="29" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="G78" s="29" t="s">
-        <x:v>226</x:v>
-      </x:c>
       <x:c r="H78" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I78" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J78" s="30" t="s">
-        <x:v>227</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -7036,25 +7042,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G79" s="29" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H79" s="31">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I79" s="31">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J79" s="30" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="G79" s="29" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="H79" s="31">
-        <x:v>46122.5945434491</x:v>
-      </x:c>
-      <x:c r="I79" s="31">
-        <x:v>46122.5999534606</x:v>
-      </x:c>
-      <x:c r="J79" s="30" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -7074,25 +7080,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G80" s="29" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="G80" s="29" t="s">
-        <x:v>231</x:v>
-      </x:c>
       <x:c r="H80" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -7112,10 +7118,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G81" s="29" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="G81" s="29" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="H81" s="31">
         <x:v>46122.6819179514</x:v>
@@ -7124,7 +7130,7 @@
         <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>234</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
@@ -7150,10 +7156,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G82" s="29" t="s">
         <x:v>235</x:v>
-      </x:c>
-      <x:c r="G82" s="29" t="s">
-        <x:v>236</x:v>
       </x:c>
       <x:c r="H82" s="31">
         <x:v>46122.7261372338</x:v>
@@ -7188,10 +7194,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G83" s="29" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="G83" s="29" t="s">
-        <x:v>238</x:v>
       </x:c>
       <x:c r="H83" s="31">
         <x:v>46122.9452935995</x:v>
@@ -7200,7 +7206,7 @@
         <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
@@ -7226,10 +7232,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G84" s="29" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="G84" s="29" t="s">
-        <x:v>241</x:v>
       </x:c>
       <x:c r="H84" s="31">
         <x:v>46123.0476912847</x:v>
@@ -7238,7 +7244,7 @@
         <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
-        <x:v>242</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
@@ -7264,10 +7270,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G85" s="29" t="s">
         <x:v>243</x:v>
-      </x:c>
-      <x:c r="G85" s="29" t="s">
-        <x:v>244</x:v>
       </x:c>
       <x:c r="H85" s="31">
         <x:v>46123.061368912</x:v>
@@ -7276,7 +7282,7 @@
         <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
@@ -7302,25 +7308,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F86" s="29" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G86" s="29" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="G86" s="29" t="s">
+      <x:c r="H86" s="31">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I86" s="31">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J86" s="30" t="s">
         <x:v>247</x:v>
-      </x:c>
-      <x:c r="H86" s="31">
-        <x:v>46122.6182774306</x:v>
-      </x:c>
-      <x:c r="I86" s="31">
-        <x:v>46122.6193276968</x:v>
-      </x:c>
-      <x:c r="J86" s="30" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -7346,80 +7352,117 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="H87" s="31">
-        <x:v>46132.4200429282</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46132.4214079282</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B88" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C88" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D88" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E88" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F88" s="29" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G88" s="29" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="H88" s="31">
+        <x:v>46122.3974322338</x:v>
+      </x:c>
+      <x:c r="I88" s="31">
+        <x:v>46122.3980999421</x:v>
+      </x:c>
+      <x:c r="J88" s="30" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K88" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L88" s="33">
+        <x:v>46122.398526713</x:v>
+      </x:c>
+      <x:c r="M88" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="90" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B90" s="17" t="s">
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B91" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C90" s="18" t="s"/>
-      <x:c r="D90" s="18" t="s"/>
-      <x:c r="E90" s="19" t="s"/>
-      <x:c r="F90" s="19" t="s"/>
-    </x:row>
-    <x:row r="91" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B91" s="20" t="s">
+      <x:c r="C91" s="18" t="s"/>
+      <x:c r="D91" s="18" t="s"/>
+      <x:c r="E91" s="19" t="s"/>
+      <x:c r="F91" s="19" t="s"/>
+    </x:row>
+    <x:row r="92" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B92" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C91" s="21" t="s"/>
-      <x:c r="D91" s="21" t="s"/>
-      <x:c r="E91" s="21" t="s"/>
-      <x:c r="F91" s="22" t="s">
+      <x:c r="C92" s="21" t="s"/>
+      <x:c r="D92" s="21" t="s"/>
+      <x:c r="E92" s="21" t="s"/>
+      <x:c r="F92" s="22" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B92" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C92" s="24" t="s"/>
-      <x:c r="D92" s="24" t="s"/>
-      <x:c r="E92" s="24" t="s"/>
-      <x:c r="F92" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:28" ht="18" customHeight="1">
       <x:c r="B93" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C93" s="24" t="s"/>
       <x:c r="D93" s="24" t="s"/>
       <x:c r="E93" s="24" t="s"/>
       <x:c r="F93" s="25" t="n">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B94" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B94" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C94" s="24" t="s"/>
+      <x:c r="D94" s="24" t="s"/>
+      <x:c r="E94" s="24" t="s"/>
+      <x:c r="F94" s="25" t="n">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B95" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C94" s="27" t="s"/>
-      <x:c r="D94" s="27" t="s"/>
-      <x:c r="E94" s="27" t="s"/>
-      <x:c r="F94" s="28" t="n">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C95" s="27" t="s"/>
+      <x:c r="D95" s="27" t="s"/>
+      <x:c r="E95" s="27" t="s"/>
+      <x:c r="F95" s="28" t="n">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
     <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8324,11 +8367,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B90:F90"/>
-    <x:mergeCell ref="B91:E91"/>
+    <x:mergeCell ref="B91:F91"/>
     <x:mergeCell ref="B92:E92"/>
     <x:mergeCell ref="B93:E93"/>
     <x:mergeCell ref="B94:E94"/>
+    <x:mergeCell ref="B95:E95"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="252">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -203,6 +203,39 @@
     <x:t>asdxzcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1326-920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08729</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1347-280</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08682</x:t>
   </x:si>
   <x:si>
@@ -218,22 +251,13 @@
     <x:t>123qweasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08338</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1326-920</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1328-100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aszxcasd</x:t>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08117</x:t>
@@ -281,13 +305,61 @@
     <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasd</x:t>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08138</x:t>
@@ -299,61 +371,25 @@
     <x:t>cxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08033</x:t>
@@ -365,18 +401,6 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08043</x:t>
   </x:si>
   <x:si>
@@ -422,88 +446,211 @@
     <x:t>asdqwe123</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08087</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1238-244</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08160</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1279-279</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08163</x:t>
@@ -512,138 +659,6 @@
     <x:t>61-4-2026-1280-364</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08625</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1344-095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08188</x:t>
   </x:si>
   <x:si>
@@ -665,6 +680,12 @@
     <x:t>61-4-2026-1283-909</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -674,6 +695,99 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08173</x:t>
   </x:si>
   <x:si>
@@ -681,105 +795,6 @@
   </x:si>
   <x:si>
     <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4616,19 +4631,19 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46133.5419909606</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I15" s="31">
-        <x:v>46133.5429334722</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J15" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K15" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46133.5457238194</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
         <x:v>21</x:v>
@@ -4648,25 +4663,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="29" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G16" s="29" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46134.4519824769</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46134.4543351736</x:v>
       </x:c>
       <x:c r="J16" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K16" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46134.4551470833</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
@@ -4692,10 +4707,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46126.455832662</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>46126.4740829051</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
         <x:v>66</x:v>
@@ -4704,7 +4719,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
@@ -4730,19 +4745,19 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="H18" s="31">
-        <x:v>46126.4798427199</x:v>
+        <x:v>46133.0575652778</x:v>
       </x:c>
       <x:c r="I18" s="31">
-        <x:v>46126.4809562153</x:v>
+        <x:v>46134.4546264699</x:v>
       </x:c>
       <x:c r="J18" s="30" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46134.4615905556</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
@@ -4753,13 +4768,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D19" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E19" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="29" t="s">
         <x:v>70</x:v>
@@ -4768,19 +4783,19 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H19" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46133.5419909606</x:v>
       </x:c>
       <x:c r="I19" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46133.5429334722</x:v>
       </x:c>
       <x:c r="J19" s="30" t="s">
-        <x:v>72</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K19" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46133.5457238194</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>21</x:v>
@@ -4791,34 +4806,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D20" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E20" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="29" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G20" s="29" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G20" s="29" t="s">
+      <x:c r="H20" s="31">
+        <x:v>46126.4716621296</x:v>
+      </x:c>
+      <x:c r="I20" s="31">
+        <x:v>46126.4737503704</x:v>
+      </x:c>
+      <x:c r="J20" s="30" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="H20" s="31">
-        <x:v>46120.2362105324</x:v>
-      </x:c>
-      <x:c r="I20" s="31">
-        <x:v>46120.5226826273</x:v>
-      </x:c>
-      <x:c r="J20" s="30" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="K20" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>21</x:v>
@@ -4844,10 +4859,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H21" s="31">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
         <x:v>77</x:v>
@@ -4856,7 +4871,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>21</x:v>
@@ -4882,19 +4897,19 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H22" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I22" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J22" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
         <x:v>21</x:v>
@@ -4914,25 +4929,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G23" s="29" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H23" s="31">
+        <x:v>46120.2362105324</x:v>
+      </x:c>
+      <x:c r="I23" s="31">
+        <x:v>46120.5226826273</x:v>
+      </x:c>
+      <x:c r="J23" s="30" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="G23" s="29" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H23" s="31">
-        <x:v>46121.0999663542</x:v>
-      </x:c>
-      <x:c r="I23" s="31">
-        <x:v>46121.1007466204</x:v>
-      </x:c>
-      <x:c r="J23" s="30" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
@@ -4958,19 +4973,19 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
@@ -4990,25 +5005,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="29" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G25" s="29" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -5034,10 +5049,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
         <x:v>90</x:v>
@@ -5046,7 +5061,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -5072,19 +5087,19 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
-        <x:v>93</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -5104,25 +5119,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="29" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G28" s="29" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G28" s="29" t="s">
+      <x:c r="H28" s="31">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I28" s="31">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J28" s="30" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="H28" s="31">
-        <x:v>46121.5178724884</x:v>
-      </x:c>
-      <x:c r="I28" s="31">
-        <x:v>46122.2064690394</x:v>
-      </x:c>
-      <x:c r="J28" s="30" t="s">
-        <x:v>96</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -5142,25 +5157,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="29" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G29" s="29" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G29" s="29" t="s">
+      <x:c r="H29" s="31">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I29" s="31">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J29" s="30" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="H29" s="31">
-        <x:v>46121.5183984954</x:v>
-      </x:c>
-      <x:c r="I29" s="31">
-        <x:v>46122.2061737153</x:v>
-      </x:c>
-      <x:c r="J29" s="30" t="s">
-        <x:v>99</x:v>
       </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -5180,25 +5195,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="29" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G30" s="29" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G30" s="29" t="s">
+      <x:c r="H30" s="31">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I30" s="31">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J30" s="30" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="H30" s="31">
-        <x:v>46122.1299166204</x:v>
-      </x:c>
-      <x:c r="I30" s="31">
-        <x:v>46122.2059087963</x:v>
-      </x:c>
-      <x:c r="J30" s="30" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -5224,10 +5239,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H31" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
         <x:v>104</x:v>
@@ -5236,7 +5251,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -5262,10 +5277,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
         <x:v>77</x:v>
@@ -5274,7 +5289,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
@@ -5300,10 +5315,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
         <x:v>109</x:v>
@@ -5312,7 +5327,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -5338,19 +5353,19 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -5370,25 +5385,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="29" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G35" s="29" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G35" s="29" t="s">
+      <x:c r="H35" s="31">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I35" s="31">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J35" s="30" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="H35" s="31">
-        <x:v>46119.8023724884</x:v>
-      </x:c>
-      <x:c r="I35" s="31">
-        <x:v>46119.8046602662</x:v>
-      </x:c>
-      <x:c r="J35" s="30" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
@@ -5414,19 +5429,19 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>72</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -5452,19 +5467,19 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
@@ -5484,25 +5499,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G38" s="29" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G38" s="29" t="s">
+      <x:c r="H38" s="31">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I38" s="31">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J38" s="30" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="H38" s="31">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I38" s="31">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J38" s="30" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
@@ -5522,25 +5537,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G39" s="29" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G39" s="29" t="s">
+      <x:c r="H39" s="31">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I39" s="31">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J39" s="30" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="H39" s="31">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I39" s="31">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J39" s="30" t="s">
-        <x:v>125</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
@@ -5560,25 +5575,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G40" s="29" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="G40" s="29" t="s">
+      <x:c r="H40" s="31">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I40" s="31">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J40" s="30" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="H40" s="31">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I40" s="31">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J40" s="30" t="s">
-        <x:v>128</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
@@ -5598,25 +5613,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G41" s="29" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="G41" s="29" t="s">
+      <x:c r="H41" s="31">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I41" s="31">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J41" s="30" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="H41" s="31">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I41" s="31">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J41" s="30" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
@@ -5636,25 +5651,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G42" s="29" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="G42" s="29" t="s">
+      <x:c r="H42" s="31">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I42" s="31">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J42" s="30" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="H42" s="31">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I42" s="31">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J42" s="30" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -5680,19 +5695,19 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="H43" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I43" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -5712,25 +5727,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G44" s="29" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="H44" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I44" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -5750,25 +5765,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F45" s="29" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G45" s="29" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H45" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I45" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J45" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -5794,19 +5809,19 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="H46" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
@@ -5826,25 +5841,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="29" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G47" s="29" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G47" s="29" t="s">
+      <x:c r="H47" s="31">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I47" s="31">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J47" s="30" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="H47" s="31">
-        <x:v>46119.5439653357</x:v>
-      </x:c>
-      <x:c r="I47" s="31">
-        <x:v>46119.5452984143</x:v>
-      </x:c>
-      <x:c r="J47" s="30" t="s">
-        <x:v>147</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -5864,25 +5879,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="29" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G48" s="29" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="G48" s="29" t="s">
+      <x:c r="H48" s="31">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I48" s="31">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J48" s="30" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="H48" s="31">
-        <x:v>46119.7254171991</x:v>
-      </x:c>
-      <x:c r="I48" s="31">
-        <x:v>46119.7262936574</x:v>
-      </x:c>
-      <x:c r="J48" s="30" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -5908,19 +5923,19 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -5940,25 +5955,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="29" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G50" s="29" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H50" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I50" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -5978,25 +5993,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F51" s="29" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G51" s="29" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
-        <x:v>157</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -6022,19 +6037,19 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -6060,19 +6075,19 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -6092,25 +6107,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="29" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G54" s="29" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>72</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
@@ -6130,25 +6145,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="29" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G55" s="29" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46124.150742662</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46124.153253125</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>72</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
@@ -6168,25 +6183,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G56" s="29" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>168</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -6206,25 +6221,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="29" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G57" s="29" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>171</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
@@ -6250,10 +6265,10 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
         <x:v>174</x:v>
@@ -6262,7 +6277,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
@@ -6288,10 +6303,10 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
         <x:v>177</x:v>
@@ -6300,7 +6315,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -6326,10 +6341,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
         <x:v>180</x:v>
@@ -6338,7 +6353,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -6364,10 +6379,10 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
         <x:v>183</x:v>
@@ -6376,7 +6391,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -6402,19 +6417,19 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -6434,25 +6449,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="29" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="G63" s="29" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
@@ -6472,25 +6487,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G64" s="29" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="H64" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I64" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
-        <x:v>191</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
@@ -6516,19 +6531,19 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H65" s="31">
-        <x:v>46132.4200429282</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I65" s="31">
-        <x:v>46132.4214079282</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J65" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
@@ -6548,25 +6563,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="29" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G66" s="29" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -6586,25 +6601,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="29" t="s">
-        <x:v>196</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G67" s="29" t="s">
-        <x:v>197</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -6624,16 +6639,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="29" t="s">
-        <x:v>198</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G68" s="29" t="s">
-        <x:v>199</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
         <x:v>28</x:v>
@@ -6642,7 +6657,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -6662,25 +6677,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="29" t="s">
-        <x:v>200</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G69" s="29" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
-        <x:v>202</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -6700,25 +6715,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G70" s="29" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H70" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
-        <x:v>205</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -6744,19 +6759,19 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="H71" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
-        <x:v>72</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -6776,25 +6791,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="G72" s="29" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="H72" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>210</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
@@ -6820,19 +6835,19 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -6858,10 +6873,10 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
         <x:v>215</x:v>
@@ -6870,7 +6885,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -6896,19 +6911,19 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="H75" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>218</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
@@ -6928,25 +6943,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F76" s="29" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G76" s="29" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G76" s="29" t="s">
-        <x:v>220</x:v>
-      </x:c>
       <x:c r="H76" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
@@ -6966,25 +6981,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G77" s="29" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="G77" s="29" t="s">
+      <x:c r="H77" s="31">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I77" s="31">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J77" s="30" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="H77" s="31">
-        <x:v>46122.5911383796</x:v>
-      </x:c>
-      <x:c r="I77" s="31">
-        <x:v>46122.5921380556</x:v>
-      </x:c>
-      <x:c r="J77" s="30" t="s">
-        <x:v>223</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -7004,25 +7019,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G78" s="29" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G78" s="29" t="s">
-        <x:v>225</x:v>
-      </x:c>
       <x:c r="H78" s="31">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I78" s="31">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J78" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -7042,25 +7057,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G79" s="29" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="G79" s="29" t="s">
+      <x:c r="H79" s="31">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I79" s="31">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J79" s="30" t="s">
         <x:v>227</x:v>
-      </x:c>
-      <x:c r="H79" s="31">
-        <x:v>46124.1410094907</x:v>
-      </x:c>
-      <x:c r="I79" s="31">
-        <x:v>46124.1426461806</x:v>
-      </x:c>
-      <x:c r="J79" s="30" t="s">
-        <x:v>228</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -7080,25 +7095,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G80" s="29" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="G80" s="29" t="s">
-        <x:v>230</x:v>
-      </x:c>
       <x:c r="H80" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>72</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -7118,25 +7133,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G81" s="29" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="G81" s="29" t="s">
+      <x:c r="H81" s="31">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I81" s="31">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J81" s="30" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="H81" s="31">
-        <x:v>46122.6819179514</x:v>
-      </x:c>
-      <x:c r="I81" s="31">
-        <x:v>46122.6826717361</x:v>
-      </x:c>
-      <x:c r="J81" s="30" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
@@ -7156,25 +7171,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G82" s="29" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="G82" s="29" t="s">
-        <x:v>235</x:v>
-      </x:c>
       <x:c r="H82" s="31">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
@@ -7194,25 +7209,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G83" s="29" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="G83" s="29" t="s">
+      <x:c r="H83" s="31">
+        <x:v>46122.6819179514</x:v>
+      </x:c>
+      <x:c r="I83" s="31">
+        <x:v>46122.6826717361</x:v>
+      </x:c>
+      <x:c r="J83" s="30" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="H83" s="31">
-        <x:v>46122.9452935995</x:v>
-      </x:c>
-      <x:c r="I83" s="31">
-        <x:v>46123.0460683681</x:v>
-      </x:c>
-      <x:c r="J83" s="30" t="s">
-        <x:v>238</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
@@ -7232,25 +7247,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G84" s="29" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="G84" s="29" t="s">
-        <x:v>240</x:v>
-      </x:c>
       <x:c r="H84" s="31">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I84" s="31">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
-        <x:v>241</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -7270,25 +7285,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G85" s="29" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="H85" s="31">
+        <x:v>46122.9452935995</x:v>
+      </x:c>
+      <x:c r="I85" s="31">
+        <x:v>46123.0460683681</x:v>
+      </x:c>
+      <x:c r="J85" s="30" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="G85" s="29" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="H85" s="31">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I85" s="31">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J85" s="30" t="s">
-        <x:v>244</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -7308,25 +7323,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F86" s="29" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G86" s="29" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="H86" s="31">
+        <x:v>46123.0476912847</x:v>
+      </x:c>
+      <x:c r="I86" s="31">
+        <x:v>46123.0484775694</x:v>
+      </x:c>
+      <x:c r="J86" s="30" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="G86" s="29" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="H86" s="31">
-        <x:v>46123.4162791088</x:v>
-      </x:c>
-      <x:c r="I86" s="31">
-        <x:v>46123.4173169792</x:v>
-      </x:c>
-      <x:c r="J86" s="30" t="s">
-        <x:v>247</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -7346,25 +7361,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G87" s="29" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H87" s="31">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I87" s="31">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J87" s="30" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="G87" s="29" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="H87" s="31">
-        <x:v>46122.6795081481</x:v>
-      </x:c>
-      <x:c r="I87" s="31">
-        <x:v>46122.6802186921</x:v>
-      </x:c>
-      <x:c r="J87" s="30" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -7384,87 +7399,161 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G88" s="29" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="G88" s="29" t="s">
+      <x:c r="H88" s="31">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I88" s="31">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J88" s="30" t="s">
         <x:v>251</x:v>
-      </x:c>
-      <x:c r="H88" s="31">
-        <x:v>46122.3974322338</x:v>
-      </x:c>
-      <x:c r="I88" s="31">
-        <x:v>46122.3980999421</x:v>
-      </x:c>
-      <x:c r="J88" s="30" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="91" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B91" s="17" t="s">
+    <x:row r="89" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B89" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C89" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D89" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E89" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F89" s="29" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="G89" s="29" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="H89" s="31">
+        <x:v>46122.6795081481</x:v>
+      </x:c>
+      <x:c r="I89" s="31">
+        <x:v>46122.6802186921</x:v>
+      </x:c>
+      <x:c r="J89" s="30" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K89" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L89" s="33">
+        <x:v>46122.6809879398</x:v>
+      </x:c>
+      <x:c r="M89" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B90" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C90" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D90" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E90" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F90" s="29" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G90" s="29" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H90" s="31">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I90" s="31">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J90" s="30" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="K90" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L90" s="33">
+        <x:v>46122.5607516551</x:v>
+      </x:c>
+      <x:c r="M90" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B93" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C91" s="18" t="s"/>
-      <x:c r="D91" s="18" t="s"/>
-      <x:c r="E91" s="19" t="s"/>
-      <x:c r="F91" s="19" t="s"/>
-    </x:row>
-    <x:row r="92" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B92" s="20" t="s">
+      <x:c r="C93" s="18" t="s"/>
+      <x:c r="D93" s="18" t="s"/>
+      <x:c r="E93" s="19" t="s"/>
+      <x:c r="F93" s="19" t="s"/>
+    </x:row>
+    <x:row r="94" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B94" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C92" s="21" t="s"/>
-      <x:c r="D92" s="21" t="s"/>
-      <x:c r="E92" s="21" t="s"/>
-      <x:c r="F92" s="22" t="s">
+      <x:c r="C94" s="21" t="s"/>
+      <x:c r="D94" s="21" t="s"/>
+      <x:c r="E94" s="21" t="s"/>
+      <x:c r="F94" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B93" s="23" t="s">
+    <x:row r="95" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B95" s="23" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C93" s="24" t="s"/>
-      <x:c r="D93" s="24" t="s"/>
-      <x:c r="E93" s="24" t="s"/>
-      <x:c r="F93" s="25" t="n">
+      <x:c r="C95" s="24" t="s"/>
+      <x:c r="D95" s="24" t="s"/>
+      <x:c r="E95" s="24" t="s"/>
+      <x:c r="F95" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B94" s="23" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C94" s="24" t="s"/>
-      <x:c r="D94" s="24" t="s"/>
-      <x:c r="E94" s="24" t="s"/>
-      <x:c r="F94" s="25" t="n">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B95" s="26" t="s">
+    <x:row r="96" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B96" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C96" s="24" t="s"/>
+      <x:c r="D96" s="24" t="s"/>
+      <x:c r="E96" s="24" t="s"/>
+      <x:c r="F96" s="25" t="n">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B97" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C95" s="27" t="s"/>
-      <x:c r="D95" s="27" t="s"/>
-      <x:c r="E95" s="27" t="s"/>
-      <x:c r="F95" s="28" t="n">
-        <x:v>81</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C97" s="27" t="s"/>
+      <x:c r="D97" s="27" t="s"/>
+      <x:c r="E97" s="27" t="s"/>
+      <x:c r="F97" s="28" t="n">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
     <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8367,11 +8456,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B91:F91"/>
-    <x:mergeCell ref="B92:E92"/>
-    <x:mergeCell ref="B93:E93"/>
+    <x:mergeCell ref="B93:F93"/>
     <x:mergeCell ref="B94:E94"/>
     <x:mergeCell ref="B95:E95"/>
+    <x:mergeCell ref="B96:E96"/>
+    <x:mergeCell ref="B97:E97"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="260">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -212,6 +212,39 @@
     <x:t>asdqwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1348-304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08729</x:t>
   </x:si>
   <x:si>
@@ -227,28 +260,10 @@
     <x:t>aszxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08635</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1345-593</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08682</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1346-976</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1327-230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qweasd</x:t>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
@@ -299,61 +314,214 @@
     <x:t>resdxcv</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08137</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08154</x:t>
@@ -362,157 +530,136 @@
     <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08160</x:t>
@@ -521,13 +668,22 @@
     <x:t>61-4-2026-1279-279</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08168</x:t>
@@ -536,133 +692,43 @@
     <x:t>61-4-2026-1282-165</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08625</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1344-095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08185</x:t>
@@ -674,127 +740,70 @@
     <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08174</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4669,19 +4678,19 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46134.4519824769</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>46134.4543351736</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J16" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K16" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46134.4551470833</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
@@ -4701,25 +4710,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="29" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G17" s="29" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46126.4798427199</x:v>
+        <x:v>46134.9871842824</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>46126.4809562153</x:v>
+        <x:v>46135.0270460764</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K17" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46135.0715283333</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
@@ -4739,10 +4748,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="29" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G18" s="29" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="31">
         <x:v>46133.0575652778</x:v>
@@ -4751,7 +4760,7 @@
         <x:v>46134.4546264699</x:v>
       </x:c>
       <x:c r="J18" s="30" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
         <x:v>361</x:v>
@@ -4777,10 +4786,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="29" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G19" s="29" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H19" s="31">
         <x:v>46133.5419909606</x:v>
@@ -4815,25 +4824,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="29" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G20" s="29" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H20" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46134.4519824769</x:v>
       </x:c>
       <x:c r="I20" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46134.4543351736</x:v>
       </x:c>
       <x:c r="J20" s="30" t="s">
-        <x:v>74</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K20" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46134.4551470833</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>21</x:v>
@@ -4844,13 +4853,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D21" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E21" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
         <x:v>75</x:v>
@@ -4859,10 +4868,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H21" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
         <x:v>77</x:v>
@@ -4871,7 +4880,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>21</x:v>
@@ -4897,19 +4906,19 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H22" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I22" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J22" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
         <x:v>21</x:v>
@@ -4929,25 +4938,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G23" s="29" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G23" s="29" t="s">
+      <x:c r="H23" s="31">
+        <x:v>46119.8029380671</x:v>
+      </x:c>
+      <x:c r="I23" s="31">
+        <x:v>46120.5237086343</x:v>
+      </x:c>
+      <x:c r="J23" s="30" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="H23" s="31">
-        <x:v>46120.2362105324</x:v>
-      </x:c>
-      <x:c r="I23" s="31">
-        <x:v>46120.5226826273</x:v>
-      </x:c>
-      <x:c r="J23" s="30" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
@@ -4973,19 +4982,19 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
         <x:v>85</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
@@ -5011,19 +5020,19 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -5049,10 +5058,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
         <x:v>90</x:v>
@@ -5061,7 +5070,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -5087,10 +5096,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
         <x:v>28</x:v>
@@ -5099,7 +5108,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -5125,10 +5134,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
         <x:v>95</x:v>
@@ -5137,7 +5146,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -5163,10 +5172,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H29" s="31">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I29" s="31">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
         <x:v>98</x:v>
@@ -5175,7 +5184,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -5201,10 +5210,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
         <x:v>101</x:v>
@@ -5213,7 +5222,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -5239,10 +5248,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H31" s="31">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
         <x:v>104</x:v>
@@ -5251,7 +5260,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -5277,19 +5286,19 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="31">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
@@ -5309,25 +5318,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="29" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G33" s="29" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -5347,25 +5356,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="29" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G34" s="29" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -5385,25 +5394,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="29" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G35" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
@@ -5423,25 +5432,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="29" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G36" s="29" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -5461,25 +5470,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F37" s="29" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G37" s="29" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
@@ -5499,10 +5508,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G38" s="29" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H38" s="31">
         <x:v>46119.729231331</x:v>
@@ -5511,7 +5520,7 @@
         <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
@@ -5537,25 +5546,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G39" s="29" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
@@ -5581,10 +5590,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H40" s="31">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I40" s="31">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
         <x:v>127</x:v>
@@ -5593,7 +5602,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
@@ -5619,10 +5628,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="H41" s="31">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I41" s="31">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
         <x:v>130</x:v>
@@ -5631,7 +5640,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
@@ -5657,10 +5666,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H42" s="31">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I42" s="31">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
         <x:v>133</x:v>
@@ -5669,7 +5678,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -5695,10 +5704,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="H43" s="31">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I43" s="31">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
         <x:v>136</x:v>
@@ -5707,7 +5716,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -5733,10 +5742,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="H44" s="31">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I44" s="31">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
         <x:v>139</x:v>
@@ -5745,7 +5754,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -5771,19 +5780,19 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="H45" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I45" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J45" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -5803,25 +5812,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="29" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G46" s="29" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H46" s="31">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
@@ -5841,25 +5850,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="29" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G47" s="29" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H47" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I47" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J47" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -5885,10 +5894,10 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
         <x:v>149</x:v>
@@ -5897,7 +5906,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -5923,10 +5932,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
         <x:v>152</x:v>
@@ -5935,7 +5944,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -5961,10 +5970,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="H50" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I50" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
         <x:v>155</x:v>
@@ -5973,7 +5982,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -5999,19 +6008,19 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -6031,25 +6040,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F52" s="29" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G52" s="29" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -6069,25 +6078,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="29" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G53" s="29" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>162</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -6113,19 +6122,19 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
@@ -6145,25 +6154,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="29" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G55" s="29" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
@@ -6189,19 +6198,19 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -6221,25 +6230,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="29" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G57" s="29" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46124.150742662</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46124.153253125</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
@@ -6259,25 +6268,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="29" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G58" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
@@ -6297,25 +6306,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="29" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G59" s="29" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>177</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -6341,10 +6350,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
         <x:v>180</x:v>
@@ -6353,7 +6362,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -6379,10 +6388,10 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
         <x:v>183</x:v>
@@ -6391,7 +6400,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -6417,10 +6426,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
         <x:v>186</x:v>
@@ -6429,7 +6438,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -6455,10 +6464,10 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
         <x:v>189</x:v>
@@ -6467,7 +6476,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
@@ -6493,19 +6502,19 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="H64" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I64" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
@@ -6531,10 +6540,10 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H65" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I65" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J65" s="30" t="s">
         <x:v>194</x:v>
@@ -6543,7 +6552,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
@@ -6569,10 +6578,10 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
         <x:v>197</x:v>
@@ -6581,7 +6590,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -6607,19 +6616,19 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46132.4200429282</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46132.4214079282</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -6639,25 +6648,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="29" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G68" s="29" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -6677,25 +6686,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="29" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G69" s="29" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -6715,16 +6724,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
-        <x:v>204</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G70" s="29" t="s">
-        <x:v>205</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H70" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
         <x:v>28</x:v>
@@ -6733,7 +6742,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -6753,25 +6762,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="29" t="s">
-        <x:v>206</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G71" s="29" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H71" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
-        <x:v>208</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -6791,25 +6800,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G72" s="29" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H72" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
@@ -6829,25 +6838,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="G73" s="29" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -6867,25 +6876,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G74" s="29" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -6905,25 +6914,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="G75" s="29" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="H75" s="31">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
@@ -6943,25 +6952,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F76" s="29" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G76" s="29" t="s">
-        <x:v>219</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="H76" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
@@ -6981,25 +6990,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G77" s="29" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="H77" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I77" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>222</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -7019,25 +7028,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G78" s="29" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H78" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I78" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J78" s="30" t="s">
-        <x:v>162</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -7057,25 +7066,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="G79" s="29" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="H79" s="31">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I79" s="31">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J79" s="30" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -7095,25 +7104,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="G80" s="29" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H80" s="31">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -7133,25 +7142,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
-        <x:v>230</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G81" s="29" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H81" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>232</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
@@ -7171,25 +7180,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G82" s="29" t="s">
-        <x:v>234</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H82" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
@@ -7209,25 +7218,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="G83" s="29" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="H83" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>237</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
@@ -7247,16 +7256,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="G84" s="29" t="s">
-        <x:v>239</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="H84" s="31">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I84" s="31">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
         <x:v>28</x:v>
@@ -7265,7 +7274,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -7285,25 +7294,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="G85" s="29" t="s">
-        <x:v>241</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H85" s="31">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I85" s="31">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -7323,25 +7332,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F86" s="29" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="G86" s="29" t="s">
-        <x:v>244</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
-        <x:v>245</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -7361,25 +7370,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="G87" s="29" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="H87" s="31">
-        <x:v>46123.061368912</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -7399,25 +7408,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G88" s="29" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="H88" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
@@ -7437,25 +7446,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F89" s="29" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G89" s="29" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
@@ -7475,86 +7484,123 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F90" s="29" t="s">
-        <x:v>254</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G90" s="29" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="H90" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I90" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J90" s="30" t="s">
-        <x:v>256</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B91" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C91" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D91" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E91" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F91" s="29" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G91" s="29" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="H91" s="31">
+        <x:v>46122.5623107755</x:v>
+      </x:c>
+      <x:c r="I91" s="31">
+        <x:v>46122.5630093981</x:v>
+      </x:c>
+      <x:c r="J91" s="30" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="K91" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L91" s="33">
+        <x:v>46122.5634620023</x:v>
+      </x:c>
+      <x:c r="M91" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="93" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B93" s="17" t="s">
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B94" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C93" s="18" t="s"/>
-      <x:c r="D93" s="18" t="s"/>
-      <x:c r="E93" s="19" t="s"/>
-      <x:c r="F93" s="19" t="s"/>
-    </x:row>
-    <x:row r="94" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B94" s="20" t="s">
+      <x:c r="C94" s="18" t="s"/>
+      <x:c r="D94" s="18" t="s"/>
+      <x:c r="E94" s="19" t="s"/>
+      <x:c r="F94" s="19" t="s"/>
+    </x:row>
+    <x:row r="95" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B95" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C94" s="21" t="s"/>
-      <x:c r="D94" s="21" t="s"/>
-      <x:c r="E94" s="21" t="s"/>
-      <x:c r="F94" s="22" t="s">
+      <x:c r="C95" s="21" t="s"/>
+      <x:c r="D95" s="21" t="s"/>
+      <x:c r="E95" s="21" t="s"/>
+      <x:c r="F95" s="22" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B95" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C95" s="24" t="s"/>
-      <x:c r="D95" s="24" t="s"/>
-      <x:c r="E95" s="24" t="s"/>
-      <x:c r="F95" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:28" ht="18" customHeight="1">
       <x:c r="B96" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C96" s="24" t="s"/>
       <x:c r="D96" s="24" t="s"/>
       <x:c r="E96" s="24" t="s"/>
       <x:c r="F96" s="25" t="n">
-        <x:v>82</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B97" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B97" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C97" s="24" t="s"/>
+      <x:c r="D97" s="24" t="s"/>
+      <x:c r="E97" s="24" t="s"/>
+      <x:c r="F97" s="25" t="n">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B98" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C97" s="27" t="s"/>
-      <x:c r="D97" s="27" t="s"/>
-      <x:c r="E97" s="27" t="s"/>
-      <x:c r="F97" s="28" t="n">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C98" s="27" t="s"/>
+      <x:c r="D98" s="27" t="s"/>
+      <x:c r="E98" s="27" t="s"/>
+      <x:c r="F98" s="28" t="n">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
     <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8456,11 +8502,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B93:F93"/>
-    <x:mergeCell ref="B94:E94"/>
+    <x:mergeCell ref="B94:F94"/>
     <x:mergeCell ref="B95:E95"/>
     <x:mergeCell ref="B96:E96"/>
     <x:mergeCell ref="B97:E97"/>
+    <x:mergeCell ref="B98:E98"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="260">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -221,6 +221,36 @@
     <x:t>123qweasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08984</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1354-199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>edwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08729</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1347-280</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08756</x:t>
   </x:si>
   <x:si>
@@ -228,27 +258,6 @@
   </x:si>
   <x:si>
     <x:t>1555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08635</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1345-593</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08682</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1346-976</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08729</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1347-280</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08340</x:t>
@@ -4716,19 +4725,19 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46134.9871842824</x:v>
+        <x:v>46139.4236006019</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>46135.0270460764</x:v>
+        <x:v>46139.424377581</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="K17" s="32" t="n">
-        <x:v>270</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46135.0715283333</x:v>
+        <x:v>46139.4248658449</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
@@ -4868,19 +4877,19 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H21" s="31">
-        <x:v>46126.4798427199</x:v>
+        <x:v>46134.9871842824</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46126.4809562153</x:v>
+        <x:v>46135.0270460764</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46135.0715283333</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>21</x:v>
@@ -4891,13 +4900,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D22" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E22" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
         <x:v>78</x:v>
@@ -4906,19 +4915,19 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H22" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I22" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J22" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
         <x:v>21</x:v>
@@ -4938,25 +4947,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G23" s="29" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H23" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I23" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J23" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
@@ -4982,19 +4991,19 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
         <x:v>85</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
@@ -5020,19 +5029,19 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -5052,25 +5061,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="29" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G26" s="29" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H26" s="31">
+        <x:v>46120.2362105324</x:v>
+      </x:c>
+      <x:c r="I26" s="31">
+        <x:v>46120.5226826273</x:v>
+      </x:c>
+      <x:c r="J26" s="30" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="G26" s="29" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H26" s="31">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I26" s="31">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J26" s="30" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -5096,19 +5105,19 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -5128,25 +5137,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="29" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G28" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -5172,10 +5181,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H29" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I29" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
         <x:v>98</x:v>
@@ -5184,7 +5193,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -5210,10 +5219,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
         <x:v>101</x:v>
@@ -5222,7 +5231,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -5248,10 +5257,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H31" s="31">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
         <x:v>104</x:v>
@@ -5260,7 +5269,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -5286,10 +5295,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
         <x:v>107</x:v>
@@ -5298,7 +5307,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
@@ -5324,10 +5333,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
         <x:v>110</x:v>
@@ -5336,7 +5345,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -5362,19 +5371,19 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -5394,25 +5403,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G35" s="29" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
@@ -5438,19 +5447,19 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -5470,25 +5479,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F37" s="29" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G37" s="29" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
@@ -5508,25 +5517,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G38" s="29" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H38" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I38" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>122</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
@@ -5552,19 +5561,19 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
@@ -5584,25 +5593,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G40" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H40" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I40" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
@@ -5628,10 +5637,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="H41" s="31">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I41" s="31">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
         <x:v>130</x:v>
@@ -5640,7 +5649,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
@@ -5666,10 +5675,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H42" s="31">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I42" s="31">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
         <x:v>133</x:v>
@@ -5678,7 +5687,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -5704,10 +5713,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="H43" s="31">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I43" s="31">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
         <x:v>136</x:v>
@@ -5716,7 +5725,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -5742,10 +5751,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="H44" s="31">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I44" s="31">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
         <x:v>139</x:v>
@@ -5754,7 +5763,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -5780,10 +5789,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="H45" s="31">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I45" s="31">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J45" s="30" t="s">
         <x:v>142</x:v>
@@ -5792,7 +5801,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -5818,19 +5827,19 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="H46" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
@@ -5850,25 +5859,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="29" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G47" s="29" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H47" s="31">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I47" s="31">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J47" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -5888,25 +5897,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="29" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G48" s="29" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -5932,10 +5941,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
         <x:v>152</x:v>
@@ -5944,7 +5953,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -5970,10 +5979,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="H50" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I50" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
         <x:v>155</x:v>
@@ -5982,7 +5991,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -6008,10 +6017,10 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
         <x:v>158</x:v>
@@ -6020,7 +6029,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -6046,19 +6055,19 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -6078,25 +6087,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="29" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G53" s="29" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -6116,25 +6125,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="29" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G54" s="29" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>165</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
@@ -6160,19 +6169,19 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>90</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
@@ -6192,25 +6201,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G56" s="29" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>170</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -6236,19 +6245,19 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
@@ -6268,25 +6277,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G58" s="29" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>175</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
@@ -6312,19 +6321,19 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46124.150742662</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46124.153253125</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -6344,25 +6353,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G60" s="29" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
-        <x:v>180</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -6388,10 +6397,10 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
         <x:v>183</x:v>
@@ -6400,7 +6409,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -6426,10 +6435,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
         <x:v>186</x:v>
@@ -6438,7 +6447,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -6464,10 +6473,10 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
         <x:v>189</x:v>
@@ -6476,7 +6485,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
@@ -6502,19 +6511,19 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="H64" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I64" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
@@ -6534,25 +6543,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F65" s="29" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G65" s="29" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="H65" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I65" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J65" s="30" t="s">
-        <x:v>194</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
@@ -6578,10 +6587,10 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
         <x:v>197</x:v>
@@ -6590,7 +6599,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -6616,10 +6625,10 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
         <x:v>200</x:v>
@@ -6628,7 +6637,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -6654,10 +6663,10 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
         <x:v>203</x:v>
@@ -6666,7 +6675,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -6692,19 +6701,19 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46132.4200429282</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46132.4214079282</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -6724,25 +6733,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="G70" s="29" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H70" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -6762,16 +6771,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="29" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="G71" s="29" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="H71" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
         <x:v>28</x:v>
@@ -6780,7 +6789,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -6800,25 +6809,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G72" s="29" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H72" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
@@ -6838,25 +6847,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G73" s="29" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -6876,25 +6885,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="G74" s="29" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
-        <x:v>216</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -6920,10 +6929,10 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="H75" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
         <x:v>219</x:v>
@@ -6932,7 +6941,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
@@ -6958,19 +6967,19 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="H76" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
@@ -6990,25 +6999,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G77" s="29" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H77" s="31">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I77" s="31">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -7028,16 +7037,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="G78" s="29" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="H78" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I78" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J78" s="30" t="s">
         <x:v>85</x:v>
@@ -7046,7 +7055,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -7066,25 +7075,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G79" s="29" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H79" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I79" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J79" s="30" t="s">
-        <x:v>228</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -7110,10 +7119,10 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="H80" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
         <x:v>231</x:v>
@@ -7122,7 +7131,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -7148,10 +7157,10 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="H81" s="31">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
         <x:v>234</x:v>
@@ -7160,7 +7169,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
@@ -7186,10 +7195,10 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="H82" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
         <x:v>237</x:v>
@@ -7198,7 +7207,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
@@ -7224,19 +7233,19 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="H83" s="31">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
@@ -7256,16 +7265,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="G84" s="29" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="H84" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I84" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
         <x:v>28</x:v>
@@ -7274,7 +7283,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -7294,25 +7303,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="G85" s="29" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="H85" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I85" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
-        <x:v>244</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -7338,19 +7347,19 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -7370,25 +7379,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="G87" s="29" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="H87" s="31">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
-        <x:v>249</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -7414,10 +7423,10 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="H88" s="31">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
         <x:v>252</x:v>
@@ -7426,7 +7435,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
@@ -7452,10 +7461,10 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46123.061368912</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
         <x:v>255</x:v>
@@ -7464,7 +7473,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
@@ -7490,19 +7499,19 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="H90" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I90" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J90" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>21</x:v>
@@ -7522,86 +7531,123 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F91" s="29" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G91" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="H91" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I91" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J91" s="30" t="s">
-        <x:v>165</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K91" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L91" s="33">
+        <x:v>46122.6199813426</x:v>
+      </x:c>
+      <x:c r="M91" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B92" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C92" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D92" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E92" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F92" s="29" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="G92" s="29" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="H92" s="31">
+        <x:v>46122.5623107755</x:v>
+      </x:c>
+      <x:c r="I92" s="31">
+        <x:v>46122.5630093981</x:v>
+      </x:c>
+      <x:c r="J92" s="30" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="K92" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L92" s="33">
         <x:v>46122.5634620023</x:v>
       </x:c>
-      <x:c r="M91" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="M92" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="94" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B94" s="17" t="s">
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B95" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C94" s="18" t="s"/>
-      <x:c r="D94" s="18" t="s"/>
-      <x:c r="E94" s="19" t="s"/>
-      <x:c r="F94" s="19" t="s"/>
-    </x:row>
-    <x:row r="95" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B95" s="20" t="s">
+      <x:c r="C95" s="18" t="s"/>
+      <x:c r="D95" s="18" t="s"/>
+      <x:c r="E95" s="19" t="s"/>
+      <x:c r="F95" s="19" t="s"/>
+    </x:row>
+    <x:row r="96" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B96" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C95" s="21" t="s"/>
-      <x:c r="D95" s="21" t="s"/>
-      <x:c r="E95" s="21" t="s"/>
-      <x:c r="F95" s="22" t="s">
+      <x:c r="C96" s="21" t="s"/>
+      <x:c r="D96" s="21" t="s"/>
+      <x:c r="E96" s="21" t="s"/>
+      <x:c r="F96" s="22" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B96" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C96" s="24" t="s"/>
-      <x:c r="D96" s="24" t="s"/>
-      <x:c r="E96" s="24" t="s"/>
-      <x:c r="F96" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:28" ht="18" customHeight="1">
       <x:c r="B97" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C97" s="24" t="s"/>
       <x:c r="D97" s="24" t="s"/>
       <x:c r="E97" s="24" t="s"/>
       <x:c r="F97" s="25" t="n">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B98" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B98" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C98" s="24" t="s"/>
+      <x:c r="D98" s="24" t="s"/>
+      <x:c r="E98" s="24" t="s"/>
+      <x:c r="F98" s="25" t="n">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B99" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C98" s="27" t="s"/>
-      <x:c r="D98" s="27" t="s"/>
-      <x:c r="E98" s="27" t="s"/>
-      <x:c r="F98" s="28" t="n">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C99" s="27" t="s"/>
+      <x:c r="D99" s="27" t="s"/>
+      <x:c r="E99" s="27" t="s"/>
+      <x:c r="F99" s="28" t="n">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
     <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8502,11 +8548,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B94:F94"/>
-    <x:mergeCell ref="B95:E95"/>
+    <x:mergeCell ref="B95:F95"/>
     <x:mergeCell ref="B96:E96"/>
     <x:mergeCell ref="B97:E97"/>
     <x:mergeCell ref="B98:E98"/>
+    <x:mergeCell ref="B99:E99"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="266">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -221,6 +221,54 @@
     <x:t>123qweasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-09014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1355-793</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123456</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08729</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1347-280</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1348-304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1555</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08984</x:t>
   </x:si>
   <x:si>
@@ -230,43 +278,433 @@
     <x:t>edwa</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08635</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1345-593</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08682</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1346-976</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08729</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1347-280</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08756</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1348-304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1328-100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aszxcasd</x:t>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08344</x:t>
@@ -275,415 +713,37 @@
     <x:t>61-4-2026-1332-041</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08625</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1344-095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08184</x:t>
@@ -695,33 +755,6 @@
     <x:t>test12</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -731,6 +764,57 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08175</x:t>
   </x:si>
   <x:si>
@@ -738,81 +822,6 @@
   </x:si>
   <x:si>
     <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4725,10 +4734,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46139.4236006019</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>46139.424377581</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
         <x:v>67</x:v>
@@ -4737,7 +4746,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46139.4248658449</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
@@ -4763,19 +4772,19 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="31">
-        <x:v>46133.0575652778</x:v>
+        <x:v>46140.5605711921</x:v>
       </x:c>
       <x:c r="I18" s="31">
-        <x:v>46134.4546264699</x:v>
+        <x:v>46140.5613520833</x:v>
       </x:c>
       <x:c r="J18" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
-        <x:v>361</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46134.4615905556</x:v>
+        <x:v>46140.562271713</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
@@ -4801,19 +4810,19 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="H19" s="31">
-        <x:v>46133.5419909606</x:v>
+        <x:v>46133.0575652778</x:v>
       </x:c>
       <x:c r="I19" s="31">
-        <x:v>46133.5429334722</x:v>
+        <x:v>46134.4546264699</x:v>
       </x:c>
       <x:c r="J19" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K19" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46133.5457238194</x:v>
+        <x:v>46134.4615905556</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>21</x:v>
@@ -4833,16 +4842,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="29" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G20" s="29" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H20" s="31">
-        <x:v>46134.4519824769</x:v>
+        <x:v>46133.5419909606</x:v>
       </x:c>
       <x:c r="I20" s="31">
-        <x:v>46134.4543351736</x:v>
+        <x:v>46133.5429334722</x:v>
       </x:c>
       <x:c r="J20" s="30" t="s">
         <x:v>28</x:v>
@@ -4851,7 +4860,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46134.4551470833</x:v>
+        <x:v>46133.5457238194</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>21</x:v>
@@ -4871,25 +4880,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G21" s="29" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="31">
-        <x:v>46134.9871842824</x:v>
+        <x:v>46134.4519824769</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46135.0270460764</x:v>
+        <x:v>46134.4543351736</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
-        <x:v>270</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46135.0715283333</x:v>
+        <x:v>46134.4551470833</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>21</x:v>
@@ -4915,19 +4924,19 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H22" s="31">
-        <x:v>46126.4798427199</x:v>
+        <x:v>46134.9871842824</x:v>
       </x:c>
       <x:c r="I22" s="31">
-        <x:v>46126.4809562153</x:v>
+        <x:v>46135.0270460764</x:v>
       </x:c>
       <x:c r="J22" s="30" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46135.0715283333</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
         <x:v>21</x:v>
@@ -4938,13 +4947,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D23" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
         <x:v>81</x:v>
@@ -4953,19 +4962,19 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H23" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46139.4236006019</x:v>
       </x:c>
       <x:c r="I23" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46139.424377581</x:v>
       </x:c>
       <x:c r="J23" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46139.4248658449</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
@@ -4985,25 +4994,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F24" s="29" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G24" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
@@ -5029,19 +5038,19 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -5067,19 +5076,19 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -5099,25 +5108,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="29" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G27" s="29" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H27" s="31">
+        <x:v>46120.2362105324</x:v>
+      </x:c>
+      <x:c r="I27" s="31">
+        <x:v>46120.5226826273</x:v>
+      </x:c>
+      <x:c r="J27" s="30" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="G27" s="29" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H27" s="31">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I27" s="31">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J27" s="30" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -5143,19 +5152,19 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -5175,25 +5184,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="29" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G29" s="29" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H29" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I29" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
-        <x:v>98</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -5219,10 +5228,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
         <x:v>101</x:v>
@@ -5231,7 +5240,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -5257,10 +5266,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H31" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
         <x:v>104</x:v>
@@ -5269,7 +5278,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -5295,10 +5304,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="31">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
         <x:v>107</x:v>
@@ -5307,7 +5316,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
@@ -5333,19 +5342,19 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
-        <x:v>110</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -5365,25 +5374,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="29" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G34" s="29" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G34" s="29" t="s">
+      <x:c r="H34" s="31">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I34" s="31">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J34" s="30" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="H34" s="31">
-        <x:v>46121.5183984954</x:v>
-      </x:c>
-      <x:c r="I34" s="31">
-        <x:v>46122.2061737153</x:v>
-      </x:c>
-      <x:c r="J34" s="30" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -5403,25 +5412,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="29" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G35" s="29" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="G35" s="29" t="s">
+      <x:c r="H35" s="31">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I35" s="31">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J35" s="30" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="H35" s="31">
-        <x:v>46122.1299166204</x:v>
-      </x:c>
-      <x:c r="I35" s="31">
-        <x:v>46122.2059087963</x:v>
-      </x:c>
-      <x:c r="J35" s="30" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
@@ -5447,10 +5456,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
         <x:v>118</x:v>
@@ -5459,7 +5468,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -5485,19 +5494,19 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
@@ -5523,19 +5532,19 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="H38" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I38" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
@@ -5561,19 +5570,19 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
@@ -5593,16 +5602,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G40" s="29" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="G40" s="29" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="H40" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I40" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
         <x:v>88</x:v>
@@ -5611,7 +5620,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
@@ -5631,25 +5640,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G41" s="29" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G41" s="29" t="s">
+      <x:c r="H41" s="31">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I41" s="31">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J41" s="30" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="H41" s="31">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I41" s="31">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J41" s="30" t="s">
-        <x:v>130</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
@@ -5669,25 +5678,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G42" s="29" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="G42" s="29" t="s">
+      <x:c r="H42" s="31">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I42" s="31">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J42" s="30" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="H42" s="31">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I42" s="31">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J42" s="30" t="s">
-        <x:v>133</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -5707,25 +5716,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G43" s="29" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="G43" s="29" t="s">
+      <x:c r="H43" s="31">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I43" s="31">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J43" s="30" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="H43" s="31">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I43" s="31">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J43" s="30" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -5745,25 +5754,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G44" s="29" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="G44" s="29" t="s">
+      <x:c r="H44" s="31">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I44" s="31">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J44" s="30" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="H44" s="31">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I44" s="31">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J44" s="30" t="s">
-        <x:v>139</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -5783,25 +5792,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F45" s="29" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G45" s="29" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="G45" s="29" t="s">
+      <x:c r="H45" s="31">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I45" s="31">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J45" s="30" t="s">
         <x:v>141</x:v>
-      </x:c>
-      <x:c r="H45" s="31">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I45" s="31">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J45" s="30" t="s">
-        <x:v>142</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -5821,25 +5830,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="29" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G46" s="29" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="G46" s="29" t="s">
+      <x:c r="H46" s="31">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I46" s="31">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J46" s="30" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="H46" s="31">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I46" s="31">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J46" s="30" t="s">
-        <x:v>145</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
@@ -5859,25 +5868,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="29" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G47" s="29" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="G47" s="29" t="s">
+      <x:c r="H47" s="31">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I47" s="31">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J47" s="30" t="s">
         <x:v>147</x:v>
-      </x:c>
-      <x:c r="H47" s="31">
-        <x:v>46119.8017436343</x:v>
-      </x:c>
-      <x:c r="I47" s="31">
-        <x:v>46119.8048384144</x:v>
-      </x:c>
-      <x:c r="J47" s="30" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -5903,19 +5912,19 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -5941,19 +5950,19 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>152</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -5973,25 +5982,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="29" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G50" s="29" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G50" s="29" t="s">
+      <x:c r="H50" s="31">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I50" s="31">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J50" s="30" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="H50" s="31">
-        <x:v>46119.542956794</x:v>
-      </x:c>
-      <x:c r="I50" s="31">
-        <x:v>46119.5456356481</x:v>
-      </x:c>
-      <x:c r="J50" s="30" t="s">
-        <x:v>155</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -6011,25 +6020,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F51" s="29" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G51" s="29" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="G51" s="29" t="s">
+      <x:c r="H51" s="31">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I51" s="31">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J51" s="30" t="s">
         <x:v>157</x:v>
-      </x:c>
-      <x:c r="H51" s="31">
-        <x:v>46119.5434206134</x:v>
-      </x:c>
-      <x:c r="I51" s="31">
-        <x:v>46119.545474919</x:v>
-      </x:c>
-      <x:c r="J51" s="30" t="s">
-        <x:v>158</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -6049,25 +6058,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F52" s="29" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G52" s="29" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="G52" s="29" t="s">
+      <x:c r="H52" s="31">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I52" s="31">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J52" s="30" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="H52" s="31">
-        <x:v>46119.5439653357</x:v>
-      </x:c>
-      <x:c r="I52" s="31">
-        <x:v>46119.5452984143</x:v>
-      </x:c>
-      <x:c r="J52" s="30" t="s">
-        <x:v>161</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -6087,25 +6096,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="29" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G53" s="29" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G53" s="29" t="s">
+      <x:c r="H53" s="31">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I53" s="31">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J53" s="30" t="s">
         <x:v>163</x:v>
-      </x:c>
-      <x:c r="H53" s="31">
-        <x:v>46119.7254171991</x:v>
-      </x:c>
-      <x:c r="I53" s="31">
-        <x:v>46119.7262936574</x:v>
-      </x:c>
-      <x:c r="J53" s="30" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -6131,19 +6140,19 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
@@ -6169,10 +6178,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
         <x:v>168</x:v>
@@ -6181,7 +6190,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
@@ -6207,19 +6216,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>93</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -6239,25 +6248,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="29" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G57" s="29" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
@@ -6283,19 +6292,19 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
@@ -6315,25 +6324,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="29" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G59" s="29" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>178</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -6359,19 +6368,19 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46124.150742662</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46124.153253125</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -6397,10 +6406,10 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
         <x:v>183</x:v>
@@ -6409,7 +6418,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -6435,19 +6444,19 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
-        <x:v>186</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -6467,25 +6476,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="29" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G63" s="29" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="G63" s="29" t="s">
+      <x:c r="H63" s="31">
+        <x:v>46124.1512647338</x:v>
+      </x:c>
+      <x:c r="I63" s="31">
+        <x:v>46124.1530803935</x:v>
+      </x:c>
+      <x:c r="J63" s="30" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="H63" s="31">
-        <x:v>46124.5490358102</x:v>
-      </x:c>
-      <x:c r="I63" s="31">
-        <x:v>46124.6984689583</x:v>
-      </x:c>
-      <x:c r="J63" s="30" t="s">
-        <x:v>189</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
@@ -6505,25 +6514,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G64" s="29" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="G64" s="29" t="s">
+      <x:c r="H64" s="31">
+        <x:v>46124.1518079282</x:v>
+      </x:c>
+      <x:c r="I64" s="31">
+        <x:v>46124.1529164583</x:v>
+      </x:c>
+      <x:c r="J64" s="30" t="s">
         <x:v>191</x:v>
-      </x:c>
-      <x:c r="H64" s="31">
-        <x:v>46124.6761778356</x:v>
-      </x:c>
-      <x:c r="I64" s="31">
-        <x:v>46124.6772295602</x:v>
-      </x:c>
-      <x:c r="J64" s="30" t="s">
-        <x:v>192</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
@@ -6543,25 +6552,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F65" s="29" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G65" s="29" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="G65" s="29" t="s">
+      <x:c r="H65" s="31">
+        <x:v>46124.5490358102</x:v>
+      </x:c>
+      <x:c r="I65" s="31">
+        <x:v>46124.6984689583</x:v>
+      </x:c>
+      <x:c r="J65" s="30" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="H65" s="31">
-        <x:v>46124.1449755903</x:v>
-      </x:c>
-      <x:c r="I65" s="31">
-        <x:v>46124.1465040046</x:v>
-      </x:c>
-      <x:c r="J65" s="30" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
@@ -6587,10 +6596,10 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
         <x:v>197</x:v>
@@ -6599,7 +6608,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -6625,10 +6634,10 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
         <x:v>200</x:v>
@@ -6637,7 +6646,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -6663,19 +6672,19 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
-        <x:v>203</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -6695,25 +6704,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="29" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G69" s="29" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="G69" s="29" t="s">
+      <x:c r="H69" s="31">
+        <x:v>46124.7023532986</x:v>
+      </x:c>
+      <x:c r="I69" s="31">
+        <x:v>46124.7048005093</x:v>
+      </x:c>
+      <x:c r="J69" s="30" t="s">
         <x:v>205</x:v>
-      </x:c>
-      <x:c r="H69" s="31">
-        <x:v>46124.7035032407</x:v>
-      </x:c>
-      <x:c r="I69" s="31">
-        <x:v>46124.704475463</x:v>
-      </x:c>
-      <x:c r="J69" s="30" t="s">
-        <x:v>206</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -6733,25 +6742,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G70" s="29" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="G70" s="29" t="s">
+      <x:c r="H70" s="31">
+        <x:v>46124.7029179398</x:v>
+      </x:c>
+      <x:c r="I70" s="31">
+        <x:v>46124.7046092014</x:v>
+      </x:c>
+      <x:c r="J70" s="30" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="H70" s="31">
-        <x:v>46132.4200429282</x:v>
-      </x:c>
-      <x:c r="I70" s="31">
-        <x:v>46132.4214079282</x:v>
-      </x:c>
-      <x:c r="J70" s="30" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -6777,19 +6786,19 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="H71" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -6809,25 +6818,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="G72" s="29" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="H72" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
@@ -6847,25 +6856,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G73" s="29" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -6885,25 +6894,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="G74" s="29" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -6923,25 +6932,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G75" s="29" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H75" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>219</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
@@ -6961,25 +6970,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F76" s="29" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="G76" s="29" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H76" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
@@ -6999,25 +7008,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G77" s="29" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H77" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I77" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -7037,25 +7046,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G78" s="29" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H78" s="31">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I78" s="31">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J78" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -7075,25 +7084,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="G79" s="29" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H79" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I79" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J79" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -7113,25 +7122,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
-        <x:v>229</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="G80" s="29" t="s">
-        <x:v>230</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="H80" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>231</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -7151,25 +7160,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="G81" s="29" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="H81" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>234</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
@@ -7195,10 +7204,10 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="H82" s="31">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
         <x:v>237</x:v>
@@ -7207,7 +7216,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
@@ -7233,19 +7242,19 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="H83" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>240</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
@@ -7265,25 +7274,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G84" s="29" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="G84" s="29" t="s">
+      <x:c r="H84" s="31">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I84" s="31">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J84" s="30" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="H84" s="31">
-        <x:v>46122.5945434491</x:v>
-      </x:c>
-      <x:c r="I84" s="31">
-        <x:v>46122.5999534606</x:v>
-      </x:c>
-      <x:c r="J84" s="30" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -7309,19 +7318,19 @@
         <x:v>244</x:v>
       </x:c>
       <x:c r="H85" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I85" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -7341,25 +7350,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F86" s="29" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="G86" s="29" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
-        <x:v>247</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -7385,10 +7394,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="H87" s="31">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
         <x:v>28</x:v>
@@ -7397,7 +7406,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -7423,10 +7432,10 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="H88" s="31">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
         <x:v>252</x:v>
@@ -7435,7 +7444,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
@@ -7461,19 +7470,19 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
-        <x:v>255</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
@@ -7493,25 +7502,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F90" s="29" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="G90" s="29" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="G90" s="29" t="s">
+      <x:c r="H90" s="31">
+        <x:v>46122.9452935995</x:v>
+      </x:c>
+      <x:c r="I90" s="31">
+        <x:v>46123.0460683681</x:v>
+      </x:c>
+      <x:c r="J90" s="30" t="s">
         <x:v>257</x:v>
-      </x:c>
-      <x:c r="H90" s="31">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I90" s="31">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J90" s="30" t="s">
-        <x:v>258</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>21</x:v>
@@ -7531,25 +7540,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F91" s="29" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G91" s="29" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="G91" s="29" t="s">
+      <x:c r="H91" s="31">
+        <x:v>46123.0476912847</x:v>
+      </x:c>
+      <x:c r="I91" s="31">
+        <x:v>46123.0484775694</x:v>
+      </x:c>
+      <x:c r="J91" s="30" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="H91" s="31">
-        <x:v>46122.6182774306</x:v>
-      </x:c>
-      <x:c r="I91" s="31">
-        <x:v>46122.6193276968</x:v>
-      </x:c>
-      <x:c r="J91" s="30" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="K91" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L91" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M91" s="29" t="s">
         <x:v>21</x:v>
@@ -7575,80 +7584,117 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="H92" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I92" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J92" s="30" t="s">
-        <x:v>168</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K92" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L92" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M92" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B93" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C93" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D93" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E93" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F93" s="29" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G93" s="29" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H93" s="31">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I93" s="31">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J93" s="30" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="K93" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L93" s="33">
+        <x:v>46122.5928339699</x:v>
+      </x:c>
+      <x:c r="M93" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="95" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B95" s="17" t="s">
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B96" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C95" s="18" t="s"/>
-      <x:c r="D95" s="18" t="s"/>
-      <x:c r="E95" s="19" t="s"/>
-      <x:c r="F95" s="19" t="s"/>
-    </x:row>
-    <x:row r="96" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B96" s="20" t="s">
+      <x:c r="C96" s="18" t="s"/>
+      <x:c r="D96" s="18" t="s"/>
+      <x:c r="E96" s="19" t="s"/>
+      <x:c r="F96" s="19" t="s"/>
+    </x:row>
+    <x:row r="97" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B97" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C96" s="21" t="s"/>
-      <x:c r="D96" s="21" t="s"/>
-      <x:c r="E96" s="21" t="s"/>
-      <x:c r="F96" s="22" t="s">
+      <x:c r="C97" s="21" t="s"/>
+      <x:c r="D97" s="21" t="s"/>
+      <x:c r="E97" s="21" t="s"/>
+      <x:c r="F97" s="22" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B97" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C97" s="24" t="s"/>
-      <x:c r="D97" s="24" t="s"/>
-      <x:c r="E97" s="24" t="s"/>
-      <x:c r="F97" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:28" ht="18" customHeight="1">
       <x:c r="B98" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C98" s="24" t="s"/>
       <x:c r="D98" s="24" t="s"/>
       <x:c r="E98" s="24" t="s"/>
       <x:c r="F98" s="25" t="n">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B99" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B99" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C99" s="24" t="s"/>
+      <x:c r="D99" s="24" t="s"/>
+      <x:c r="E99" s="24" t="s"/>
+      <x:c r="F99" s="25" t="n">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B100" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C99" s="27" t="s"/>
-      <x:c r="D99" s="27" t="s"/>
-      <x:c r="E99" s="27" t="s"/>
-      <x:c r="F99" s="28" t="n">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C100" s="27" t="s"/>
+      <x:c r="D100" s="27" t="s"/>
+      <x:c r="E100" s="27" t="s"/>
+      <x:c r="F100" s="28" t="n">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
     <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8548,11 +8594,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B95:F95"/>
-    <x:mergeCell ref="B96:E96"/>
+    <x:mergeCell ref="B96:F96"/>
     <x:mergeCell ref="B97:E97"/>
     <x:mergeCell ref="B98:E98"/>
     <x:mergeCell ref="B99:E99"/>
+    <x:mergeCell ref="B100:E100"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="266">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="269">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -230,6 +230,54 @@
     <x:t>aszxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-09141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1357-087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>testzxcad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08729</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1347-280</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1348-304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08984</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1354-199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>edwa</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-09014</x:t>
   </x:si>
   <x:si>
@@ -239,45 +287,6 @@
     <x:t>123456</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08635</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1345-593</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08682</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1346-976</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08729</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1347-280</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08756</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1348-304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08984</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1354-199</x:t>
-  </x:si>
-  <x:si>
-    <x:t>edwa</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08369</x:t>
   </x:si>
   <x:si>
@@ -332,6 +341,24 @@
     <x:t>resdxcv</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08145</x:t>
   </x:si>
   <x:si>
@@ -341,30 +368,12 @@
     <x:t>sdf</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08147</x:t>
   </x:si>
   <x:si>
@@ -401,138 +410,138 @@
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08096</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
   </x:si>
   <x:si>
@@ -548,6 +557,162 @@
     <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08165</x:t>
   </x:si>
   <x:si>
@@ -557,166 +722,10 @@
     <x:t>zscasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08625</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1344-095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08344</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08169</x:t>
@@ -4772,10 +4781,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="31">
-        <x:v>46140.5605711921</x:v>
+        <x:v>46142.575376088</x:v>
       </x:c>
       <x:c r="I18" s="31">
-        <x:v>46140.5613520833</x:v>
+        <x:v>46142.5762906829</x:v>
       </x:c>
       <x:c r="J18" s="30" t="s">
         <x:v>70</x:v>
@@ -4784,7 +4793,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46140.562271713</x:v>
+        <x:v>46142.5767170718</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
@@ -4985,13 +4994,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D24" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F24" s="29" t="s">
         <x:v>84</x:v>
@@ -5000,19 +5009,19 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46140.5605711921</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46140.5613520833</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46140.562271713</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
@@ -5032,25 +5041,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="29" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G25" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -5076,19 +5085,19 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
         <x:v>91</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -5114,19 +5123,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -5146,25 +5155,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="29" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G28" s="29" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H28" s="31">
+        <x:v>46120.2362105324</x:v>
+      </x:c>
+      <x:c r="I28" s="31">
+        <x:v>46120.5226826273</x:v>
+      </x:c>
+      <x:c r="J28" s="30" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G28" s="29" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H28" s="31">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I28" s="31">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J28" s="30" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -5190,19 +5199,19 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="H29" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I29" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -5222,25 +5231,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="29" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G30" s="29" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>101</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -5266,10 +5275,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H31" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
         <x:v>104</x:v>
@@ -5278,7 +5287,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -5304,10 +5313,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
         <x:v>107</x:v>
@@ -5316,7 +5325,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
@@ -5342,19 +5351,19 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -5374,25 +5383,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="29" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G34" s="29" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -5412,25 +5421,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G35" s="29" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
@@ -5456,10 +5465,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
         <x:v>118</x:v>
@@ -5468,7 +5477,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -5494,19 +5503,19 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
@@ -5526,25 +5535,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G38" s="29" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H38" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I38" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
@@ -5564,25 +5573,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G39" s="29" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
@@ -5602,25 +5611,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G40" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H40" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I40" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
@@ -5640,25 +5649,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G41" s="29" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H41" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I41" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
-        <x:v>129</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
@@ -5684,10 +5693,10 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="H42" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I42" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
         <x:v>132</x:v>
@@ -5696,7 +5705,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -5722,10 +5731,10 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="H43" s="31">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I43" s="31">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
         <x:v>135</x:v>
@@ -5734,7 +5743,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -5760,10 +5769,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="H44" s="31">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I44" s="31">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
         <x:v>138</x:v>
@@ -5772,7 +5781,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -5798,10 +5807,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="H45" s="31">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I45" s="31">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J45" s="30" t="s">
         <x:v>141</x:v>
@@ -5810,7 +5819,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -5836,10 +5845,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="H46" s="31">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
         <x:v>144</x:v>
@@ -5848,7 +5857,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
@@ -5874,10 +5883,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="H47" s="31">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I47" s="31">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J47" s="30" t="s">
         <x:v>147</x:v>
@@ -5886,7 +5895,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -5912,19 +5921,19 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -5944,25 +5953,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F49" s="29" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G49" s="29" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -5982,25 +5991,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="29" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G50" s="29" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H50" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I50" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
-        <x:v>154</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -6026,10 +6035,10 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
         <x:v>157</x:v>
@@ -6038,7 +6047,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -6064,10 +6073,10 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
         <x:v>160</x:v>
@@ -6076,7 +6085,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -6102,10 +6111,10 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
         <x:v>163</x:v>
@@ -6114,7 +6123,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -6140,19 +6149,19 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
@@ -6172,10 +6181,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="29" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G55" s="29" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H55" s="31">
         <x:v>46122.1996025926</x:v>
@@ -6184,7 +6193,7 @@
         <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
@@ -6210,25 +6219,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G56" s="29" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>171</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -6254,19 +6263,19 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>96</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
@@ -6286,25 +6295,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="29" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G58" s="29" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>176</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
@@ -6330,19 +6339,19 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -6368,10 +6377,10 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
         <x:v>91</x:v>
@@ -6380,7 +6389,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -6406,19 +6415,19 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
-        <x:v>183</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -6438,25 +6447,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F62" s="29" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G62" s="29" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="G62" s="29" t="s">
+      <x:c r="H62" s="31">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I62" s="31">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J62" s="30" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="H62" s="31">
-        <x:v>46124.150742662</x:v>
-      </x:c>
-      <x:c r="I62" s="31">
-        <x:v>46124.153253125</x:v>
-      </x:c>
-      <x:c r="J62" s="30" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -6482,19 +6491,19 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
@@ -6514,25 +6523,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G64" s="29" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="G64" s="29" t="s">
+      <x:c r="H64" s="31">
+        <x:v>46124.1512647338</x:v>
+      </x:c>
+      <x:c r="I64" s="31">
+        <x:v>46124.1530803935</x:v>
+      </x:c>
+      <x:c r="J64" s="30" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="H64" s="31">
-        <x:v>46124.1518079282</x:v>
-      </x:c>
-      <x:c r="I64" s="31">
-        <x:v>46124.1529164583</x:v>
-      </x:c>
-      <x:c r="J64" s="30" t="s">
-        <x:v>191</x:v>
-      </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
@@ -6552,25 +6561,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F65" s="29" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G65" s="29" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="G65" s="29" t="s">
+      <x:c r="H65" s="31">
+        <x:v>46124.1518079282</x:v>
+      </x:c>
+      <x:c r="I65" s="31">
+        <x:v>46124.1529164583</x:v>
+      </x:c>
+      <x:c r="J65" s="30" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="H65" s="31">
-        <x:v>46124.5490358102</x:v>
-      </x:c>
-      <x:c r="I65" s="31">
-        <x:v>46124.6984689583</x:v>
-      </x:c>
-      <x:c r="J65" s="30" t="s">
-        <x:v>194</x:v>
-      </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
@@ -6590,25 +6599,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="29" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G66" s="29" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="G66" s="29" t="s">
+      <x:c r="H66" s="31">
+        <x:v>46124.5490358102</x:v>
+      </x:c>
+      <x:c r="I66" s="31">
+        <x:v>46124.6984689583</x:v>
+      </x:c>
+      <x:c r="J66" s="30" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="H66" s="31">
-        <x:v>46124.1410094907</x:v>
-      </x:c>
-      <x:c r="I66" s="31">
-        <x:v>46124.1426461806</x:v>
-      </x:c>
-      <x:c r="J66" s="30" t="s">
-        <x:v>197</x:v>
-      </x:c>
       <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -6628,25 +6637,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="29" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G67" s="29" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="G67" s="29" t="s">
+      <x:c r="H67" s="31">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I67" s="31">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J67" s="30" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="H67" s="31">
-        <x:v>46124.6761778356</x:v>
-      </x:c>
-      <x:c r="I67" s="31">
-        <x:v>46124.6772295602</x:v>
-      </x:c>
-      <x:c r="J67" s="30" t="s">
-        <x:v>200</x:v>
-      </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -6666,25 +6675,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="29" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G68" s="29" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="G68" s="29" t="s">
+      <x:c r="H68" s="31">
+        <x:v>46124.6761778356</x:v>
+      </x:c>
+      <x:c r="I68" s="31">
+        <x:v>46124.6772295602</x:v>
+      </x:c>
+      <x:c r="J68" s="30" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="H68" s="31">
-        <x:v>46124.701771875</x:v>
-      </x:c>
-      <x:c r="I68" s="31">
-        <x:v>46124.7049218519</x:v>
-      </x:c>
-      <x:c r="J68" s="30" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -6710,19 +6719,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
-        <x:v>205</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -6742,25 +6751,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G70" s="29" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="G70" s="29" t="s">
+      <x:c r="H70" s="31">
+        <x:v>46124.7023532986</x:v>
+      </x:c>
+      <x:c r="I70" s="31">
+        <x:v>46124.7048005093</x:v>
+      </x:c>
+      <x:c r="J70" s="30" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="H70" s="31">
-        <x:v>46124.7029179398</x:v>
-      </x:c>
-      <x:c r="I70" s="31">
-        <x:v>46124.7046092014</x:v>
-      </x:c>
-      <x:c r="J70" s="30" t="s">
-        <x:v>208</x:v>
-      </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -6780,25 +6789,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="29" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G71" s="29" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="G71" s="29" t="s">
-        <x:v>210</x:v>
-      </x:c>
       <x:c r="H71" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
-        <x:v>211</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -6818,25 +6827,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G72" s="29" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="G72" s="29" t="s">
+      <x:c r="H72" s="31">
+        <x:v>46124.7035032407</x:v>
+      </x:c>
+      <x:c r="I72" s="31">
+        <x:v>46124.704475463</x:v>
+      </x:c>
+      <x:c r="J72" s="30" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="H72" s="31">
-        <x:v>46132.4200429282</x:v>
-      </x:c>
-      <x:c r="I72" s="31">
-        <x:v>46132.4214079282</x:v>
-      </x:c>
-      <x:c r="J72" s="30" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
@@ -6862,19 +6871,19 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -6900,19 +6909,19 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
-        <x:v>218</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -6932,25 +6941,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G75" s="29" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G75" s="29" t="s">
+      <x:c r="H75" s="31">
+        <x:v>46124.6975491551</x:v>
+      </x:c>
+      <x:c r="I75" s="31">
+        <x:v>46124.6983328357</x:v>
+      </x:c>
+      <x:c r="J75" s="30" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="H75" s="31">
-        <x:v>46122.3569147569</x:v>
-      </x:c>
-      <x:c r="I75" s="31">
-        <x:v>46122.3577305324</x:v>
-      </x:c>
-      <x:c r="J75" s="30" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
@@ -6976,19 +6985,19 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="H76" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>223</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
@@ -7008,25 +7017,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G77" s="29" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G77" s="29" t="s">
+      <x:c r="H77" s="31">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I77" s="31">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J77" s="30" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="H77" s="31">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I77" s="31">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J77" s="30" t="s">
-        <x:v>226</x:v>
-      </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -7046,25 +7055,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G78" s="29" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="G78" s="29" t="s">
+      <x:c r="H78" s="31">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I78" s="31">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J78" s="30" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="H78" s="31">
-        <x:v>46126.5341923727</x:v>
-      </x:c>
-      <x:c r="I78" s="31">
-        <x:v>46126.5348242708</x:v>
-      </x:c>
-      <x:c r="J78" s="30" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -7090,19 +7099,19 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="H79" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I79" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J79" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -7122,25 +7131,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G80" s="29" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H80" s="31">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -7160,16 +7169,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="G81" s="29" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H81" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
         <x:v>91</x:v>
@@ -7178,7 +7187,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
@@ -7198,25 +7207,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="G82" s="29" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="H82" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
-        <x:v>237</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
@@ -7242,19 +7251,19 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="H83" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>171</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
@@ -7274,25 +7283,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="G84" s="29" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="H84" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I84" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
-        <x:v>242</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -7318,10 +7327,10 @@
         <x:v>244</x:v>
       </x:c>
       <x:c r="H85" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I85" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
         <x:v>245</x:v>
@@ -7330,7 +7339,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -7356,19 +7365,19 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -7388,25 +7397,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G87" s="29" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H87" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -7426,25 +7435,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G88" s="29" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="H88" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
-        <x:v>252</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
@@ -7470,19 +7479,19 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
@@ -7502,25 +7511,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F90" s="29" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G90" s="29" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="H90" s="31">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I90" s="31">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J90" s="30" t="s">
-        <x:v>257</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>21</x:v>
@@ -7546,10 +7555,10 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="H91" s="31">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I91" s="31">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J91" s="30" t="s">
         <x:v>260</x:v>
@@ -7558,7 +7567,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L91" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M91" s="29" t="s">
         <x:v>21</x:v>
@@ -7584,19 +7593,19 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="H92" s="31">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I92" s="31">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J92" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="K92" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L92" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M92" s="29" t="s">
         <x:v>21</x:v>
@@ -7616,86 +7625,123 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F93" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="G93" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="H93" s="31">
+        <x:v>46122.5945434491</x:v>
+      </x:c>
+      <x:c r="I93" s="31">
+        <x:v>46122.5999534606</x:v>
+      </x:c>
+      <x:c r="J93" s="30" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K93" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L93" s="33">
+        <x:v>46122.6007489699</x:v>
+      </x:c>
+      <x:c r="M93" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B94" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C94" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D94" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E94" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F94" s="29" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G94" s="29" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="H94" s="31">
         <x:v>46122.5911383796</x:v>
       </x:c>
-      <x:c r="I93" s="31">
+      <x:c r="I94" s="31">
         <x:v>46122.5921380556</x:v>
       </x:c>
-      <x:c r="J93" s="30" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="K93" s="32" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L93" s="33">
+      <x:c r="J94" s="30" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="K94" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L94" s="33">
         <x:v>46122.5928339699</x:v>
       </x:c>
-      <x:c r="M93" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="M94" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="96" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B96" s="17" t="s">
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B97" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C96" s="18" t="s"/>
-      <x:c r="D96" s="18" t="s"/>
-      <x:c r="E96" s="19" t="s"/>
-      <x:c r="F96" s="19" t="s"/>
-    </x:row>
-    <x:row r="97" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B97" s="20" t="s">
+      <x:c r="C97" s="18" t="s"/>
+      <x:c r="D97" s="18" t="s"/>
+      <x:c r="E97" s="19" t="s"/>
+      <x:c r="F97" s="19" t="s"/>
+    </x:row>
+    <x:row r="98" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B98" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C97" s="21" t="s"/>
-      <x:c r="D97" s="21" t="s"/>
-      <x:c r="E97" s="21" t="s"/>
-      <x:c r="F97" s="22" t="s">
+      <x:c r="C98" s="21" t="s"/>
+      <x:c r="D98" s="21" t="s"/>
+      <x:c r="E98" s="21" t="s"/>
+      <x:c r="F98" s="22" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B98" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C98" s="24" t="s"/>
-      <x:c r="D98" s="24" t="s"/>
-      <x:c r="E98" s="24" t="s"/>
-      <x:c r="F98" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:28" ht="18" customHeight="1">
       <x:c r="B99" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C99" s="24" t="s"/>
       <x:c r="D99" s="24" t="s"/>
       <x:c r="E99" s="24" t="s"/>
       <x:c r="F99" s="25" t="n">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B100" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B100" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C100" s="24" t="s"/>
+      <x:c r="D100" s="24" t="s"/>
+      <x:c r="E100" s="24" t="s"/>
+      <x:c r="F100" s="25" t="n">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B101" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C100" s="27" t="s"/>
-      <x:c r="D100" s="27" t="s"/>
-      <x:c r="E100" s="27" t="s"/>
-      <x:c r="F100" s="28" t="n">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C101" s="27" t="s"/>
+      <x:c r="D101" s="27" t="s"/>
+      <x:c r="E101" s="27" t="s"/>
+      <x:c r="F101" s="28" t="n">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
     <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8594,11 +8640,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B96:F96"/>
-    <x:mergeCell ref="B97:E97"/>
+    <x:mergeCell ref="B97:F97"/>
     <x:mergeCell ref="B98:E98"/>
     <x:mergeCell ref="B99:E99"/>
     <x:mergeCell ref="B100:E100"/>
+    <x:mergeCell ref="B101:E101"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="269">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="272">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -230,6 +230,63 @@
     <x:t>aszxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-09142</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1358-123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>edward123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08729</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1347-280</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1348-304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08984</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1354-199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>edwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-09014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1355-793</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123456</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-09141</x:t>
   </x:si>
   <x:si>
@@ -239,52 +296,439 @@
     <x:t>testzxcad</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08635</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1345-593</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08682</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1346-976</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08729</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1347-280</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08756</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1348-304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08984</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1354-199</x:t>
-  </x:si>
-  <x:si>
-    <x:t>edwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-09014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1355-793</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123456</x:t>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08369</x:t>
@@ -293,441 +737,6 @@
     <x:t>61-4-2026-1334-994</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08625</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1344-095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08169</x:t>
   </x:si>
   <x:si>
@@ -764,6 +773,60 @@
     <x:t>test12</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -773,64 +836,10 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08176</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4781,10 +4790,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="31">
-        <x:v>46142.575376088</x:v>
+        <x:v>46142.5874879051</x:v>
       </x:c>
       <x:c r="I18" s="31">
-        <x:v>46142.5762906829</x:v>
+        <x:v>46142.5907669907</x:v>
       </x:c>
       <x:c r="J18" s="30" t="s">
         <x:v>70</x:v>
@@ -4793,7 +4802,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46142.5767170718</x:v>
+        <x:v>46142.6055910417</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
@@ -5032,13 +5041,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D25" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F25" s="29" t="s">
         <x:v>87</x:v>
@@ -5047,19 +5056,19 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46142.575376088</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46142.5762906829</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46142.5767170718</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -5079,25 +5088,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="29" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G26" s="29" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -5123,19 +5132,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -5161,19 +5170,19 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -5193,25 +5202,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="29" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G29" s="29" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H29" s="31">
+        <x:v>46120.2362105324</x:v>
+      </x:c>
+      <x:c r="I29" s="31">
+        <x:v>46120.5226826273</x:v>
+      </x:c>
+      <x:c r="J29" s="30" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G29" s="29" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H29" s="31">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I29" s="31">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J29" s="30" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -5237,19 +5246,19 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -5269,25 +5278,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G31" s="29" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H31" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
-        <x:v>104</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -5313,10 +5322,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="31">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
         <x:v>107</x:v>
@@ -5325,7 +5334,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
@@ -5351,10 +5360,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
         <x:v>110</x:v>
@@ -5363,7 +5372,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -5389,10 +5398,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
         <x:v>113</x:v>
@@ -5401,7 +5410,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -5427,19 +5436,19 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
@@ -5459,25 +5468,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="29" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G36" s="29" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -5503,10 +5512,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
         <x:v>121</x:v>
@@ -5515,7 +5524,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
@@ -5541,19 +5550,19 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="H38" s="31">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I38" s="31">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
@@ -5573,25 +5582,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G39" s="29" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
@@ -5611,25 +5620,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G40" s="29" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H40" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I40" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
@@ -5649,16 +5658,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G41" s="29" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H41" s="31">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I41" s="31">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
         <x:v>46</x:v>
@@ -5667,7 +5676,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
@@ -5687,25 +5696,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G42" s="29" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H42" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I42" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
-        <x:v>132</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -5731,10 +5740,10 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="H43" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I43" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
         <x:v>135</x:v>
@@ -5743,7 +5752,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -5769,10 +5778,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="H44" s="31">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I44" s="31">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
         <x:v>138</x:v>
@@ -5781,7 +5790,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -5807,10 +5816,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="H45" s="31">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I45" s="31">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J45" s="30" t="s">
         <x:v>141</x:v>
@@ -5819,7 +5828,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -5845,10 +5854,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="H46" s="31">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
         <x:v>144</x:v>
@@ -5857,7 +5866,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
@@ -5883,10 +5892,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="H47" s="31">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I47" s="31">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J47" s="30" t="s">
         <x:v>147</x:v>
@@ -5895,7 +5904,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -5921,10 +5930,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
         <x:v>150</x:v>
@@ -5933,7 +5942,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -5959,19 +5968,19 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -5991,25 +6000,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="29" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G50" s="29" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H50" s="31">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I50" s="31">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -6029,25 +6038,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F51" s="29" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G51" s="29" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
-        <x:v>157</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -6073,10 +6082,10 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
         <x:v>160</x:v>
@@ -6085,7 +6094,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -6111,10 +6120,10 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
         <x:v>163</x:v>
@@ -6123,7 +6132,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -6149,10 +6158,10 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
         <x:v>166</x:v>
@@ -6161,7 +6170,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
@@ -6187,10 +6196,10 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
         <x:v>169</x:v>
@@ -6199,7 +6208,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
@@ -6225,19 +6234,19 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -6257,25 +6266,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="29" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G57" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>174</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
@@ -6301,19 +6310,19 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
@@ -6333,25 +6342,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="29" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G59" s="29" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -6371,25 +6380,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G60" s="29" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -6409,16 +6418,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F61" s="29" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G61" s="29" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
         <x:v>94</x:v>
@@ -6427,7 +6436,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -6447,25 +6456,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F62" s="29" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G62" s="29" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
-        <x:v>185</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -6491,19 +6500,19 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.150742662</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.153253125</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
@@ -6523,25 +6532,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G64" s="29" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H64" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I64" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
-        <x:v>190</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
@@ -6567,10 +6576,10 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H65" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I65" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J65" s="30" t="s">
         <x:v>193</x:v>
@@ -6579,7 +6588,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
@@ -6605,10 +6614,10 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
         <x:v>196</x:v>
@@ -6617,7 +6626,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -6643,10 +6652,10 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
         <x:v>199</x:v>
@@ -6655,7 +6664,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -6681,10 +6690,10 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
         <x:v>202</x:v>
@@ -6693,7 +6702,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -6719,19 +6728,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -6751,25 +6760,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G70" s="29" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H70" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
-        <x:v>207</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -6795,10 +6804,10 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="H71" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
         <x:v>210</x:v>
@@ -6807,7 +6816,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -6833,10 +6842,10 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H72" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
         <x:v>213</x:v>
@@ -6845,7 +6854,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
@@ -6871,19 +6880,19 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46132.4200429282</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46132.4214079282</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -6903,25 +6912,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="G74" s="29" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -6941,25 +6950,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G75" s="29" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H75" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>220</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
@@ -6985,19 +6994,19 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="H76" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
@@ -7017,25 +7026,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G77" s="29" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H77" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I77" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>225</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -7061,10 +7070,10 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="H78" s="31">
-        <x:v>46123.061368912</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I78" s="31">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J78" s="30" t="s">
         <x:v>228</x:v>
@@ -7073,7 +7082,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -7099,10 +7108,10 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="H79" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I79" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J79" s="30" t="s">
         <x:v>231</x:v>
@@ -7111,7 +7120,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -7137,19 +7146,19 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="H80" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -7169,25 +7178,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G81" s="29" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H81" s="31">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
@@ -7207,16 +7216,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="G82" s="29" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="H82" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
         <x:v>94</x:v>
@@ -7225,7 +7234,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
@@ -7245,25 +7254,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="G83" s="29" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="H83" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>240</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
@@ -7289,19 +7298,19 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="H84" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I84" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
-        <x:v>174</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -7321,25 +7330,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="G85" s="29" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="H85" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I85" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
-        <x:v>245</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -7365,10 +7374,10 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
         <x:v>248</x:v>
@@ -7377,7 +7386,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -7403,19 +7412,19 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="H87" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -7435,25 +7444,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="G88" s="29" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="H88" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
@@ -7473,25 +7482,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F89" s="29" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G89" s="29" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
-        <x:v>255</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
@@ -7517,19 +7526,19 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="H90" s="31">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I90" s="31">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J90" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>21</x:v>
@@ -7549,25 +7558,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F91" s="29" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G91" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="H91" s="31">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I91" s="31">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J91" s="30" t="s">
-        <x:v>260</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K91" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L91" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M91" s="29" t="s">
         <x:v>21</x:v>
@@ -7593,10 +7602,10 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="H92" s="31">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I92" s="31">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J92" s="30" t="s">
         <x:v>263</x:v>
@@ -7605,7 +7614,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L92" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M92" s="29" t="s">
         <x:v>21</x:v>
@@ -7631,19 +7640,19 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="H93" s="31">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I93" s="31">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J93" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="K93" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L93" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M93" s="29" t="s">
         <x:v>21</x:v>
@@ -7663,86 +7672,123 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F94" s="29" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="G94" s="29" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="H94" s="31">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I94" s="31">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J94" s="30" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="K94" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L94" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M94" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B95" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C95" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D95" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E95" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F95" s="29" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G95" s="29" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H95" s="31">
+        <x:v>46122.5945434491</x:v>
+      </x:c>
+      <x:c r="I95" s="31">
+        <x:v>46122.5999534606</x:v>
+      </x:c>
+      <x:c r="J95" s="30" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K95" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L95" s="33">
+        <x:v>46122.6007489699</x:v>
+      </x:c>
+      <x:c r="M95" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="97" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B97" s="17" t="s">
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B98" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C97" s="18" t="s"/>
-      <x:c r="D97" s="18" t="s"/>
-      <x:c r="E97" s="19" t="s"/>
-      <x:c r="F97" s="19" t="s"/>
-    </x:row>
-    <x:row r="98" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B98" s="20" t="s">
+      <x:c r="C98" s="18" t="s"/>
+      <x:c r="D98" s="18" t="s"/>
+      <x:c r="E98" s="19" t="s"/>
+      <x:c r="F98" s="19" t="s"/>
+    </x:row>
+    <x:row r="99" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B99" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C98" s="21" t="s"/>
-      <x:c r="D98" s="21" t="s"/>
-      <x:c r="E98" s="21" t="s"/>
-      <x:c r="F98" s="22" t="s">
+      <x:c r="C99" s="21" t="s"/>
+      <x:c r="D99" s="21" t="s"/>
+      <x:c r="E99" s="21" t="s"/>
+      <x:c r="F99" s="22" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B99" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C99" s="24" t="s"/>
-      <x:c r="D99" s="24" t="s"/>
-      <x:c r="E99" s="24" t="s"/>
-      <x:c r="F99" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:28" ht="18" customHeight="1">
       <x:c r="B100" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C100" s="24" t="s"/>
       <x:c r="D100" s="24" t="s"/>
       <x:c r="E100" s="24" t="s"/>
       <x:c r="F100" s="25" t="n">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B101" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B101" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C101" s="24" t="s"/>
+      <x:c r="D101" s="24" t="s"/>
+      <x:c r="E101" s="24" t="s"/>
+      <x:c r="F101" s="25" t="n">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B102" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C101" s="27" t="s"/>
-      <x:c r="D101" s="27" t="s"/>
-      <x:c r="E101" s="27" t="s"/>
-      <x:c r="F101" s="28" t="n">
-        <x:v>87</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C102" s="27" t="s"/>
+      <x:c r="D102" s="27" t="s"/>
+      <x:c r="E102" s="27" t="s"/>
+      <x:c r="F102" s="28" t="n">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
     <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8640,11 +8686,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B97:F97"/>
-    <x:mergeCell ref="B98:E98"/>
+    <x:mergeCell ref="B98:F98"/>
     <x:mergeCell ref="B99:E99"/>
     <x:mergeCell ref="B100:E100"/>
     <x:mergeCell ref="B101:E101"/>
+    <x:mergeCell ref="B102:E102"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -104,15 +104,21 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-06446</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1085-817</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-07610</x:t>
   </x:si>
   <x:si>
     <x:t>61-3-2026-1161-496</x:t>
   </x:si>
   <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-07584</x:t>
   </x:si>
   <x:si>
@@ -125,12 +131,6 @@
     <x:t>61-3-2026-1159-185</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-06446</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1085-817</x:t>
-  </x:si>
-  <x:si>
     <x:t>Amateur Radio Operator Certificate (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -149,6 +149,531 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08219</x:t>
   </x:si>
   <x:si>
@@ -164,9 +689,6 @@
     <x:t>61-4-2026-1321-473</x:t>
   </x:si>
   <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08292</x:t>
   </x:si>
   <x:si>
@@ -203,6 +725,15 @@
     <x:t>asdxzcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08338</x:t>
   </x:si>
   <x:si>
@@ -212,15 +743,6 @@
     <x:t>asdqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1327-230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qweasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08340</x:t>
   </x:si>
   <x:si>
@@ -230,6 +752,87 @@
     <x:t>aszxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08729</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1347-280</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1348-304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08984</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1354-199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>edwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-09014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1355-793</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123456</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-09141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1357-087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>testzxcad</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-09142</x:t>
   </x:si>
   <x:si>
@@ -237,609 +840,6 @@
   </x:si>
   <x:si>
     <x:t>edward123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08635</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1345-593</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08682</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1346-976</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08729</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1347-280</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08756</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1348-304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08984</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1354-199</x:t>
-  </x:si>
-  <x:si>
-    <x:t>edwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-09014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1355-793</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123456</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-09141</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1357-087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>testzxcad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08625</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1344-095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3043,10 +3043,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H8" s="31">
-        <x:v>46106.5066742245</x:v>
+        <x:v>46078.2888967361</x:v>
       </x:c>
       <x:c r="I8" s="31">
-        <x:v>46106.5082381134</x:v>
+        <x:v>46078.2901145602</x:v>
       </x:c>
       <x:c r="J8" s="30" t="s">
         <x:v>28</x:v>
@@ -3055,7 +3055,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L8" s="33">
-        <x:v>46106.5099302546</x:v>
+        <x:v>46089.2508762037</x:v>
       </x:c>
       <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
@@ -3081,10 +3081,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H9" s="31">
-        <x:v>46105.676846794</x:v>
+        <x:v>46106.5066742245</x:v>
       </x:c>
       <x:c r="I9" s="31">
-        <x:v>46106.5084437037</x:v>
+        <x:v>46106.5082381134</x:v>
       </x:c>
       <x:c r="J9" s="30" t="s">
         <x:v>28</x:v>
@@ -3093,7 +3093,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="33">
-        <x:v>46106.5101144792</x:v>
+        <x:v>46106.5099302546</x:v>
       </x:c>
       <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
@@ -3119,10 +3119,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>46105.6741278125</x:v>
+        <x:v>46105.676846794</x:v>
       </x:c>
       <x:c r="I10" s="31">
-        <x:v>46106.5086548727</x:v>
+        <x:v>46106.5084437037</x:v>
       </x:c>
       <x:c r="J10" s="30" t="s">
         <x:v>28</x:v>
@@ -3131,7 +3131,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>46106.5103567593</x:v>
+        <x:v>46106.5101144792</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
@@ -3157,10 +3157,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46078.2888967361</x:v>
+        <x:v>46105.6741278125</x:v>
       </x:c>
       <x:c r="I11" s="31">
-        <x:v>46078.2901145602</x:v>
+        <x:v>46106.5086548727</x:v>
       </x:c>
       <x:c r="J11" s="30" t="s">
         <x:v>28</x:v>
@@ -3169,7 +3169,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46089.2508762037</x:v>
+        <x:v>46106.5103567593</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
@@ -4433,13 +4433,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F9" s="29" t="s">
         <x:v>41</x:v>
@@ -4448,19 +4448,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="31">
-        <x:v>46124.9835281713</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I9" s="31">
-        <x:v>46125.0608962963</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J9" s="30" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="K9" s="32" t="n">
-        <x:v>240</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="33">
-        <x:v>46126.1641622569</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
@@ -4471,13 +4471,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
         <x:v>44</x:v>
@@ -4486,10 +4486,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I10" s="31">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J10" s="30" t="s">
         <x:v>46</x:v>
@@ -4498,7 +4498,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>46126.176386169</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
@@ -4509,13 +4509,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
         <x:v>47</x:v>
@@ -4524,10 +4524,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I11" s="31">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J11" s="30" t="s">
         <x:v>49</x:v>
@@ -4536,7 +4536,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
@@ -4547,13 +4547,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D12" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
         <x:v>50</x:v>
@@ -4562,10 +4562,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J12" s="30" t="s">
         <x:v>52</x:v>
@@ -4574,7 +4574,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
@@ -4585,13 +4585,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D13" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E13" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="29" t="s">
         <x:v>53</x:v>
@@ -4600,10 +4600,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>46126.4381590509</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I13" s="31">
-        <x:v>46126.4434486343</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J13" s="30" t="s">
         <x:v>55</x:v>
@@ -4612,7 +4612,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>46126.444417662</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
@@ -4623,13 +4623,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D14" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F14" s="29" t="s">
         <x:v>56</x:v>
@@ -4638,10 +4638,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H14" s="31">
-        <x:v>46126.4485157523</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I14" s="31">
-        <x:v>46126.4527227431</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J14" s="30" t="s">
         <x:v>58</x:v>
@@ -4650,7 +4650,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="33">
-        <x:v>46126.4533495949</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
@@ -4661,13 +4661,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D15" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="29" t="s">
         <x:v>59</x:v>
@@ -4676,10 +4676,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46126.455832662</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I15" s="31">
-        <x:v>46126.4740829051</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J15" s="30" t="s">
         <x:v>61</x:v>
@@ -4688,7 +4688,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
         <x:v>21</x:v>
@@ -4699,13 +4699,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D16" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E16" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F16" s="29" t="s">
         <x:v>62</x:v>
@@ -4714,19 +4714,19 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J16" s="30" t="s">
-        <x:v>64</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K16" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
@@ -4737,34 +4737,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D17" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F17" s="29" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G17" s="29" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G17" s="29" t="s">
+      <x:c r="H17" s="31">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I17" s="31">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J17" s="30" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="H17" s="31">
-        <x:v>46126.4798427199</x:v>
-      </x:c>
-      <x:c r="I17" s="31">
-        <x:v>46126.4809562153</x:v>
-      </x:c>
-      <x:c r="J17" s="30" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="K17" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
@@ -4775,34 +4775,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D18" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F18" s="29" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G18" s="29" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G18" s="29" t="s">
+      <x:c r="H18" s="31">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I18" s="31">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J18" s="30" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H18" s="31">
-        <x:v>46142.5874879051</x:v>
-      </x:c>
-      <x:c r="I18" s="31">
-        <x:v>46142.5907669907</x:v>
-      </x:c>
-      <x:c r="J18" s="30" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="K18" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46142.6055910417</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
@@ -4813,34 +4813,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D19" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E19" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="29" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G19" s="29" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G19" s="29" t="s">
+      <x:c r="H19" s="31">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I19" s="31">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J19" s="30" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H19" s="31">
-        <x:v>46133.0575652778</x:v>
-      </x:c>
-      <x:c r="I19" s="31">
-        <x:v>46134.4546264699</x:v>
-      </x:c>
-      <x:c r="J19" s="30" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="K19" s="32" t="n">
-        <x:v>361</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46134.4615905556</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>21</x:v>
@@ -4851,34 +4851,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D20" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E20" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="29" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G20" s="29" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G20" s="29" t="s">
+      <x:c r="H20" s="31">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I20" s="31">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J20" s="30" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="H20" s="31">
-        <x:v>46133.5419909606</x:v>
-      </x:c>
-      <x:c r="I20" s="31">
-        <x:v>46133.5429334722</x:v>
-      </x:c>
-      <x:c r="J20" s="30" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="K20" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46133.5457238194</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>21</x:v>
@@ -4889,13 +4889,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D21" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E21" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
         <x:v>76</x:v>
@@ -4904,19 +4904,19 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="31">
-        <x:v>46134.4519824769</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46134.4543351736</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46134.4551470833</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>21</x:v>
@@ -4927,34 +4927,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D22" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E22" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G22" s="29" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H22" s="31">
-        <x:v>46134.9871842824</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I22" s="31">
-        <x:v>46135.0270460764</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J22" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
-        <x:v>270</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46135.0715283333</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
         <x:v>21</x:v>
@@ -4965,34 +4965,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D23" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G23" s="29" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H23" s="31">
-        <x:v>46139.4236006019</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I23" s="31">
-        <x:v>46139.424377581</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J23" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46139.4248658449</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
@@ -5003,34 +5003,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D24" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F24" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G24" s="29" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46140.5605711921</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46140.5613520833</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46140.562271713</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
@@ -5041,34 +5041,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D25" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G25" s="29" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46142.575376088</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46142.5762906829</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46142.5767170718</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -5088,25 +5088,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="29" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G26" s="29" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H26" s="31">
+        <x:v>46119.8023724884</x:v>
+      </x:c>
+      <x:c r="I26" s="31">
+        <x:v>46119.8046602662</x:v>
+      </x:c>
+      <x:c r="J26" s="30" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G26" s="29" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H26" s="31">
-        <x:v>46126.5341923727</x:v>
-      </x:c>
-      <x:c r="I26" s="31">
-        <x:v>46126.5348242708</x:v>
-      </x:c>
-      <x:c r="J26" s="30" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -5126,25 +5126,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="29" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G27" s="29" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -5170,19 +5170,19 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
         <x:v>97</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -5214,7 +5214,7 @@
         <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
@@ -5246,19 +5246,19 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -5278,25 +5278,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G31" s="29" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G31" s="29" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="H31" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -5316,10 +5316,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F32" s="29" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G32" s="29" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="G32" s="29" t="s">
-        <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="31">
         <x:v>46121.0999663542</x:v>
@@ -5328,7 +5328,7 @@
         <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
@@ -5354,25 +5354,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="29" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G33" s="29" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G33" s="29" t="s">
-        <x:v>109</x:v>
-      </x:c>
       <x:c r="H33" s="31">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
-        <x:v>110</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -5392,25 +5392,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="29" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G34" s="29" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -5430,10 +5430,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="29" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G35" s="29" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H35" s="31">
         <x:v>46121.4966047917</x:v>
@@ -5442,7 +5442,7 @@
         <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
@@ -5468,25 +5468,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="29" t="s">
-        <x:v>117</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G36" s="29" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -5506,25 +5506,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F37" s="29" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G37" s="29" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H37" s="31">
+        <x:v>46122.1996025926</x:v>
+      </x:c>
+      <x:c r="I37" s="31">
+        <x:v>46122.2050823032</x:v>
+      </x:c>
+      <x:c r="J37" s="30" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G37" s="29" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H37" s="31">
-        <x:v>46121.5178724884</x:v>
-      </x:c>
-      <x:c r="I37" s="31">
-        <x:v>46122.2064690394</x:v>
-      </x:c>
-      <x:c r="J37" s="30" t="s">
-        <x:v>121</x:v>
-      </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
@@ -5544,25 +5544,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G38" s="29" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H38" s="31">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I38" s="31">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
@@ -5582,25 +5582,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G39" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
@@ -5620,25 +5620,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G40" s="29" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H40" s="31">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I40" s="31">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J40" s="30" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="G40" s="29" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="H40" s="31">
-        <x:v>46121.2273626852</x:v>
-      </x:c>
-      <x:c r="I40" s="31">
-        <x:v>46121.228379213</x:v>
-      </x:c>
-      <x:c r="J40" s="30" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
@@ -5658,25 +5658,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G41" s="29" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="G41" s="29" t="s">
+      <x:c r="H41" s="31">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I41" s="31">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J41" s="30" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="H41" s="31">
-        <x:v>46119.8017436343</x:v>
-      </x:c>
-      <x:c r="I41" s="31">
-        <x:v>46119.8048384144</x:v>
-      </x:c>
-      <x:c r="J41" s="30" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
@@ -5702,19 +5702,19 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H42" s="31">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I42" s="31">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -5740,19 +5740,19 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="H43" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I43" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
-        <x:v>135</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -5772,25 +5772,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G44" s="29" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G44" s="29" t="s">
-        <x:v>137</x:v>
-      </x:c>
       <x:c r="H44" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I44" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -5810,25 +5810,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F45" s="29" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G45" s="29" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H45" s="31">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I45" s="31">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J45" s="30" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="G45" s="29" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="H45" s="31">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I45" s="31">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J45" s="30" t="s">
-        <x:v>141</x:v>
-      </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -5848,25 +5848,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="29" t="s">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G46" s="29" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H46" s="31">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
@@ -5886,25 +5886,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="29" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G47" s="29" t="s">
-        <x:v>146</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H47" s="31">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I47" s="31">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J47" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -5924,25 +5924,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="29" t="s">
-        <x:v>148</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G48" s="29" t="s">
-        <x:v>149</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -5962,25 +5962,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F49" s="29" t="s">
-        <x:v>151</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G49" s="29" t="s">
-        <x:v>152</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>153</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -6000,25 +6000,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="29" t="s">
-        <x:v>154</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G50" s="29" t="s">
-        <x:v>155</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H50" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I50" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -6038,25 +6038,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F51" s="29" t="s">
-        <x:v>156</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G51" s="29" t="s">
-        <x:v>157</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -6076,25 +6076,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F52" s="29" t="s">
-        <x:v>158</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G52" s="29" t="s">
-        <x:v>159</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
-        <x:v>160</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -6114,25 +6114,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="29" t="s">
-        <x:v>161</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G53" s="29" t="s">
-        <x:v>162</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>163</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -6152,25 +6152,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="29" t="s">
-        <x:v>164</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G54" s="29" t="s">
-        <x:v>165</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
@@ -6190,25 +6190,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="29" t="s">
-        <x:v>167</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G55" s="29" t="s">
-        <x:v>168</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>169</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
@@ -6228,25 +6228,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
-        <x:v>170</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G56" s="29" t="s">
-        <x:v>171</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>172</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -6266,25 +6266,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G57" s="29" t="s">
-        <x:v>174</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
@@ -6304,25 +6304,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="29" t="s">
-        <x:v>175</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G58" s="29" t="s">
-        <x:v>176</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>177</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
@@ -6342,25 +6342,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="29" t="s">
-        <x:v>178</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G59" s="29" t="s">
-        <x:v>179</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -6380,25 +6380,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
-        <x:v>180</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G60" s="29" t="s">
-        <x:v>181</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -6418,25 +6418,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F61" s="29" t="s">
-        <x:v>182</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G61" s="29" t="s">
-        <x:v>183</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -6456,25 +6456,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F62" s="29" t="s">
-        <x:v>184</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G62" s="29" t="s">
-        <x:v>185</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -6494,25 +6494,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="29" t="s">
-        <x:v>186</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G63" s="29" t="s">
-        <x:v>187</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
@@ -6532,25 +6532,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
-        <x:v>189</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G64" s="29" t="s">
-        <x:v>190</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H64" s="31">
-        <x:v>46124.150742662</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I64" s="31">
-        <x:v>46124.153253125</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
@@ -6570,25 +6570,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F65" s="29" t="s">
-        <x:v>191</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G65" s="29" t="s">
-        <x:v>192</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H65" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I65" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J65" s="30" t="s">
-        <x:v>193</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
@@ -6608,25 +6608,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="29" t="s">
-        <x:v>194</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G66" s="29" t="s">
-        <x:v>195</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
-        <x:v>196</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -6646,25 +6646,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="29" t="s">
-        <x:v>197</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G67" s="29" t="s">
-        <x:v>198</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
-        <x:v>199</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -6684,25 +6684,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="29" t="s">
-        <x:v>200</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G68" s="29" t="s">
-        <x:v>201</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
-        <x:v>202</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -6722,25 +6722,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="29" t="s">
-        <x:v>203</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G69" s="29" t="s">
-        <x:v>204</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
-        <x:v>205</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -6760,25 +6760,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
-        <x:v>206</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G70" s="29" t="s">
-        <x:v>207</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H70" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -6798,25 +6798,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="29" t="s">
-        <x:v>208</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G71" s="29" t="s">
-        <x:v>209</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H71" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
-        <x:v>210</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -6836,10 +6836,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
-        <x:v>211</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G72" s="29" t="s">
-        <x:v>212</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H72" s="31">
         <x:v>46124.7029179398</x:v>
@@ -6848,7 +6848,7 @@
         <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>213</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
@@ -6874,25 +6874,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
-        <x:v>214</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G73" s="29" t="s">
-        <x:v>215</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>216</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -6912,25 +6912,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
-        <x:v>217</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G74" s="29" t="s">
-        <x:v>218</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46132.4200429282</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46132.4214079282</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -6941,34 +6941,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C75" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D75" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E75" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
-        <x:v>219</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="G75" s="29" t="s">
-        <x:v>220</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="H75" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46124.9835281713</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46125.0608962963</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46126.1641622569</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
@@ -6979,34 +6979,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C76" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D76" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E76" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F76" s="29" t="s">
-        <x:v>221</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G76" s="29" t="s">
-        <x:v>222</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H76" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>223</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
@@ -7017,34 +7017,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C77" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D77" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E77" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
-        <x:v>224</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="G77" s="29" t="s">
-        <x:v>225</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H77" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I77" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>28</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -7055,34 +7055,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C78" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D78" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E78" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G78" s="29" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H78" s="31">
+        <x:v>46126.2608066551</x:v>
+      </x:c>
+      <x:c r="I78" s="31">
+        <x:v>46126.2618529282</x:v>
+      </x:c>
+      <x:c r="J78" s="30" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="G78" s="29" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="H78" s="31">
-        <x:v>46123.4191184375</x:v>
-      </x:c>
-      <x:c r="I78" s="31">
-        <x:v>46123.4205974074</x:v>
-      </x:c>
-      <x:c r="J78" s="30" t="s">
-        <x:v>228</x:v>
-      </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -7093,34 +7093,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C79" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D79" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E79" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G79" s="29" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H79" s="31">
+        <x:v>46126.4381590509</x:v>
+      </x:c>
+      <x:c r="I79" s="31">
+        <x:v>46126.4434486343</x:v>
+      </x:c>
+      <x:c r="J79" s="30" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="G79" s="29" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="H79" s="31">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I79" s="31">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J79" s="30" t="s">
-        <x:v>231</x:v>
-      </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -7131,34 +7131,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C80" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D80" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E80" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G80" s="29" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="H80" s="31">
+        <x:v>46126.4485157523</x:v>
+      </x:c>
+      <x:c r="I80" s="31">
+        <x:v>46126.4527227431</x:v>
+      </x:c>
+      <x:c r="J80" s="30" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="G80" s="29" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="H80" s="31">
-        <x:v>46122.3767795718</x:v>
-      </x:c>
-      <x:c r="I80" s="31">
-        <x:v>46122.3776183449</x:v>
-      </x:c>
-      <x:c r="J80" s="30" t="s">
-        <x:v>234</x:v>
-      </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -7169,34 +7169,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C81" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D81" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E81" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G81" s="29" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H81" s="31">
+        <x:v>46126.4716621296</x:v>
+      </x:c>
+      <x:c r="I81" s="31">
+        <x:v>46126.4737503704</x:v>
+      </x:c>
+      <x:c r="J81" s="30" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="G81" s="29" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="H81" s="31">
-        <x:v>46127.1221474769</x:v>
-      </x:c>
-      <x:c r="I81" s="31">
-        <x:v>46127.1231965625</x:v>
-      </x:c>
-      <x:c r="J81" s="30" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
@@ -7207,34 +7207,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C82" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D82" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E82" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G82" s="29" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="G82" s="29" t="s">
+      <x:c r="H82" s="31">
+        <x:v>46126.455832662</x:v>
+      </x:c>
+      <x:c r="I82" s="31">
+        <x:v>46126.4740829051</x:v>
+      </x:c>
+      <x:c r="J82" s="30" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="H82" s="31">
-        <x:v>46122.3885020718</x:v>
-      </x:c>
-      <x:c r="I82" s="31">
-        <x:v>46122.3892655903</x:v>
-      </x:c>
-      <x:c r="J82" s="30" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
@@ -7245,13 +7245,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C83" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D83" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E83" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
         <x:v>239</x:v>
@@ -7260,19 +7260,19 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="H83" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
@@ -7292,25 +7292,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="G84" s="29" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H84" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I84" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
-        <x:v>243</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -7336,19 +7336,19 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="H85" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I85" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
-        <x:v>177</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -7374,19 +7374,19 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
-        <x:v>248</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -7406,25 +7406,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G87" s="29" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="G87" s="29" t="s">
-        <x:v>250</x:v>
-      </x:c>
       <x:c r="H87" s="31">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
-        <x:v>251</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -7435,34 +7435,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C88" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D88" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E88" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
-        <x:v>252</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G88" s="29" t="s">
-        <x:v>253</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="H88" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46133.5419909606</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46133.5429334722</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46133.5457238194</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
@@ -7473,25 +7473,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C89" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D89" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E89" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F89" s="29" t="s">
-        <x:v>254</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="G89" s="29" t="s">
-        <x:v>255</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46134.4519824769</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46134.4543351736</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
         <x:v>28</x:v>
@@ -7500,7 +7500,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46134.4551470833</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
@@ -7511,34 +7511,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C90" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D90" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E90" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F90" s="29" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G90" s="29" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H90" s="31">
+        <x:v>46133.0575652778</x:v>
+      </x:c>
+      <x:c r="I90" s="31">
+        <x:v>46134.4546264699</x:v>
+      </x:c>
+      <x:c r="J90" s="30" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="G90" s="29" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="H90" s="31">
-        <x:v>46122.6819179514</x:v>
-      </x:c>
-      <x:c r="I90" s="31">
-        <x:v>46122.6826717361</x:v>
-      </x:c>
-      <x:c r="J90" s="30" t="s">
-        <x:v>258</x:v>
-      </x:c>
       <x:c r="K90" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46134.4615905556</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>21</x:v>
@@ -7549,34 +7549,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C91" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D91" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E91" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F91" s="29" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G91" s="29" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H91" s="31">
+        <x:v>46134.9871842824</x:v>
+      </x:c>
+      <x:c r="I91" s="31">
+        <x:v>46135.0270460764</x:v>
+      </x:c>
+      <x:c r="J91" s="30" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="G91" s="29" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="H91" s="31">
-        <x:v>46122.7261372338</x:v>
-      </x:c>
-      <x:c r="I91" s="31">
-        <x:v>46122.727234375</x:v>
-      </x:c>
-      <x:c r="J91" s="30" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="K91" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L91" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46135.0715283333</x:v>
       </x:c>
       <x:c r="M91" s="29" t="s">
         <x:v>21</x:v>
@@ -7587,34 +7587,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C92" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D92" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E92" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F92" s="29" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G92" s="29" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="G92" s="29" t="s">
+      <x:c r="H92" s="31">
+        <x:v>46139.4236006019</x:v>
+      </x:c>
+      <x:c r="I92" s="31">
+        <x:v>46139.424377581</x:v>
+      </x:c>
+      <x:c r="J92" s="30" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="H92" s="31">
-        <x:v>46122.9452935995</x:v>
-      </x:c>
-      <x:c r="I92" s="31">
-        <x:v>46123.0460683681</x:v>
-      </x:c>
-      <x:c r="J92" s="30" t="s">
-        <x:v>263</x:v>
-      </x:c>
       <x:c r="K92" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L92" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46139.4248658449</x:v>
       </x:c>
       <x:c r="M92" s="29" t="s">
         <x:v>21</x:v>
@@ -7625,34 +7625,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C93" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D93" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E93" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F93" s="29" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G93" s="29" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="G93" s="29" t="s">
+      <x:c r="H93" s="31">
+        <x:v>46140.5605711921</x:v>
+      </x:c>
+      <x:c r="I93" s="31">
+        <x:v>46140.5613520833</x:v>
+      </x:c>
+      <x:c r="J93" s="30" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="H93" s="31">
-        <x:v>46123.0476912847</x:v>
-      </x:c>
-      <x:c r="I93" s="31">
-        <x:v>46123.0484775694</x:v>
-      </x:c>
-      <x:c r="J93" s="30" t="s">
-        <x:v>266</x:v>
-      </x:c>
       <x:c r="K93" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L93" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46140.562271713</x:v>
       </x:c>
       <x:c r="M93" s="29" t="s">
         <x:v>21</x:v>
@@ -7663,34 +7663,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C94" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D94" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E94" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F94" s="29" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G94" s="29" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="G94" s="29" t="s">
+      <x:c r="H94" s="31">
+        <x:v>46142.575376088</x:v>
+      </x:c>
+      <x:c r="I94" s="31">
+        <x:v>46142.5762906829</x:v>
+      </x:c>
+      <x:c r="J94" s="30" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="H94" s="31">
-        <x:v>46118.3446055671</x:v>
-      </x:c>
-      <x:c r="I94" s="31">
-        <x:v>46118.476906412</x:v>
-      </x:c>
-      <x:c r="J94" s="30" t="s">
-        <x:v>269</x:v>
-      </x:c>
       <x:c r="K94" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L94" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46142.5767170718</x:v>
       </x:c>
       <x:c r="M94" s="29" t="s">
         <x:v>21</x:v>
@@ -7701,34 +7701,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C95" s="29" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D95" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E95" s="29" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F95" s="29" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="G95" s="29" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="G95" s="29" t="s">
+      <x:c r="H95" s="31">
+        <x:v>46142.5874879051</x:v>
+      </x:c>
+      <x:c r="I95" s="31">
+        <x:v>46142.5907669907</x:v>
+      </x:c>
+      <x:c r="J95" s="30" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="H95" s="31">
-        <x:v>46122.5945434491</x:v>
-      </x:c>
-      <x:c r="I95" s="31">
-        <x:v>46122.5999534606</x:v>
-      </x:c>
-      <x:c r="J95" s="30" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="K95" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L95" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46142.6055910417</x:v>
       </x:c>
       <x:c r="M95" s="29" t="s">
         <x:v>21</x:v>
